--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.7941601539378</v>
+        <v>582.1736849330782</v>
       </c>
       <c r="E2" t="n">
-        <v>10812.05611551268</v>
+        <v>10654.0882820394</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6889356122733441</v>
+        <v>0.6889519930512242</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027460727855696</v>
+        <v>0.5027460603346304</v>
       </c>
       <c r="H2" t="n">
-        <v>1.370345089830642</v>
+        <v>1.370377706376563</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.7666982572273</v>
+        <v>227.9718057593025</v>
       </c>
       <c r="E3" t="n">
-        <v>4621.332588748673</v>
+        <v>4537.548628114438</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2923231889570972</v>
+        <v>0.2934558435021475</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035695943829423</v>
+        <v>0.6035694238472759</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4843239150506794</v>
+        <v>0.4862006455389994</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890893543925698</v>
+        <v>0.8908919506899777</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069558339792266</v>
+        <v>1.069556151330593</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.57874383121582</v>
+        <v>40.43509103881406</v>
       </c>
       <c r="E4" t="n">
-        <v>1853.5702356038</v>
+        <v>1837.245403097487</v>
       </c>
       <c r="F4" t="n">
-        <v>1.016977254755218</v>
+        <v>1.008300761016785</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117646001166036</v>
+        <v>1.117666544391411</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9099278785001769</v>
+        <v>0.9021481103434322</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715994521315699</v>
+        <v>0.4715956391374816</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048404493557829</v>
+        <v>1.048415313277674</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.55905523301573</v>
+        <v>37.62480476172951</v>
       </c>
       <c r="E5" t="n">
-        <v>410.7749134883818</v>
+        <v>409.7159473053212</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3292103058639745</v>
+        <v>-0.3276894725897286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672379865692722</v>
+        <v>0.5672486428331284</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5803742232692851</v>
+        <v>-0.5776822505084906</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367438402745192</v>
+        <v>0.7367249789198101</v>
       </c>
       <c r="N5" t="n">
-        <v>0.831252823635437</v>
+        <v>0.831247179053709</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.9789697341369</v>
+        <v>10.98246406382997</v>
       </c>
       <c r="E6" t="n">
-        <v>204.6921697262349</v>
+        <v>202.7417695749178</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2996727616349352</v>
+        <v>-0.3012170498787368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204457391912906</v>
+        <v>0.720440540929546</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.415954658807923</v>
+        <v>-0.4181011933199824</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500342677876666</v>
+        <v>0.7500436783722113</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074814944811229</v>
+        <v>1.074820701742734</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.34906323177876</v>
+        <v>10.42744578281679</v>
       </c>
       <c r="E7" t="n">
-        <v>408.0259941396155</v>
+        <v>405.7689207954464</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2809331589283122</v>
+        <v>-0.2774425232436629</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178155005286223</v>
+        <v>1.178181854885364</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2384517806806429</v>
+        <v>-0.2354836157875286</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386741234653758</v>
+        <v>0.7386521034641894</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731038118337193</v>
+        <v>1.731026007036555</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.25933794885514</v>
+        <v>10.19099693804041</v>
       </c>
       <c r="E8" t="n">
-        <v>759.4013625088545</v>
+        <v>767.7214589859027</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.535456250865347</v>
+        <v>-0.5381867004850073</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8100551828499041</v>
+        <v>0.8100969341492351</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6610120670810672</v>
+        <v>-0.6643485215139243</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6839002186184318</v>
+        <v>0.6838741161195164</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101941808465071</v>
+        <v>1.10195657116376</v>
       </c>
     </row>
     <row r="9">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.219524135088692</v>
+        <v>7.218244308731177</v>
       </c>
       <c r="E9" t="n">
-        <v>166.164436561925</v>
+        <v>162.8828100634881</v>
       </c>
       <c r="F9" t="n">
         <v>0.3928643262405387</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6829694320298093</v>
+        <v>0.6829693754219341</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6545161188956643</v>
+        <v>0.6545160808557942</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.204372421394607</v>
+        <v>7.204746707816485</v>
       </c>
       <c r="E10" t="n">
-        <v>255.1735974060878</v>
+        <v>253.1517807487819</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1956351689889653</v>
+        <v>-0.1953467108153244</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9664763449821313</v>
+        <v>0.9664770145059126</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2024210628689337</v>
+        <v>-0.202122459079061</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132358878638776</v>
+        <v>0.7132349705175235</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371120832816083</v>
+        <v>1.371120053110252</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.929058914882227</v>
+        <v>7.021394017113488</v>
       </c>
       <c r="E11" t="n">
-        <v>449.0498741121477</v>
+        <v>480.9082697566906</v>
       </c>
       <c r="F11" t="n">
-        <v>1.112962081427869</v>
+        <v>1.140524608231891</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283031451337263</v>
+        <v>0.8283983965322194</v>
       </c>
       <c r="H11" t="n">
-        <v>1.343665164096637</v>
+        <v>1.376782732808599</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626719692039768</v>
+        <v>0.6625756869996529</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091790281408576</v>
+        <v>1.09175721103893</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.749937788659317</v>
+        <v>6.710406590297964</v>
       </c>
       <c r="E12" t="n">
-        <v>217.6285913824485</v>
+        <v>198.3228804127422</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.224694496968972</v>
+        <v>-0.23285770698541</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6633030595694975</v>
+        <v>0.6632985681546437</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.338750882763612</v>
+        <v>-0.3510601683239586</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887329856786842</v>
+        <v>0.7887588206326823</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040622753521134</v>
+        <v>1.040649818313386</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.846901569897895</v>
+        <v>4.848044893826803</v>
       </c>
       <c r="E13" t="n">
-        <v>102.3481777683936</v>
+        <v>101.5182840682216</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3568981655110597</v>
+        <v>-0.358167107887967</v>
       </c>
       <c r="G13" t="n">
-        <v>0.858003459915345</v>
+        <v>0.8579997313295545</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4159635504806392</v>
+        <v>-0.4174443124043314</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603646451428473</v>
+        <v>0.7603709607473629</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297664032888677</v>
+        <v>1.297669204205784</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.800036888896847</v>
+        <v>4.811586633953631</v>
       </c>
       <c r="E14" t="n">
-        <v>189.1573933818396</v>
+        <v>188.0353136844516</v>
       </c>
       <c r="F14" t="n">
         <v>1.87910146821821</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021623006016987</v>
+        <v>0.6021623199447512</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037780284422189</v>
+        <v>1.037780343459971</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.391240811459147</v>
+        <v>4.378965313630967</v>
       </c>
       <c r="E15" t="n">
-        <v>535.7957460556536</v>
+        <v>505.2186135345202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05406544939091207</v>
+        <v>0.04728659660559975</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971502335774739</v>
+        <v>0.7971484869145068</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06782341284437135</v>
+        <v>0.05931968432710728</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169491017830131</v>
+        <v>0.716961087060872</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136788877897911</v>
+        <v>1.136805418916151</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.296305940859645</v>
+        <v>4.263875993004364</v>
       </c>
       <c r="E16" t="n">
-        <v>349.283404818921</v>
+        <v>338.5948812279979</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6104429724933922</v>
+        <v>0.6019454620971412</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9641495075682579</v>
+        <v>0.9641761982796232</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6331414035910559</v>
+        <v>0.6243106427758648</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129269671972416</v>
+        <v>0.512919701293126</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9836740844172246</v>
+        <v>0.9836874053003108</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.591373701297852</v>
+        <v>3.582230565708937</v>
       </c>
       <c r="E17" t="n">
-        <v>137.5615453431506</v>
+        <v>137.3834353945895</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1473631600406256</v>
+        <v>-0.1505927120910012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569088533340532</v>
+        <v>0.7569198029902</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1946907601774192</v>
+        <v>-0.1989546468411674</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230655236813368</v>
+        <v>0.7230614429034677</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088610585026805</v>
+        <v>1.088620216234051</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.278997441728102</v>
+        <v>3.292257964476142</v>
       </c>
       <c r="E18" t="n">
-        <v>67.47756866421132</v>
+        <v>65.64731313771426</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4367183380900247</v>
+        <v>-0.4329255340159142</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531496691282266</v>
+        <v>0.75320454964938</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5798559781557465</v>
+        <v>-0.5747781717694654</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641691108823716</v>
+        <v>0.7641021207356876</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14478012693407</v>
+        <v>1.144763209783856</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.965412225210599</v>
+        <v>2.982180566899578</v>
       </c>
       <c r="E19" t="n">
-        <v>107.9864318929289</v>
+        <v>107.2131323849335</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1173384145248852</v>
+        <v>0.1221061995620547</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859603087749947</v>
+        <v>0.4859789115517475</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2414567865031428</v>
+        <v>0.2512582267657775</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174838658273132</v>
+        <v>0.7174452368005919</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935284030099857</v>
+        <v>0.693517628057126</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.664423928310137</v>
+        <v>2.672715228580009</v>
       </c>
       <c r="E20" t="n">
-        <v>110.9367598356046</v>
+        <v>115.2130786466134</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2992682251916323</v>
+        <v>-0.297717647299041</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858122075888607</v>
+        <v>0.785814801648237</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3808393688740075</v>
+        <v>-0.3788649013413617</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320303836354435</v>
+        <v>0.73202439813805</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144192750426592</v>
+        <v>1.144187200276899</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.1736849330782</v>
+        <v>582.2479470639596</v>
       </c>
       <c r="E2" t="n">
-        <v>10654.0882820394</v>
+        <v>10425.97866732218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6889519930512242</v>
+        <v>0.6883459335502164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027460603346304</v>
+        <v>0.5027466101175823</v>
       </c>
       <c r="H2" t="n">
-        <v>1.370377706376563</v>
+        <v>1.369170710846218</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.9718057593025</v>
+        <v>227.807514738361</v>
       </c>
       <c r="E3" t="n">
-        <v>4537.548628114438</v>
+        <v>4448.902278917644</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2934558435021475</v>
+        <v>0.2910870212939418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035694238472759</v>
+        <v>0.6035708184794779</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4862006455389994</v>
+        <v>0.4822748422915</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908919506899777</v>
+        <v>0.8908941122648361</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069556151330593</v>
+        <v>1.069560048137318</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.43509103881406</v>
+        <v>40.56329515506579</v>
       </c>
       <c r="E4" t="n">
-        <v>1837.245403097487</v>
+        <v>1820.243744938659</v>
       </c>
       <c r="F4" t="n">
-        <v>1.008300761016785</v>
+        <v>1.017338999864816</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117666544391411</v>
+        <v>1.117645401554649</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9021481103434322</v>
+        <v>0.9102520338290607</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715956391374816</v>
+        <v>0.4716012803450228</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048415313277674</v>
+        <v>1.048406874830295</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.62480476172951</v>
+        <v>37.6252296409387</v>
       </c>
       <c r="E5" t="n">
-        <v>409.7159473053212</v>
+        <v>394.190746824506</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3276894725897286</v>
+        <v>-0.3280697702487327</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672486428331284</v>
+        <v>0.5672453716197403</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5776822505084906</v>
+        <v>-0.5783560107541225</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367249789198101</v>
+        <v>0.7367258319419823</v>
       </c>
       <c r="N5" t="n">
-        <v>0.831247179053709</v>
+        <v>0.8312424388581209</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.98246406382997</v>
+        <v>10.95365445458999</v>
       </c>
       <c r="E6" t="n">
-        <v>202.7417695749178</v>
+        <v>200.2481320734856</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3012170498787368</v>
+        <v>-0.3021431698630492</v>
       </c>
       <c r="G6" t="n">
-        <v>0.720440540929546</v>
+        <v>0.7204397448362025</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4181011933199824</v>
+        <v>-0.4193871479588397</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500436783722113</v>
+        <v>0.7500460755566655</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074820701742734</v>
+        <v>1.074821773861506</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.42744578281679</v>
+        <v>10.3994850609827</v>
       </c>
       <c r="E7" t="n">
-        <v>405.7689207954464</v>
+        <v>400.4513606821114</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2774425232436629</v>
+        <v>-0.2797701334874383</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178181854885364</v>
+        <v>1.178162353247244</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2354836157875286</v>
+        <v>-0.237463141405204</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386521034641894</v>
+        <v>0.7386634638383752</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731026007036555</v>
+        <v>1.731022084087336</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.19099693804041</v>
+        <v>10.18231175903888</v>
       </c>
       <c r="E8" t="n">
-        <v>767.7214589859027</v>
+        <v>764.6366737975469</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5381867004850073</v>
+        <v>-0.5398579982065965</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8100969341492351</v>
+        <v>0.8101374360385688</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6643485215139243</v>
+        <v>-0.6663782886597714</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838741161195164</v>
+        <v>0.683854022782732</v>
       </c>
       <c r="N8" t="n">
-        <v>1.10195657116376</v>
+        <v>1.101978080990522</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.218244308731177</v>
+        <v>7.212331609067717</v>
       </c>
       <c r="E9" t="n">
-        <v>162.8828100634881</v>
+        <v>161.2981291438276</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3928643262405387</v>
+        <v>0.3902296412280384</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4818010776436712</v>
+        <v>0.4818109226325031</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8154077366574343</v>
+        <v>0.8099227786201155</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6829693754219341</v>
+        <v>0.682964399547239</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6545160808557942</v>
+        <v>0.6545239706221955</v>
       </c>
     </row>
     <row r="10">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.204746707816485</v>
+        <v>7.197320975841724</v>
       </c>
       <c r="E10" t="n">
-        <v>253.1517807487819</v>
+        <v>251.4218345579497</v>
       </c>
       <c r="F10" t="n">
         <v>-0.1953467108153244</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132349705175235</v>
+        <v>0.7132327646682362</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371120053110252</v>
+        <v>1.371114313198723</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.021394017113488</v>
+        <v>6.974429735561252</v>
       </c>
       <c r="E11" t="n">
-        <v>480.9082697566906</v>
+        <v>493.3165838039113</v>
       </c>
       <c r="F11" t="n">
-        <v>1.140524608231891</v>
+        <v>1.122551290316251</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283983965322194</v>
+        <v>0.8283196064198393</v>
       </c>
       <c r="H11" t="n">
-        <v>1.376782732808599</v>
+        <v>1.355215162862242</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6625756869996529</v>
+        <v>0.6626471255277906</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09175721103893</v>
+        <v>1.091769880027723</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.710406590297964</v>
+        <v>6.583883833895602</v>
       </c>
       <c r="E12" t="n">
-        <v>198.3228804127422</v>
+        <v>186.7457082224712</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.23285770698541</v>
+        <v>-0.2371241165334191</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632985681546437</v>
+        <v>0.6633443209931454</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3510601683239586</v>
+        <v>-0.3574676213077422</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887588206326823</v>
+        <v>0.7887222437749557</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040649818313386</v>
+        <v>1.040672200905987</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.848044893826803</v>
+        <v>4.83761332499455</v>
       </c>
       <c r="E13" t="n">
-        <v>101.5182840682216</v>
+        <v>100.0465531560489</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.358167107887967</v>
+        <v>-0.3594353564350079</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8579997313295545</v>
+        <v>0.8579992555333531</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4174443124043314</v>
+        <v>-0.4189226903368047</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603709607473629</v>
+        <v>0.7603739067794982</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297669204205784</v>
+        <v>1.297672093286146</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.811586633953631</v>
+        <v>4.800267283194238</v>
       </c>
       <c r="E14" t="n">
-        <v>188.0353136844516</v>
+        <v>189.4074870935123</v>
       </c>
       <c r="F14" t="n">
-        <v>1.87910146821821</v>
+        <v>1.869440457917952</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664440830756235</v>
+        <v>0.8664479873405033</v>
       </c>
       <c r="H14" t="n">
-        <v>2.16875099608038</v>
+        <v>2.157591090558197</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021623199447512</v>
+        <v>0.6021657291483198</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037780343459971</v>
+        <v>1.03778976042019</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.378965313630967</v>
+        <v>4.384287921707398</v>
       </c>
       <c r="E15" t="n">
-        <v>505.2186135345202</v>
+        <v>488.229675281542</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04728659660559975</v>
+        <v>0.05049612348238286</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971484869145068</v>
+        <v>0.7971446591590274</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05931968432710728</v>
+        <v>0.06334624826522117</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.716961087060872</v>
+        <v>0.7169587654388395</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136805418916151</v>
+        <v>1.136795035919097</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.263875993004364</v>
+        <v>4.330854035858971</v>
       </c>
       <c r="E16" t="n">
-        <v>338.5948812279979</v>
+        <v>321.1968587466332</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6019454620971412</v>
+        <v>0.6388575807548829</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9641761982796232</v>
+        <v>0.9642093421316269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6243106427758648</v>
+        <v>0.6625714487919477</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.512919701293126</v>
+        <v>0.5128641811026061</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9836874053003108</v>
+        <v>0.9836136628512798</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.582230565708937</v>
+        <v>3.586013203798426</v>
       </c>
       <c r="E17" t="n">
-        <v>137.3834353945895</v>
+        <v>131.7462236264413</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1505927120910012</v>
+        <v>-0.1477432833242935</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569198029902</v>
+        <v>0.7569094396582937</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1989546468411674</v>
+        <v>-0.1951928138074115</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230614429034677</v>
+        <v>0.7230660105926248</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088620216234051</v>
+        <v>1.088610997865545</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.292257964476142</v>
+        <v>3.296527688201876</v>
       </c>
       <c r="E18" t="n">
-        <v>65.64731313771426</v>
+        <v>64.25412807340493</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4329255340159142</v>
+        <v>-0.4323477511422718</v>
       </c>
       <c r="G18" t="n">
-        <v>0.75320454964938</v>
+        <v>0.7532166804821104</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5747781717694654</v>
+        <v>-0.5740018275558363</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641021207356876</v>
+        <v>0.7640784500885812</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144763209783856</v>
+        <v>1.144744931584989</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.982180566899578</v>
+        <v>2.974473703245915</v>
       </c>
       <c r="E19" t="n">
-        <v>107.2131323849335</v>
+        <v>106.1480623686193</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1221061995620547</v>
+        <v>0.1182915220376524</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859789115517475</v>
+        <v>0.485961888313183</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2512582267657775</v>
+        <v>0.2434172820594075</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174452368005919</v>
+        <v>0.7174767796226631</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693517628057126</v>
+        <v>0.6935230663509494</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.672715228580009</v>
+        <v>2.665174250073577</v>
       </c>
       <c r="E20" t="n">
-        <v>115.2130786466134</v>
+        <v>114.6622606129304</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.297717647299041</v>
+        <v>-0.2997848736795705</v>
       </c>
       <c r="G20" t="n">
-        <v>0.785814801648237</v>
+        <v>0.7858123301057556</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3788649013413617</v>
+        <v>-0.3814967800762621</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.73202439813805</v>
+        <v>0.7320310450760283</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144187200276899</v>
+        <v>1.144192739770853</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.2479470639596</v>
+        <v>581.80400450902</v>
       </c>
       <c r="E2" t="n">
-        <v>10425.97866732218</v>
+        <v>10472.59067900769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6883459335502164</v>
+        <v>0.6890276572148026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027466101175823</v>
+        <v>0.5027460045592718</v>
       </c>
       <c r="H2" t="n">
-        <v>1.369170710846218</v>
+        <v>1.370528360178284</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.807514738361</v>
+        <v>227.9544674953138</v>
       </c>
       <c r="E3" t="n">
-        <v>4448.902278917644</v>
+        <v>4427.3103073516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2910870212939418</v>
+        <v>0.2938334560273506</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035708184794779</v>
+        <v>0.603569569026053</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4822748422915</v>
+        <v>0.4868261607381788</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908941122648361</v>
+        <v>0.8908912772017996</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069560048137318</v>
+        <v>1.069555718699631</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.56329515506579</v>
+        <v>40.81729871365842</v>
       </c>
       <c r="E4" t="n">
-        <v>1820.243744938659</v>
+        <v>1818.68284052118</v>
       </c>
       <c r="F4" t="n">
-        <v>1.017338999864816</v>
+        <v>1.036899854667185</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117645401554649</v>
+        <v>1.117643478632145</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9102520338290607</v>
+        <v>0.9277554734504598</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716012803450228</v>
+        <v>0.4715895220945894</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048406874830295</v>
+        <v>1.048380194333555</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.6252296409387</v>
+        <v>37.64368208969952</v>
       </c>
       <c r="E5" t="n">
-        <v>394.190746824506</v>
+        <v>389.6536223965315</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3280697702487327</v>
+        <v>-0.3269286986811221</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672453716197403</v>
+        <v>0.5672563995140377</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5783560107541225</v>
+        <v>-0.576333204810379</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367258319419823</v>
+        <v>0.7367131090129139</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312424388581209</v>
+        <v>0.8312452449220582</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.95365445458999</v>
+        <v>10.97927686612439</v>
       </c>
       <c r="E6" t="n">
-        <v>200.2481320734856</v>
+        <v>199.3238569213868</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3021431698630492</v>
+        <v>-0.2990547822832146</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204397448362025</v>
+        <v>0.720449173481172</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4193871479588397</v>
+        <v>-0.4150949064709143</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500460755566655</v>
+        <v>0.750029680882385</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074821773861506</v>
+        <v>1.074813641038803</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.3994850609827</v>
+        <v>10.46180520162183</v>
       </c>
       <c r="E7" t="n">
-        <v>400.4513606821114</v>
+        <v>399.8121851030856</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2797701334874383</v>
+        <v>-0.2704472445024406</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178162353247244</v>
+        <v>1.178278802076908</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.237463141405204</v>
+        <v>-0.2295273784317712</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386634638383752</v>
+        <v>0.7385819959359563</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731022084087336</v>
+        <v>1.731004327264406</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.18231175903888</v>
+        <v>10.18891953232849</v>
       </c>
       <c r="E8" t="n">
-        <v>764.6366737975469</v>
+        <v>749.0893078515751</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5398579982065965</v>
+        <v>-0.5382747053144019</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8101374360385688</v>
+        <v>0.8100987832967005</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6663782886597714</v>
+        <v>-0.6644556397478968</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.683854022782732</v>
+        <v>0.683872047201651</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101978080990522</v>
+        <v>1.101955875023501</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.212331609067717</v>
+        <v>8.255774051761833</v>
       </c>
       <c r="E9" t="n">
-        <v>161.2981291438276</v>
+        <v>423.3065573299181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3902296412280384</v>
+        <v>0.6815133171374896</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4818109226325031</v>
+        <v>0.5102907737450273</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8099227786201155</v>
+        <v>1.335539171394103</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.682964399547239</v>
+        <v>0.6443599094371423</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6545239706221955</v>
+        <v>0.6540298953647669</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.197320975841724</v>
+        <v>7.208869554434238</v>
       </c>
       <c r="E10" t="n">
-        <v>251.4218345579497</v>
+        <v>248.635436556562</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1953467108153244</v>
+        <v>-0.1914497264197037</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9664770145059126</v>
+        <v>0.9664953864596859</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.202122459079061</v>
+        <v>-0.1980865393687933</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132327646682362</v>
+        <v>0.7132155860370448</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371114313198723</v>
+        <v>1.371109003760719</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.974429735561252</v>
+        <v>6.958062704682005</v>
       </c>
       <c r="E11" t="n">
-        <v>493.3165838039113</v>
+        <v>497.2049043608712</v>
       </c>
       <c r="F11" t="n">
-        <v>1.122551290316251</v>
+        <v>1.116672607867885</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283196064198393</v>
+        <v>0.8283073973392694</v>
       </c>
       <c r="H11" t="n">
-        <v>1.355215162862242</v>
+        <v>1.348137915289562</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626471255277906</v>
+        <v>0.6626662569144396</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091769880027723</v>
+        <v>1.091786623049419</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.583883833895602</v>
+        <v>6.614126152228659</v>
       </c>
       <c r="E12" t="n">
-        <v>186.7457082224712</v>
+        <v>171.6717796997368</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2371241165334191</v>
+        <v>-0.2326636229121865</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6633443209931454</v>
+        <v>0.6632972742471056</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3574676213077422</v>
+        <v>-0.3507682481829552</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887222437749557</v>
+        <v>0.7887595162610034</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040672200905987</v>
+        <v>1.040648821527747</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.83761332499455</v>
+        <v>4.835256699191901</v>
       </c>
       <c r="E13" t="n">
-        <v>100.0465531560489</v>
+        <v>97.74203620128927</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3594353564350079</v>
+        <v>-0.3588013189285081</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8579992555333531</v>
+        <v>0.85799908683155</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4189226903368047</v>
+        <v>-0.4181838004670874</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603739067794982</v>
+        <v>0.7603731078227071</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297672093286146</v>
+        <v>1.297672037662579</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.800267283194238</v>
+        <v>4.804999282422076</v>
       </c>
       <c r="E14" t="n">
-        <v>189.4074870935123</v>
+        <v>187.8625526403117</v>
       </c>
       <c r="F14" t="n">
-        <v>1.869440457917952</v>
+        <v>1.87910146821821</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664479873405033</v>
+        <v>0.8664440830756235</v>
       </c>
       <c r="H14" t="n">
-        <v>2.157591090558197</v>
+        <v>2.16875099608038</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021657291483198</v>
+        <v>0.6021624072118095</v>
       </c>
       <c r="N14" t="n">
-        <v>1.03778976042019</v>
+        <v>1.037780608990867</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.384287921707398</v>
+        <v>4.395048438459231</v>
       </c>
       <c r="E15" t="n">
-        <v>488.229675281542</v>
+        <v>472.6258060585048</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05049612348238286</v>
+        <v>0.05710200870763771</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971446591590274</v>
+        <v>0.7971631052132356</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06334624826522117</v>
+        <v>0.07163152475849131</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169587654388395</v>
+        <v>0.7169335726729918</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136795035919097</v>
+        <v>1.136782764737501</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.330854035858971</v>
+        <v>4.340415986227851</v>
       </c>
       <c r="E16" t="n">
-        <v>321.1968587466332</v>
+        <v>316.7417577014948</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6388575807548829</v>
+        <v>0.6417065932890922</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9642093421316269</v>
+        <v>0.9642279157773099</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6625714487919477</v>
+        <v>0.6655133944880469</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5128641811026061</v>
+        <v>0.5128606736034248</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9836136628512798</v>
+        <v>0.9836270679590774</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.586013203798426</v>
+        <v>3.601126299042732</v>
       </c>
       <c r="E17" t="n">
-        <v>131.7462236264413</v>
+        <v>124.965982105129</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1477432833242935</v>
+        <v>-0.1389885987510942</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569094396582937</v>
+        <v>0.7569433068947782</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1951928138074115</v>
+        <v>-0.1836182412673276</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230660105926248</v>
+        <v>0.7230168954047146</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088610997865545</v>
+        <v>1.088587069385488</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.296527688201876</v>
+        <v>3.307005772785985</v>
       </c>
       <c r="E18" t="n">
-        <v>64.25412807340493</v>
+        <v>64.37951587763618</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4323477511422718</v>
+        <v>-0.4295390630905309</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7532166804821104</v>
+        <v>0.7532897998764471</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5740018275558363</v>
+        <v>-0.5702175486260175</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7640784500885812</v>
+        <v>0.7640070682129433</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144744931584989</v>
+        <v>1.144750482945842</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.974473703245915</v>
+        <v>2.972426645162484</v>
       </c>
       <c r="E19" t="n">
-        <v>106.1480623686193</v>
+        <v>106.195301641587</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1182915220376524</v>
+        <v>0.1201984114761419</v>
       </c>
       <c r="G19" t="n">
-        <v>0.485961888313183</v>
+        <v>0.4859682589609403</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2434172820594075</v>
+        <v>0.2473379881499684</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174767796226631</v>
+        <v>0.7174659700737899</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935230663509494</v>
+        <v>0.6935225445424213</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.665174250073577</v>
+        <v>2.673316410409456</v>
       </c>
       <c r="E20" t="n">
-        <v>114.6622606129304</v>
+        <v>114.3632724638218</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2997848736795705</v>
+        <v>-0.2956487357353516</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858123301057556</v>
+        <v>0.7858251707306728</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3814967800762621</v>
+        <v>-0.3762271135454374</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320310450760283</v>
+        <v>0.7320104661328143</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144192739770853</v>
+        <v>1.144180648496114</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.80400450902</v>
+        <v>581.4925067163271</v>
       </c>
       <c r="E2" t="n">
-        <v>10472.59067900769</v>
+        <v>10409.82304830246</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6890276572148026</v>
+        <v>0.6874568432305743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027460045592718</v>
+        <v>0.5027477482247078</v>
       </c>
       <c r="H2" t="n">
-        <v>1.370528360178284</v>
+        <v>1.367399149291284</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.9544674953138</v>
+        <v>227.8938119970617</v>
       </c>
       <c r="E3" t="n">
-        <v>4427.3103073516</v>
+        <v>4409.4634074403</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2938334560273506</v>
+        <v>0.2941355680065998</v>
       </c>
       <c r="G3" t="n">
-        <v>0.603569569026053</v>
+        <v>0.6035697578976628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4868261607381788</v>
+        <v>0.487326550341297</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908912772017996</v>
+        <v>0.8908856871739514</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069555718699631</v>
+        <v>1.069545632816518</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.81729871365842</v>
+        <v>40.70725032638446</v>
       </c>
       <c r="E4" t="n">
-        <v>1818.68284052118</v>
+        <v>1819.742235761682</v>
       </c>
       <c r="F4" t="n">
-        <v>1.036899854667185</v>
+        <v>1.030736176017188</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117643478632145</v>
+        <v>1.117637633839922</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9277554734504598</v>
+        <v>0.9222454083581972</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715895220945894</v>
+        <v>0.4715919053425383</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048380194333555</v>
+        <v>1.048376373810264</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.64368208969952</v>
+        <v>37.63183276543077</v>
       </c>
       <c r="E5" t="n">
-        <v>389.6536223965315</v>
+        <v>385.3524954941543</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3269286986811221</v>
+        <v>-0.3273091153955133</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672563995140377</v>
+        <v>0.5672523188005172</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.576333204810379</v>
+        <v>-0.5770079813646677</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367131090129139</v>
+        <v>0.7367044032216745</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312452449220582</v>
+        <v>0.8312265593903025</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.97927686612439</v>
+        <v>10.98178079103924</v>
       </c>
       <c r="E6" t="n">
-        <v>199.3238569213868</v>
+        <v>198.7132406966878</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2990547822832146</v>
+        <v>-0.2971999396715996</v>
       </c>
       <c r="G6" t="n">
-        <v>0.720449173481172</v>
+        <v>0.7204641218663046</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4150949064709143</v>
+        <v>-0.4125117832401244</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.750029680882385</v>
+        <v>0.7499941861008944</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074813641038803</v>
+        <v>1.074781348304524</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.46180520162183</v>
+        <v>10.42001219636206</v>
       </c>
       <c r="E7" t="n">
-        <v>399.8121851030856</v>
+        <v>399.4304973861161</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2704472445024406</v>
+        <v>-0.2762779391893622</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178278802076908</v>
+        <v>1.178194008482917</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2295273784317712</v>
+        <v>-0.2344927382079519</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7385819959359563</v>
+        <v>0.7386262017341533</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731004327264406</v>
+        <v>1.730977350897472</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.18891953232849</v>
+        <v>10.17476510068694</v>
       </c>
       <c r="E8" t="n">
-        <v>749.0893078515751</v>
+        <v>743.4225889601748</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5382747053144019</v>
+        <v>-0.538450701049046</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8100987832967005</v>
+        <v>0.8101025757723508</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6644556397478968</v>
+        <v>-0.6646697802876232</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.683872047201651</v>
+        <v>0.6838859476490982</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101955875023501</v>
+        <v>1.101979610413742</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.255774051761833</v>
+        <v>7.964819582733588</v>
       </c>
       <c r="E9" t="n">
-        <v>423.3065573299181</v>
+        <v>557.3170681241245</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6815133171374896</v>
+        <v>0.5903414038280745</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5102907737450273</v>
+        <v>0.4953971724328896</v>
       </c>
       <c r="H9" t="n">
-        <v>1.335539171394103</v>
+        <v>1.191652751930163</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6443599094371423</v>
+        <v>0.6635186007017543</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6540298953647669</v>
+        <v>0.6538174259457028</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.208869554434238</v>
+        <v>7.214263802832325</v>
       </c>
       <c r="E10" t="n">
-        <v>248.635436556562</v>
+        <v>246.6105982318284</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1914497264197037</v>
+        <v>-0.1898605734436913</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9664953864596859</v>
+        <v>0.9665078537504983</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1980865393687933</v>
+        <v>-0.1964397627054393</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132155860370448</v>
+        <v>0.7131884013745537</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371109003760719</v>
+        <v>1.371069673740595</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.958062704682005</v>
+        <v>6.962607555944017</v>
       </c>
       <c r="E11" t="n">
-        <v>497.2049043608712</v>
+        <v>501.0551768118635</v>
       </c>
       <c r="F11" t="n">
-        <v>1.116672607867885</v>
+        <v>1.123479915641846</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283073973392694</v>
+        <v>0.8283221478110425</v>
       </c>
       <c r="H11" t="n">
-        <v>1.348137915289562</v>
+        <v>1.356332096891045</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626662569144396</v>
+        <v>0.6626363989049294</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091786623049419</v>
+        <v>1.091753085114526</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.614126152228659</v>
+        <v>6.594625293970701</v>
       </c>
       <c r="E12" t="n">
-        <v>171.6717796997368</v>
+        <v>161.1688453219414</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2326636229121865</v>
+        <v>-0.2344098903345075</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632972742471056</v>
+        <v>0.663311379301774</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3507682481829552</v>
+        <v>-0.3533934403194711</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887595162610034</v>
+        <v>0.7887579283903881</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040648821527747</v>
+        <v>1.040665246663607</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.835256699191901</v>
+        <v>4.838541119541878</v>
       </c>
       <c r="E13" t="n">
-        <v>97.74203620128927</v>
+        <v>96.1955797329634</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3588013189285081</v>
+        <v>-0.358167107887967</v>
       </c>
       <c r="G13" t="n">
-        <v>0.85799908683155</v>
+        <v>0.8579997313295545</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4181838004670874</v>
+        <v>-0.4174443124043314</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603731078227071</v>
+        <v>0.7603665341193152</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297672037662579</v>
+        <v>1.297657292926876</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.804999282422076</v>
+        <v>4.798950178584874</v>
       </c>
       <c r="E14" t="n">
-        <v>187.8625526403117</v>
+        <v>186.5666815310887</v>
       </c>
       <c r="F14" t="n">
-        <v>1.87910146821821</v>
+        <v>1.87265979620354</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664440830756235</v>
+        <v>0.8664456464944069</v>
       </c>
       <c r="H14" t="n">
-        <v>2.16875099608038</v>
+        <v>2.161312488302321</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021624072118095</v>
+        <v>0.602165377179754</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037780608990867</v>
+        <v>1.037784000762669</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.395048438459231</v>
+        <v>4.397357369942463</v>
       </c>
       <c r="E15" t="n">
-        <v>472.6258060585048</v>
+        <v>451.0993128515159</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05710200870763771</v>
+        <v>0.05728070509977812</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971631052132356</v>
+        <v>0.7971640951129779</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07163152475849131</v>
+        <v>0.07185560093704424</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169335726729918</v>
+        <v>0.7169190107212104</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136782764737501</v>
+        <v>1.136757144052741</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.340415986227851</v>
+        <v>4.321934727629923</v>
       </c>
       <c r="E16" t="n">
-        <v>316.7417577014948</v>
+        <v>311.4128612893587</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6417065932890922</v>
+        <v>0.6374335881082893</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9642279157773099</v>
+        <v>0.9642009136293571</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6655133944880469</v>
+        <v>0.6611003776266089</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5128606736034248</v>
+        <v>0.5128594251203631</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9836270679590774</v>
+        <v>0.9835937167508898</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.601126299042732</v>
+        <v>3.584928798095298</v>
       </c>
       <c r="E17" t="n">
-        <v>124.965982105129</v>
+        <v>121.5270712485409</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1389885987510942</v>
+        <v>-0.1483133802930557</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569433068947782</v>
+        <v>0.7569106700828873</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1836182412673276</v>
+        <v>-0.1959456857396585</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230168954047146</v>
+        <v>0.7230670350416536</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088587069385488</v>
+        <v>1.088611845484796</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.307005772785985</v>
+        <v>3.313692292557495</v>
       </c>
       <c r="E18" t="n">
-        <v>64.37951587763618</v>
+        <v>64.37420294750092</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4295390630905309</v>
+        <v>-0.4281332816132312</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7532897998764471</v>
+        <v>0.7533351886688985</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5702175486260175</v>
+        <v>-0.5683171157446115</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7640070682129433</v>
+        <v>0.763918473770403</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144750482945842</v>
+        <v>1.144682735223837</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.972426645162484</v>
+        <v>2.983785379040226</v>
       </c>
       <c r="E19" t="n">
-        <v>106.195301641587</v>
+        <v>105.320691032909</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1201984114761419</v>
+        <v>0.1268795968828957</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859682589609403</v>
+        <v>0.4860242744034072</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2473379881499684</v>
+        <v>0.2610560903334302</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174659700737899</v>
+        <v>0.7173404066327367</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935225445424213</v>
+        <v>0.6934786915805162</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.673316410409456</v>
+        <v>2.677267310625429</v>
       </c>
       <c r="E20" t="n">
-        <v>114.3632724638218</v>
+        <v>114.6461041765945</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2956487357353516</v>
+        <v>-0.2946136487014697</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858251707306728</v>
+        <v>0.7858333167609798</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3762271135454374</v>
+        <v>-0.3749060295837263</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320104661328143</v>
+        <v>0.7319865940482357</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144180648496114</v>
+        <v>1.144151227045175</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.4925067163271</v>
+        <v>580.7764654540039</v>
       </c>
       <c r="E2" t="n">
-        <v>10409.82304830246</v>
+        <v>10329.60175783875</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6874568432305743</v>
+        <v>0.6830445075356657</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027477482247078</v>
+        <v>0.5027592365191391</v>
       </c>
       <c r="H2" t="n">
-        <v>1.367399149291284</v>
+        <v>1.358591663605694</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.8938119970617</v>
+        <v>227.8459380474187</v>
       </c>
       <c r="E3" t="n">
-        <v>4409.4634074403</v>
+        <v>4385.867685075644</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2941355680065998</v>
+        <v>0.2922099386054362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035697578976628</v>
+        <v>0.603569661437435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.487326550341297</v>
+        <v>0.4841362269758918</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908856871739514</v>
+        <v>0.8908759792133566</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069545632816518</v>
+        <v>1.069509367703241</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.70725032638446</v>
+        <v>40.56691384846298</v>
       </c>
       <c r="E4" t="n">
-        <v>1819.742235761682</v>
+        <v>1820.277800747308</v>
       </c>
       <c r="F4" t="n">
-        <v>1.030736176017188</v>
+        <v>1.018786159793824</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117637633839922</v>
+        <v>1.117643208197904</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9222454083581972</v>
+        <v>0.9115486519499567</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715919053425383</v>
+        <v>0.4716069161205746</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048376373810264</v>
+        <v>1.048391015927667</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.63183276543077</v>
+        <v>37.60237184261804</v>
       </c>
       <c r="E5" t="n">
-        <v>385.3524954941543</v>
+        <v>379.830934602294</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3273091153955133</v>
+        <v>-0.3284500083574802</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672523188005172</v>
+        <v>0.5672425051673551</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5770079813646677</v>
+        <v>-0.5790292606168091</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367044032216745</v>
+        <v>0.7366834712700069</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312265593903025</v>
+        <v>0.8311695686622638</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.98178079103924</v>
+        <v>10.93791868249503</v>
       </c>
       <c r="E6" t="n">
-        <v>198.7132406966878</v>
+        <v>197.2946394522669</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2971999396715996</v>
+        <v>-0.3039943897277814</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204641218663046</v>
+        <v>0.7204433791148842</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4125117832401244</v>
+        <v>-0.4219545887162708</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499941861008944</v>
+        <v>0.7500468097403562</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074781348304524</v>
+        <v>1.074801254463099</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.42001219636206</v>
+        <v>10.36411814250134</v>
       </c>
       <c r="E7" t="n">
-        <v>399.4304973861161</v>
+        <v>397.7868081242813</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2762779391893622</v>
+        <v>-0.2805455415725353</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178194008482917</v>
+        <v>1.178157276613743</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2344927382079519</v>
+        <v>-0.2381223179123239</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386262017341533</v>
+        <v>0.7386225139369627</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730977350897472</v>
+        <v>1.730875190857762</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.17476510068694</v>
+        <v>10.14568933624357</v>
       </c>
       <c r="E8" t="n">
-        <v>743.4225889601748</v>
+        <v>730.7860328889258</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.538450701049046</v>
+        <v>-0.5438973432787313</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8101025757723508</v>
+        <v>0.8102824155002982</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6646697802876232</v>
+        <v>-0.6712441648420928</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838859476490982</v>
+        <v>0.6838619150720807</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101979610413742</v>
+        <v>1.102160326779339</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.964819582733588</v>
+        <v>7.996085672878002</v>
       </c>
       <c r="E9" t="n">
-        <v>557.3170681241245</v>
+        <v>587.7244294098538</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5903414038280745</v>
+        <v>0.599544458479365</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4953971724328896</v>
+        <v>0.4966747803086815</v>
       </c>
       <c r="H9" t="n">
-        <v>1.191652751930163</v>
+        <v>1.207116773891258</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6635186007017543</v>
+        <v>0.6606962045161282</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6538174259457028</v>
+        <v>0.6527003750359456</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.214263802832325</v>
+        <v>7.19416831167005</v>
       </c>
       <c r="E10" t="n">
-        <v>246.6105982318284</v>
+        <v>245.3633061594559</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1898605734436913</v>
+        <v>-0.1957793873428698</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665078537504983</v>
+        <v>0.9664760459808711</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1964397627054393</v>
+        <v>-0.2025703463184899</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131884013745537</v>
+        <v>0.7132065732649491</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371069673740595</v>
+        <v>1.371028155880402</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.962607555944017</v>
+        <v>6.930608478197073</v>
       </c>
       <c r="E11" t="n">
-        <v>501.0551768118635</v>
+        <v>513.3224813143022</v>
       </c>
       <c r="F11" t="n">
-        <v>1.123479915641846</v>
+        <v>1.105237607888185</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283221478110425</v>
+        <v>0.8283028870546296</v>
       </c>
       <c r="H11" t="n">
-        <v>1.356332096891045</v>
+        <v>1.334339919806764</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626363989049294</v>
+        <v>0.6626710470808842</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091753085114526</v>
+        <v>1.091759835711572</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.594625293970701</v>
+        <v>6.552160730000049</v>
       </c>
       <c r="E12" t="n">
-        <v>161.1688453219414</v>
+        <v>154.5097914009968</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2344098903345075</v>
+        <v>-0.2421577366017607</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663311379301774</v>
+        <v>0.6634410210332592</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3533934403194711</v>
+        <v>-0.3650026587512155</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887579283903881</v>
+        <v>0.7887194154699888</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040665246663607</v>
+        <v>1.040794034796902</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.838541119541878</v>
+        <v>4.819552434527793</v>
       </c>
       <c r="E13" t="n">
-        <v>96.1955797329634</v>
+        <v>95.7235569340332</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.358167107887967</v>
+        <v>-0.3632359329585338</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8579997313295545</v>
+        <v>0.8580173447514219</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4174443124043314</v>
+        <v>-0.4233433451904958</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603665341193152</v>
+        <v>0.7603856169228738</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297657292926876</v>
+        <v>1.297686846165977</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.798950178584874</v>
+        <v>4.778147340037714</v>
       </c>
       <c r="E14" t="n">
-        <v>186.5666815310887</v>
+        <v>190.0809358638215</v>
       </c>
       <c r="F14" t="n">
-        <v>1.87265979620354</v>
+        <v>1.850145427862814</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664456464944069</v>
+        <v>0.8664838595645662</v>
       </c>
       <c r="H14" t="n">
-        <v>2.161312488302321</v>
+        <v>2.135233573528498</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.602165377179754</v>
+        <v>0.6021901977186856</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037784000762669</v>
+        <v>1.03784883262184</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.397357369942463</v>
+        <v>4.374346458403877</v>
       </c>
       <c r="E15" t="n">
-        <v>451.0993128515159</v>
+        <v>428.2259600827463</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05728070509977812</v>
+        <v>0.04710836925881168</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971640951129779</v>
+        <v>0.7971489452535117</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07185560093704424</v>
+        <v>0.05909606923437644</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169190107212104</v>
+        <v>0.7169614748530727</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136757144052741</v>
+        <v>1.136776894291374</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.321934727629923</v>
+        <v>4.312668931913913</v>
       </c>
       <c r="E16" t="n">
-        <v>311.4128612893587</v>
+        <v>309.6950910164949</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6374335881082893</v>
+        <v>0.6288968313012961</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9642009136293571</v>
+        <v>0.9641623599849659</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6611003776266089</v>
+        <v>0.6522727472073298</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5128594251203631</v>
+        <v>0.5128542081475117</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9835937167508898</v>
+        <v>0.9835219081786118</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.584928798095298</v>
+        <v>3.571367178824136</v>
       </c>
       <c r="E17" t="n">
-        <v>121.5270712485409</v>
+        <v>116.821913937005</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1483133802930557</v>
+        <v>-0.1524908634215165</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569106700828873</v>
+        <v>0.7569325606361411</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1959456857396585</v>
+        <v>-0.2014589824136515</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230670350416536</v>
+        <v>0.7230812754425754</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088611845484796</v>
+        <v>1.088639892840556</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.313692292557495</v>
+        <v>3.295771166210953</v>
       </c>
       <c r="E18" t="n">
-        <v>64.37420294750092</v>
+        <v>64.34016174281004</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4281332816132312</v>
+        <v>-0.4333381363670098</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7533351886688985</v>
+        <v>0.7531964959526846</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5683171157446115</v>
+        <v>-0.5753321194343844</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.763918473770403</v>
+        <v>0.7640174037057609</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144682735223837</v>
+        <v>1.144594051224637</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.983785379040226</v>
+        <v>2.977814620038206</v>
       </c>
       <c r="E19" t="n">
-        <v>105.320691032909</v>
+        <v>105.2902052111169</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1268795968828957</v>
+        <v>0.1211521932308668</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4860242744034072</v>
+        <v>0.4859730500284088</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2610560903334302</v>
+        <v>0.2492981724475967</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173404066327367</v>
+        <v>0.7173938661072554</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934786915805162</v>
+        <v>0.6934414325186508</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.677267310625429</v>
+        <v>2.668839606968574</v>
       </c>
       <c r="E20" t="n">
-        <v>114.6461041765945</v>
+        <v>113.9975725633563</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2946136487014697</v>
+        <v>-0.298234611966681</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858333167609798</v>
+        <v>0.7858134433612658</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3749060295837263</v>
+        <v>-0.3795234282210824</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7319865940482357</v>
+        <v>0.7319971716612879</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144151227045175</v>
+        <v>1.144112681004851</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.7764654540039</v>
+        <v>580.6669629931561</v>
       </c>
       <c r="E2" t="n">
-        <v>10329.60175783875</v>
+        <v>10208.95636578535</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6830445075356657</v>
+        <v>0.6844388030799313</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027592365191391</v>
+        <v>0.5027545549568524</v>
       </c>
       <c r="H2" t="n">
-        <v>1.358591663605694</v>
+        <v>1.361377627177682</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.8459380474187</v>
+        <v>227.6485246803864</v>
       </c>
       <c r="E3" t="n">
-        <v>4385.867685075644</v>
+        <v>4362.255853871582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2922099386054362</v>
+        <v>0.2911813736962829</v>
       </c>
       <c r="G3" t="n">
-        <v>0.603569661437435</v>
+        <v>0.6035706868419958</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4841362269758918</v>
+        <v>0.4824312711735604</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908759792133566</v>
+        <v>0.8908881135228065</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069509367703241</v>
+        <v>1.069535711366112</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.56691384846298</v>
+        <v>40.51520541403433</v>
       </c>
       <c r="E4" t="n">
-        <v>1820.277800747308</v>
+        <v>1788.901032130102</v>
       </c>
       <c r="F4" t="n">
-        <v>1.018786159793824</v>
+        <v>1.01589212714379</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117643208197904</v>
+        <v>1.117647923052959</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9115486519499567</v>
+        <v>0.9089554109032714</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716069161205746</v>
+        <v>0.4716111703359004</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048391015927667</v>
+        <v>1.048414658440501</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.60237184261804</v>
+        <v>37.54137261638778</v>
       </c>
       <c r="E5" t="n">
-        <v>379.830934602294</v>
+        <v>373.520377597938</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3284500083574802</v>
+        <v>-0.329590365231581</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672425051673551</v>
+        <v>0.5672363344332476</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5790292606168091</v>
+        <v>-0.5810459331045678</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366834712700069</v>
+        <v>0.7367212922515047</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8311695686622638</v>
+        <v>0.8312109382112579</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.93791868249503</v>
+        <v>10.92792193919475</v>
       </c>
       <c r="E6" t="n">
-        <v>197.2946394522669</v>
+        <v>196.2609003455335</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3039943897277814</v>
+        <v>-0.3030689498799306</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204433791148842</v>
+        <v>0.7204406909002697</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4219545887162708</v>
+        <v>-0.4206716162869877</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500468097403562</v>
+        <v>0.7500428381194735</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074801254463099</v>
+        <v>1.074801561063863</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.36411814250134</v>
+        <v>10.36621087309094</v>
       </c>
       <c r="E7" t="n">
-        <v>397.7868081242813</v>
+        <v>389.419820570424</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2805455415725353</v>
+        <v>-0.2809331589283122</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178157276613743</v>
+        <v>1.178155005286223</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2381223179123239</v>
+        <v>-0.2384517806806429</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386225139369627</v>
+        <v>0.738640312938154</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730875190857762</v>
+        <v>1.730929681719052</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.14568933624357</v>
+        <v>10.12869987885796</v>
       </c>
       <c r="E8" t="n">
-        <v>730.7860328889258</v>
+        <v>716.0212641516775</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5438973432787313</v>
+        <v>-0.5420545171115</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8102824155002982</v>
+        <v>0.8102079916363778</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6712441648420928</v>
+        <v>-0.6690313138194453</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838619150720807</v>
+        <v>0.6838725205064825</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102160326779339</v>
+        <v>1.102086447376726</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.996085672878002</v>
+        <v>7.800662548497685</v>
       </c>
       <c r="E9" t="n">
-        <v>587.7244294098538</v>
+        <v>611.9588722084654</v>
       </c>
       <c r="F9" t="n">
-        <v>0.599544458479365</v>
+        <v>0.548740200502809</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4966747803086815</v>
+        <v>0.4902951157057312</v>
       </c>
       <c r="H9" t="n">
-        <v>1.207116773891258</v>
+        <v>1.119203889504288</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6606962045161282</v>
+        <v>0.6700059220214548</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6527003750359456</v>
+        <v>0.6534016008850025</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.19416831167005</v>
+        <v>7.18398734526126</v>
       </c>
       <c r="E10" t="n">
-        <v>245.3633061594559</v>
+        <v>243.2802788132681</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1957793873428698</v>
+        <v>-0.1975094492545169</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9664760459808711</v>
+        <v>0.9664743175254543</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2025703463184899</v>
+        <v>-0.2043607840094675</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132065732649491</v>
+        <v>0.7132284378367495</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371028155880402</v>
+        <v>1.371080502208831</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.930608478197073</v>
+        <v>6.91749366331979</v>
       </c>
       <c r="E11" t="n">
-        <v>513.3224813143022</v>
+        <v>517.5270870732706</v>
       </c>
       <c r="F11" t="n">
-        <v>1.105237607888185</v>
+        <v>1.102150011483026</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283028870546296</v>
+        <v>0.8283060381388934</v>
       </c>
       <c r="H11" t="n">
-        <v>1.334339919806764</v>
+        <v>1.330607240241092</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626710470808842</v>
+        <v>0.6626812087511801</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091759835711572</v>
+        <v>1.091790897084743</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.552160730000049</v>
+        <v>6.604976228859293</v>
       </c>
       <c r="E12" t="n">
-        <v>154.5097914009968</v>
+        <v>148.4790975354528</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2421577366017607</v>
+        <v>-0.2487262248322534</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6634410210332592</v>
+        <v>0.6636371223530161</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3650026587512155</v>
+        <v>-0.3747925130383915</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887194154699888</v>
+        <v>0.7885291419763412</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040794034796902</v>
+        <v>1.040860208054371</v>
       </c>
     </row>
     <row r="13">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.819552434527793</v>
+        <v>4.813462859544174</v>
       </c>
       <c r="E13" t="n">
-        <v>95.7235569340332</v>
+        <v>95.04023667653988</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3632359329585338</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603856169228738</v>
+        <v>0.7603836232406022</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297686846165977</v>
+        <v>1.29769552751513</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.778147340037714</v>
+        <v>4.763910634153344</v>
       </c>
       <c r="E14" t="n">
-        <v>190.0809358638215</v>
+        <v>190.3385175833677</v>
       </c>
       <c r="F14" t="n">
-        <v>1.850145427862814</v>
+        <v>1.842116473749208</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664838595645662</v>
+        <v>0.8665098490507643</v>
       </c>
       <c r="H14" t="n">
-        <v>2.135233573528498</v>
+        <v>2.125903676417748</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021901977186856</v>
+        <v>0.6021808676333251</v>
       </c>
       <c r="N14" t="n">
-        <v>1.03784883262184</v>
+        <v>1.037873545987053</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.374346458403877</v>
+        <v>4.385418536931589</v>
       </c>
       <c r="E15" t="n">
-        <v>428.2259600827463</v>
+        <v>394.2340907492453</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04710836925881168</v>
+        <v>0.05495830413728697</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971489452535117</v>
+        <v>0.7971532435269693</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05909606923437644</v>
+        <v>0.06894321083625826</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169614748530727</v>
+        <v>0.7169121252251754</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136776894291374</v>
+        <v>1.136715362024135</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.312668931913913</v>
+        <v>4.348687805652695</v>
       </c>
       <c r="E16" t="n">
-        <v>309.6950910164949</v>
+        <v>307.0923871134568</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6288968313012961</v>
+        <v>0.6431316129111795</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9641623599849659</v>
+        <v>0.9642380608876562</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6522727472073298</v>
+        <v>0.6669842635325209</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5128542081475117</v>
+        <v>0.5127812581476581</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9835219081786118</v>
+        <v>0.9834683766480538</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.571367178824136</v>
+        <v>3.584313318881485</v>
       </c>
       <c r="E17" t="n">
-        <v>116.821913937005</v>
+        <v>115.0104798630322</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1524908634215165</v>
+        <v>-0.1479333273759477</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569325606361411</v>
+        <v>0.7569098030081278</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2014589824136515</v>
+        <v>-0.1954437989678925</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230812754425754</v>
+        <v>0.7230627617380867</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088639892840556</v>
+        <v>1.088589426298998</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.295771166210953</v>
+        <v>3.296313059980926</v>
       </c>
       <c r="E18" t="n">
-        <v>64.34016174281004</v>
+        <v>63.54126701538159</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4333381363670098</v>
+        <v>-0.4330905849284471</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531964959526846</v>
+        <v>0.7532012670511057</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5753321194343844</v>
+        <v>-0.5749998093126698</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7640174037057609</v>
+        <v>0.7640342114432901</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144594051224637</v>
+        <v>1.144637140440959</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.977814620038206</v>
+        <v>2.970119667688362</v>
       </c>
       <c r="E19" t="n">
-        <v>105.2902052111169</v>
+        <v>104.3657072840763</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1211521932308668</v>
+        <v>0.1182915220376524</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859730500284088</v>
+        <v>0.485961888313183</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2492981724475967</v>
+        <v>0.2434172820594075</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173938661072554</v>
+        <v>0.717454028881708</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934414325186508</v>
+        <v>0.6934901160332168</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.668839606968574</v>
+        <v>2.668531187324311</v>
       </c>
       <c r="E20" t="n">
-        <v>113.9975725633563</v>
+        <v>113.4535132242849</v>
       </c>
       <c r="F20" t="n">
         <v>-0.298234611966681</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7319971716612879</v>
+        <v>0.7320064679606821</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144112681004851</v>
+        <v>1.144137865046828</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.6669629931561</v>
+        <v>581.0994652923816</v>
       </c>
       <c r="E2" t="n">
-        <v>10208.95636578535</v>
+        <v>10078.77317538274</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6844388030799313</v>
+        <v>0.6904646742796463</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027545549568524</v>
+        <v>0.5027454871473026</v>
       </c>
       <c r="H2" t="n">
-        <v>1.361377627177682</v>
+        <v>1.373388109752127</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.6485246803864</v>
+        <v>227.5637683920133</v>
       </c>
       <c r="E3" t="n">
-        <v>4362.255853871582</v>
+        <v>4329.276235483956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2911813736962829</v>
+        <v>0.2929083595216235</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035706868419958</v>
+        <v>0.6035693927606099</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4824312711735604</v>
+        <v>0.4852935934705324</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908881135228065</v>
+        <v>0.8908935920838954</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069535711366112</v>
+        <v>1.069559286229547</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.51520541403433</v>
+        <v>40.63383653896075</v>
       </c>
       <c r="E4" t="n">
-        <v>1788.901032130102</v>
+        <v>1741.535939563432</v>
       </c>
       <c r="F4" t="n">
-        <v>1.01589212714379</v>
+        <v>1.031098602237813</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117647923052959</v>
+        <v>1.117637813577692</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9089554109032714</v>
+        <v>0.9225695388178958</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716111703359004</v>
+        <v>0.4715973030137897</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048414658440501</v>
+        <v>1.048393256835018</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.54137261638778</v>
+        <v>37.46641221437817</v>
       </c>
       <c r="E5" t="n">
-        <v>373.520377597938</v>
+        <v>368.8835266087273</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.329590365231581</v>
+        <v>-0.3311100064456307</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672363344332476</v>
+        <v>0.567233773715012</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5810459331045678</v>
+        <v>-0.5837275948452005</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367212922515047</v>
+        <v>0.7367560791075611</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312109382112579</v>
+        <v>0.8312614269916075</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.92792193919475</v>
+        <v>10.93658534653074</v>
       </c>
       <c r="E6" t="n">
-        <v>196.2609003455335</v>
+        <v>194.6224536684452</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3030689498799306</v>
+        <v>-0.3012170498787368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204406909002697</v>
+        <v>0.720440540929546</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4206716162869877</v>
+        <v>-0.4181011933199824</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500428381194735</v>
+        <v>0.7500467749124442</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074801561063863</v>
+        <v>1.074826364541902</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.36621087309094</v>
+        <v>10.36788708125481</v>
       </c>
       <c r="E7" t="n">
-        <v>389.419820570424</v>
+        <v>383.1608598263206</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2809331589283122</v>
+        <v>-0.2782186242120286</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178155005286223</v>
+        <v>1.178174642394195</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2384517806806429</v>
+        <v>-0.2361437890452764</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.738640312938154</v>
+        <v>0.7386699171364774</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730929681719052</v>
+        <v>1.731059129755309</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.12869987885796</v>
+        <v>10.14657167545495</v>
       </c>
       <c r="E8" t="n">
-        <v>716.0212641516775</v>
+        <v>707.6697207851769</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5420545171115</v>
+        <v>-0.5383627055025465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8102079916363778</v>
+        <v>0.8101006638378119</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6690313138194453</v>
+        <v>-0.6645627260099748</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838725205064825</v>
+        <v>0.6838544334669912</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102086447376726</v>
+        <v>1.101931185227572</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.800662548497685</v>
+        <v>7.814256450270187</v>
       </c>
       <c r="E9" t="n">
-        <v>611.9588722084654</v>
+        <v>631.3550217220502</v>
       </c>
       <c r="F9" t="n">
-        <v>0.548740200502809</v>
+        <v>0.5583703988139466</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4902951157057312</v>
+        <v>0.4913763413980993</v>
       </c>
       <c r="H9" t="n">
-        <v>1.119203889504288</v>
+        <v>1.136339607285998</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6700059220214548</v>
+        <v>0.6696539452895266</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6534016008850025</v>
+        <v>0.6545103119797065</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.18398734526126</v>
+        <v>7.188630183362799</v>
       </c>
       <c r="E10" t="n">
-        <v>243.2802788132681</v>
+        <v>240.4049717233619</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1975094492545169</v>
+        <v>-0.1937596794490128</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9664743175254543</v>
+        <v>0.9664824014670346</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2043607840094675</v>
+        <v>-0.2004792628969786</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132284378367495</v>
+        <v>0.7132353598973293</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371080502208831</v>
+        <v>1.371130007265096</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.91749366331979</v>
+        <v>6.925401656692129</v>
       </c>
       <c r="E11" t="n">
-        <v>517.5270870732706</v>
+        <v>516.1643003743659</v>
       </c>
       <c r="F11" t="n">
-        <v>1.102150011483026</v>
+        <v>1.110489398255748</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283060381388934</v>
+        <v>0.8283017980112122</v>
       </c>
       <c r="H11" t="n">
-        <v>1.330607240241092</v>
+        <v>1.340682105148244</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626812087511801</v>
+        <v>0.6626768017353118</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091790897084743</v>
+        <v>1.091797739433221</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.604976228859293</v>
+        <v>6.582393289296177</v>
       </c>
       <c r="E12" t="n">
-        <v>148.4790975354528</v>
+        <v>145.921832195401</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2487262248322534</v>
+        <v>-0.2433180308165068</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6636371223530161</v>
+        <v>0.663469892819092</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3747925130383915</v>
+        <v>-0.366735602398845</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7885291419763412</v>
+        <v>0.7885467155814893</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040860208054371</v>
+        <v>1.040639882892492</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.813462859544174</v>
+        <v>4.811499377814563</v>
       </c>
       <c r="E13" t="n">
-        <v>95.04023667653988</v>
+        <v>94.32219246786576</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3632359329585338</v>
+        <v>-0.3619697695855547</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8580173447514219</v>
+        <v>0.8580080622943669</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4233433451904958</v>
+        <v>-0.4218722241579235</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603836232406022</v>
+        <v>0.7603663624875797</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29769552751513</v>
+        <v>1.297675436160869</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.763910634153344</v>
+        <v>4.765328035357993</v>
       </c>
       <c r="E14" t="n">
-        <v>190.3385175833677</v>
+        <v>189.1565302778925</v>
       </c>
       <c r="F14" t="n">
-        <v>1.842116473749208</v>
+        <v>1.848539135706206</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8665098490507643</v>
+        <v>0.8664885378365259</v>
       </c>
       <c r="H14" t="n">
-        <v>2.125903676417748</v>
+        <v>2.13336825011176</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021808676333251</v>
+        <v>0.6021325618543383</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037873545987053</v>
+        <v>1.037783483777068</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.385418536931589</v>
+        <v>4.3950656945645</v>
       </c>
       <c r="E15" t="n">
-        <v>394.2340907492453</v>
+        <v>383.9462738206967</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05495830413728697</v>
+        <v>0.05656596968410699</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971532435269693</v>
+        <v>0.7971602906748128</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06894321083625826</v>
+        <v>0.07095934198656925</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169121252251754</v>
+        <v>0.7169465798424752</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136715362024135</v>
+        <v>1.136800545398206</v>
       </c>
     </row>
     <row r="16">
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.348687805652695</v>
+        <v>4.331513681943129</v>
       </c>
       <c r="E16" t="n">
-        <v>307.0923871134568</v>
+        <v>299.8160169512761</v>
       </c>
       <c r="F16" t="n">
         <v>0.6431316129111795</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5127812581476581</v>
+        <v>0.5128747925457238</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9834683766480538</v>
+        <v>0.9836655088612479</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.584313318881485</v>
+        <v>3.584707421466888</v>
       </c>
       <c r="E17" t="n">
-        <v>115.0104798630322</v>
+        <v>113.3574917545029</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1479333273759477</v>
+        <v>-0.1433690357958857</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569098030081278</v>
+        <v>0.756913997172691</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1954437989678925</v>
+        <v>-0.1894125836375249</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230627617380867</v>
+        <v>0.7230594389151601</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088589426298998</v>
+        <v>1.088610090183389</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.296313059980926</v>
+        <v>3.298963201152283</v>
       </c>
       <c r="E18" t="n">
-        <v>63.54126701538159</v>
+        <v>63.21423653729132</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4330905849284471</v>
+        <v>-0.4302002759092179</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7532012670511057</v>
+        <v>0.7532704769783112</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5749998093126698</v>
+        <v>-0.5711099652211706</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7640342114432901</v>
+        <v>0.7640562963945335</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144637140440959</v>
+        <v>1.144796055931101</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.970119667688362</v>
+        <v>2.977285698940998</v>
       </c>
       <c r="E19" t="n">
-        <v>104.3657072840763</v>
+        <v>103.759938213437</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1182915220376524</v>
+        <v>0.1230604303844198</v>
       </c>
       <c r="G19" t="n">
-        <v>0.485961888313183</v>
+        <v>0.4859858434922239</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2434172820594075</v>
+        <v>0.2532181380019743</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717454028881708</v>
+        <v>0.7174491733802435</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934901160332168</v>
+        <v>0.6935321163526178</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.668531187324311</v>
+        <v>2.672222982871452</v>
       </c>
       <c r="E20" t="n">
-        <v>113.4535132242849</v>
+        <v>113.5164332099147</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.298234611966681</v>
+        <v>-0.295131244793984</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858134433612658</v>
+        <v>0.7858289969604957</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3795234282210824</v>
+        <v>-0.3755667529901808</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320064679606821</v>
+        <v>0.732015875817656</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144137865046828</v>
+        <v>1.144195852889683</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.0994652923816</v>
+        <v>582.3672876729883</v>
       </c>
       <c r="E2" t="n">
-        <v>10078.77317538274</v>
+        <v>10034.70213233406</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6904646742796463</v>
+        <v>0.6899848508479662</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027454871473026</v>
+        <v>0.5027455454405244</v>
       </c>
       <c r="H2" t="n">
-        <v>1.373388109752127</v>
+        <v>1.372433544375566</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.5637683920133</v>
+        <v>227.8598883875713</v>
       </c>
       <c r="E3" t="n">
-        <v>4329.276235483956</v>
+        <v>4306.605290484932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2929083595216235</v>
+        <v>0.2922099386054362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035693927606099</v>
+        <v>0.603569661437435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4852935934705324</v>
+        <v>0.4841362269758918</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908935920838954</v>
+        <v>0.8908935568848088</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069559286229547</v>
+        <v>1.069559596066811</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.63383653896075</v>
+        <v>40.7319579764271</v>
       </c>
       <c r="E4" t="n">
-        <v>1741.535939563432</v>
+        <v>1687.927249451345</v>
       </c>
       <c r="F4" t="n">
-        <v>1.031098602237813</v>
+        <v>1.032185988270528</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117637813577692</v>
+        <v>1.117638475846561</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9225695388178958</v>
+        <v>0.9235419239559498</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715973030137897</v>
+        <v>0.4715961736724705</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048393256835018</v>
+        <v>1.048391245906571</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.46641221437817</v>
+        <v>37.53581020972887</v>
       </c>
       <c r="E5" t="n">
-        <v>368.8835266087273</v>
+        <v>363.8267958394698</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3311100064456307</v>
+        <v>-0.329590365231581</v>
       </c>
       <c r="G5" t="n">
-        <v>0.567233773715012</v>
+        <v>0.5672363344332476</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5837275948452005</v>
+        <v>-0.5810459331045678</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367560791075611</v>
+        <v>0.7367512093186629</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312614269916075</v>
+        <v>0.8312595887786343</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.93658534653074</v>
+        <v>10.96939770779997</v>
       </c>
       <c r="E6" t="n">
-        <v>194.6224536684452</v>
+        <v>190.2474790878316</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3012170498787368</v>
+        <v>-0.2999816947426205</v>
       </c>
       <c r="G6" t="n">
-        <v>0.720440540929546</v>
+        <v>0.7204443123981737</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4181011933199824</v>
+        <v>-0.4163842917213943</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500467749124442</v>
+        <v>0.7500410521066084</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074826364541902</v>
+        <v>1.074823665681338</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.36788708125481</v>
+        <v>10.43290468390176</v>
       </c>
       <c r="E7" t="n">
-        <v>383.1608598263206</v>
+        <v>381.0603542808956</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2782186242120286</v>
+        <v>-0.2747243535074416</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178174642394195</v>
+        <v>1.17821270494101</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2361437890452764</v>
+        <v>-0.2331704219071347</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386699171364774</v>
+        <v>0.7386407076632487</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731059129755309</v>
+        <v>1.731046399213521</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.14657167545495</v>
+        <v>10.18718100783094</v>
       </c>
       <c r="E8" t="n">
-        <v>707.6697207851769</v>
+        <v>696.2683967730164</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5383627055025465</v>
+        <v>-0.5373063970091754</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8101006638378119</v>
+        <v>0.8100801693706072</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6645627260099748</v>
+        <v>-0.6632755834853188</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838544334669912</v>
+        <v>0.6838761977006724</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101931185227572</v>
+        <v>1.101938249052921</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.814256450270187</v>
+        <v>7.7885863667592</v>
       </c>
       <c r="E9" t="n">
-        <v>631.3550217220502</v>
+        <v>653.708613534289</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5583703988139466</v>
+        <v>0.5504674809160111</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4913763413980993</v>
+        <v>0.4904845439500456</v>
       </c>
       <c r="H9" t="n">
-        <v>1.136339607285998</v>
+        <v>1.122293225557938</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6696539452895266</v>
+        <v>0.6707819467707486</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6545103119797065</v>
+        <v>0.6544228591095426</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.188630183362799</v>
+        <v>7.218889283942646</v>
       </c>
       <c r="E10" t="n">
-        <v>240.4049717233619</v>
+        <v>238.8451785514397</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1937596794490128</v>
+        <v>-0.1907274911958995</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9664824014670346</v>
+        <v>0.9665006958311391</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2004792628969786</v>
+        <v>-0.1973381830127748</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132353598973293</v>
+        <v>0.7132182345555026</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371130007265096</v>
+        <v>1.371122879613655</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.925401656692129</v>
+        <v>6.941140355179064</v>
       </c>
       <c r="E11" t="n">
-        <v>516.1643003743659</v>
+        <v>514.0105044345452</v>
       </c>
       <c r="F11" t="n">
-        <v>1.110489398255748</v>
+        <v>1.111416560555425</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283017980112122</v>
+        <v>0.8283021637113626</v>
       </c>
       <c r="H11" t="n">
-        <v>1.340682105148244</v>
+        <v>1.341800865973253</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626768017353118</v>
+        <v>0.6626758540001214</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091797739433221</v>
+        <v>1.091796533426492</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.582393289296177</v>
+        <v>6.535461745926515</v>
       </c>
       <c r="E12" t="n">
-        <v>145.921832195401</v>
+        <v>139.3967497306863</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2433180308165068</v>
+        <v>-0.2438979934015429</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663469892819092</v>
+        <v>0.6634852504896893</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.366735602398845</v>
+        <v>-0.367601228846508</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7885467155814893</v>
+        <v>0.7885400923250419</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040639882892492</v>
+        <v>1.040655109572397</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.811499377814563</v>
+        <v>4.819127184648376</v>
       </c>
       <c r="E13" t="n">
-        <v>94.32219246786576</v>
+        <v>93.96766342525946</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3619697695855547</v>
+        <v>-0.3626029382697891</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8580080622943669</v>
+        <v>0.8580122969417705</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4218722241579235</v>
+        <v>-0.4226080903061898</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603663624875797</v>
+        <v>0.7603651797739015</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297675436160869</v>
+        <v>1.297679671812284</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.765328035357993</v>
+        <v>4.783714701895654</v>
       </c>
       <c r="E14" t="n">
-        <v>189.1565302778925</v>
+        <v>188.7849905064473</v>
       </c>
       <c r="F14" t="n">
-        <v>1.848539135706206</v>
+        <v>1.858180645496402</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664885378365259</v>
+        <v>0.8664643656018656</v>
       </c>
       <c r="H14" t="n">
-        <v>2.13336825011176</v>
+        <v>2.144555182261497</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021325618543383</v>
+        <v>0.6021525487139516</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037783483777068</v>
+        <v>1.037788859292247</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.3950656945645</v>
+        <v>4.454322940157879</v>
       </c>
       <c r="E15" t="n">
-        <v>383.9462738206967</v>
+        <v>296.6448537774909</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05656596968410699</v>
+        <v>0.7148159955764037</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7971602906748128</v>
+        <v>0.9654741795017335</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07095934198656925</v>
+        <v>0.7403781589946914</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>264</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169465798424752</v>
+        <v>0.5121928617220817</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136800545398206</v>
+        <v>0.9836168363947697</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.331513681943129</v>
+        <v>4.395999036176959</v>
       </c>
       <c r="E16" t="n">
-        <v>299.8160169512761</v>
+        <v>365.5424996532483</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6431316129111795</v>
+        <v>0.05710200870763771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9642380608876562</v>
+        <v>0.7971631052132356</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6669842635325209</v>
+        <v>0.07163152475849131</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>264</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5128747925457238</v>
+        <v>0.7169407127225274</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9836655088612479</v>
+        <v>1.136795124274834</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.584707421466888</v>
+        <v>3.586083650883852</v>
       </c>
       <c r="E17" t="n">
-        <v>113.3574917545029</v>
+        <v>111.0500091965164</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1433690357958857</v>
+        <v>-0.1479333273759477</v>
       </c>
       <c r="G17" t="n">
-        <v>0.756913997172691</v>
+        <v>0.7569098030081278</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1894125836375249</v>
+        <v>-0.1954437989678925</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230594389151601</v>
+        <v>0.7230643663730117</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088610090183389</v>
+        <v>1.088611350368173</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.298963201152283</v>
+        <v>3.301884415963005</v>
       </c>
       <c r="E18" t="n">
-        <v>63.21423653729132</v>
+        <v>62.49404524850002</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4302002759092179</v>
+        <v>-0.431852379117704</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7532704769783112</v>
+        <v>0.7532278728447095</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5711099652211706</v>
+        <v>-0.573335632796926</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7640562963945335</v>
+        <v>0.7640920080906288</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144796055931101</v>
+        <v>1.144784679111261</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.977285698940998</v>
+        <v>2.986159411466623</v>
       </c>
       <c r="E19" t="n">
-        <v>103.759938213437</v>
+        <v>100.7187616505543</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1230604303844198</v>
+        <v>0.1259244689469892</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859858434922239</v>
+        <v>0.4860130613230994</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2532181380019743</v>
+        <v>0.2590968823022539</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174491733802435</v>
+        <v>0.717401821881576</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935321163526178</v>
+        <v>0.6935251019398271</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.672222982871452</v>
+        <v>2.677607355407413</v>
       </c>
       <c r="E20" t="n">
-        <v>113.5164332099147</v>
+        <v>113.3438545298538</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.295131244793984</v>
+        <v>-0.2956487357353516</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858289969604957</v>
+        <v>0.7858251707306728</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3755667529901808</v>
+        <v>-0.3762271135454374</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732015875817656</v>
+        <v>0.7320166125551445</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144195852889683</v>
+        <v>1.144191300660438</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.3672876729883</v>
+        <v>582.0814114398707</v>
       </c>
       <c r="E2" t="n">
-        <v>10034.70213233406</v>
+        <v>9914.60768261886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6899848508479662</v>
+        <v>0.6896696702780689</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027455454405244</v>
+        <v>0.5027456461769161</v>
       </c>
       <c r="H2" t="n">
-        <v>1.372433544375566</v>
+        <v>1.371806350830882</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.8598883875713</v>
+        <v>227.8178351032672</v>
       </c>
       <c r="E3" t="n">
-        <v>4306.605290484932</v>
+        <v>4240.461251182974</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2922099386054362</v>
+        <v>0.2921438771685969</v>
       </c>
       <c r="G3" t="n">
-        <v>0.603569661437435</v>
+        <v>0.6035697047508618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4841362269758918</v>
+        <v>0.484026741019393</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908935568848088</v>
+        <v>0.8908936747243578</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069559596066811</v>
+        <v>1.069559599982231</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.7319579764271</v>
+        <v>40.83603941463057</v>
       </c>
       <c r="E4" t="n">
-        <v>1687.927249451345</v>
+        <v>1657.033369451499</v>
       </c>
       <c r="F4" t="n">
-        <v>1.032185988270528</v>
+        <v>1.03653714228006</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117638475846561</v>
+        <v>1.117642970748058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9235419239559498</v>
+        <v>0.9274313617221492</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715961736724705</v>
+        <v>0.471592368203347</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048391245906571</v>
+        <v>1.04838679238492</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.53581020972887</v>
+        <v>37.53279148528655</v>
       </c>
       <c r="E5" t="n">
-        <v>363.8267958394698</v>
+        <v>361.2327979108359</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.329590365231581</v>
+        <v>-0.3299703649886501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672363344332476</v>
+        <v>0.5672350870775722</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5810459331045678</v>
+        <v>-0.5817171266479236</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367512093186629</v>
+        <v>0.7367524042548419</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312595887786343</v>
+        <v>0.8312589424892656</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.96939770779997</v>
+        <v>10.95072805866718</v>
       </c>
       <c r="E6" t="n">
-        <v>190.2474790878316</v>
+        <v>186.9655744509485</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2999816947426205</v>
+        <v>-0.3012170498787368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204443123981737</v>
+        <v>0.720440540929546</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4163842917213943</v>
+        <v>-0.4181011933199824</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500410521066084</v>
+        <v>0.75004535973404</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074823665681338</v>
+        <v>1.074823996582825</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.43290468390176</v>
+        <v>10.45019685152973</v>
       </c>
       <c r="E7" t="n">
-        <v>381.0603542808956</v>
+        <v>377.750143363222</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2747243535074416</v>
+        <v>-0.2735585595216337</v>
       </c>
       <c r="G7" t="n">
-        <v>1.17821270494101</v>
+        <v>1.178228595956461</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2331704219071347</v>
+        <v>-0.2321778307371369</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386407076632487</v>
+        <v>0.7386262229984905</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731046399213521</v>
+        <v>1.731035453569869</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.18718100783094</v>
+        <v>10.16722512416437</v>
       </c>
       <c r="E8" t="n">
-        <v>696.2683967730164</v>
+        <v>691.3133067932201</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5373063970091754</v>
+        <v>-0.5390665398752794</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8100801693706072</v>
+        <v>0.8101168383109605</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6632755834853188</v>
+        <v>-0.6654182636163903</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838761977006724</v>
+        <v>0.6838512274530986</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101938249052921</v>
+        <v>1.101947671694846</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.7885863667592</v>
+        <v>7.798208713464948</v>
       </c>
       <c r="E9" t="n">
-        <v>653.708613534289</v>
+        <v>665.3863961745441</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5504674809160111</v>
+        <v>0.5526890526214026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4904845439500456</v>
+        <v>0.4907310799115874</v>
       </c>
       <c r="H9" t="n">
-        <v>1.122293225557938</v>
+        <v>1.126256467637994</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6707819467707486</v>
+        <v>0.6703839266689977</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6544228591095426</v>
+        <v>0.6543631571776563</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.218889283942646</v>
+        <v>7.22019843089585</v>
       </c>
       <c r="E10" t="n">
-        <v>238.8451785514397</v>
+        <v>238.1480483919211</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1907274911958995</v>
+        <v>-0.1910164066975764</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665006958311391</v>
+        <v>0.9664985005661142</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1973381830127748</v>
+        <v>-0.1976375613471629</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132182345555026</v>
+        <v>0.7132176428854955</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371122879613655</v>
+        <v>1.371118353123553</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.941140355179064</v>
+        <v>6.940271713999986</v>
       </c>
       <c r="E11" t="n">
-        <v>514.0105044345452</v>
+        <v>512.0322113872807</v>
       </c>
       <c r="F11" t="n">
-        <v>1.111416560555425</v>
+        <v>1.114198723402611</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283021637113626</v>
+        <v>0.8283042650005444</v>
       </c>
       <c r="H11" t="n">
-        <v>1.341800865973253</v>
+        <v>1.345156327792032</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626758540001214</v>
+        <v>0.6626725887222357</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091796533426492</v>
+        <v>1.091793704652837</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.535461745926515</v>
+        <v>6.541904384183073</v>
       </c>
       <c r="E12" t="n">
-        <v>139.3967497306863</v>
+        <v>136.2725888345335</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2438979934015429</v>
+        <v>-0.2423511531312955</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6634852504896893</v>
+        <v>0.663445662287949</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.367601228846508</v>
+        <v>-0.3652916386483361</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7885400923250419</v>
+        <v>0.7885926424744963</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040655109572397</v>
+        <v>1.040662155784808</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.819127184648376</v>
+        <v>4.811040467888581</v>
       </c>
       <c r="E13" t="n">
-        <v>93.96766342525946</v>
+        <v>93.37359383993183</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3626029382697891</v>
+        <v>-0.3632359329585338</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8580122969417705</v>
+        <v>0.8580173447514219</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4226080903061898</v>
+        <v>-0.4233433451904958</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603651797739015</v>
+        <v>0.7603630721574579</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297679671812284</v>
+        <v>1.297683449236664</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.783714701895654</v>
+        <v>4.785736406400283</v>
       </c>
       <c r="E14" t="n">
-        <v>188.7849905064473</v>
+        <v>185.6865672618295</v>
       </c>
       <c r="F14" t="n">
-        <v>1.858180645496402</v>
+        <v>1.864613324048329</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664643656018656</v>
+        <v>0.8664534475081502</v>
       </c>
       <c r="H14" t="n">
-        <v>2.144555182261497</v>
+        <v>2.152006353498628</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021525487139516</v>
+        <v>0.6021604223402232</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037788859292247</v>
+        <v>1.037789144186936</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.454322940157879</v>
+        <v>4.515671325120485</v>
       </c>
       <c r="E15" t="n">
-        <v>296.6448537774909</v>
+        <v>313.0189010165745</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7148159955764037</v>
+        <v>0.7524244617003593</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9654741795017335</v>
+        <v>0.9666804856677218</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7403781589946914</v>
+        <v>0.7783590057480388</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5121928617220817</v>
+        <v>0.5115212561031833</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9836168363947697</v>
+        <v>0.9835542486332773</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.395999036176959</v>
+        <v>4.379088985463375</v>
       </c>
       <c r="E16" t="n">
-        <v>365.5424996532483</v>
+        <v>393.4368850397919</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05710200870763771</v>
+        <v>0.04924765123698216</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7971631052132356</v>
+        <v>0.7971451520521112</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07163152475849131</v>
+        <v>0.06178002978529402</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169407127225274</v>
+        <v>0.7169608842240661</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136795124274834</v>
+        <v>1.136801277974849</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.586083650883852</v>
+        <v>3.575535607884759</v>
       </c>
       <c r="E17" t="n">
-        <v>111.0500091965164</v>
+        <v>108.6296818708202</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1479333273759477</v>
+        <v>-0.152301101173186</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569098030081278</v>
+        <v>0.7569310743235265</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1954437989678925</v>
+        <v>-0.2012086784907045</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230643663730117</v>
+        <v>0.7230490952576745</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088611350368173</v>
+        <v>1.088618733198241</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.301884415963005</v>
+        <v>3.291312544564692</v>
       </c>
       <c r="E18" t="n">
-        <v>62.49404524850002</v>
+        <v>62.56125381155996</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.431852379117704</v>
+        <v>-0.4339156400189538</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7532278728447095</v>
+        <v>0.7531860764694354</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.573335632796926</v>
+        <v>-0.5761068261550136</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7640920080906288</v>
+        <v>0.764132646840924</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144784679111261</v>
+        <v>1.144781808759394</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.986159411466623</v>
+        <v>2.987709353509903</v>
       </c>
       <c r="E19" t="n">
-        <v>100.7187616505543</v>
+        <v>100.140503036797</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1259244689469892</v>
+        <v>0.1278349488848183</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4860130613230994</v>
+        <v>0.4860365576011608</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2590968823022539</v>
+        <v>0.2630150898849033</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717401821881576</v>
+        <v>0.7173599906055368</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935251019398271</v>
+        <v>0.693518050421906</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.677607355407413</v>
+        <v>2.676136092441</v>
       </c>
       <c r="E20" t="n">
-        <v>113.3438545298538</v>
+        <v>112.4829190380893</v>
       </c>
       <c r="F20" t="n">
         <v>-0.2956487357353516</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320166125551445</v>
+        <v>0.7320146622241214</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144191300660438</v>
+        <v>1.144188022897767</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.0814114398707</v>
+        <v>580.877373690215</v>
       </c>
       <c r="E2" t="n">
-        <v>9914.60768261886</v>
+        <v>9928.458769207919</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6896696702780689</v>
+        <v>0.6851006012249863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027456461769161</v>
+        <v>0.5027526729345647</v>
       </c>
       <c r="H2" t="n">
-        <v>1.371806350830882</v>
+        <v>1.362699072739002</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.8178351032672</v>
+        <v>226.8051489651916</v>
       </c>
       <c r="E3" t="n">
-        <v>4240.461251182974</v>
+        <v>4283.72155072567</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2921438771685969</v>
+        <v>0.2855424565774722</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035697047508618</v>
+        <v>0.6035896578953733</v>
       </c>
       <c r="H3" t="n">
-        <v>0.484026741019393</v>
+        <v>0.4730738057592239</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908936747243578</v>
+        <v>0.8908947729976101</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069559599982231</v>
+        <v>1.069581327366492</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.83603941463057</v>
+        <v>40.52907834167108</v>
       </c>
       <c r="E4" t="n">
-        <v>1657.033369451499</v>
+        <v>1558.576957545233</v>
       </c>
       <c r="F4" t="n">
-        <v>1.03653714228006</v>
+        <v>1.017338999864816</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117642970748058</v>
+        <v>1.117645401554649</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9274313617221492</v>
+        <v>0.9102520338290607</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471592368203347</v>
+        <v>0.4716081781917677</v>
       </c>
       <c r="N4" t="n">
-        <v>1.04838679238492</v>
+        <v>1.048409566109254</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.53279148528655</v>
+        <v>37.30971934453531</v>
       </c>
       <c r="E5" t="n">
-        <v>361.2327979108359</v>
+        <v>365.3562927104558</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3299703649886501</v>
+        <v>-0.3352840940095975</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672350870775722</v>
+        <v>0.5672601259530503</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5817171266479236</v>
+        <v>-0.5910588082430237</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367524042548419</v>
+        <v>0.7367628911479764</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312589424892656</v>
+        <v>0.8312958496881638</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.95072805866718</v>
+        <v>10.82058794106589</v>
       </c>
       <c r="E6" t="n">
-        <v>186.9655744509485</v>
+        <v>197.7415874682678</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3012170498787368</v>
+        <v>-0.3116931325403627</v>
       </c>
       <c r="G6" t="n">
-        <v>0.720440540929546</v>
+        <v>0.720533525487168</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4181011933199824</v>
+        <v>-0.432586578576785</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.75004535973404</v>
+        <v>0.7500255281019456</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074823996582825</v>
+        <v>1.074919273555026</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.45019685152973</v>
+        <v>10.30182350778305</v>
       </c>
       <c r="E7" t="n">
-        <v>377.750143363222</v>
+        <v>380.6518788224017</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2735585595216337</v>
+        <v>-0.2844191120203916</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178228595956461</v>
+        <v>1.178142573175382</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2321778307371369</v>
+        <v>-0.2414131519361129</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386262229984905</v>
+        <v>0.73867271890379</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731035453569869</v>
+        <v>1.730993835804101</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.16722512416437</v>
+        <v>9.98080558278461</v>
       </c>
       <c r="E8" t="n">
-        <v>691.3133067932201</v>
+        <v>719.1994730423006</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5390665398752794</v>
+        <v>-0.5508987479162897</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8101168383109605</v>
+        <v>0.8106926370474029</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6654182636163903</v>
+        <v>-0.6795408305701406</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838512274530986</v>
+        <v>0.6835591970089218</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101947671694846</v>
+        <v>1.102244578366058</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.798208713464948</v>
+        <v>7.653225505974199</v>
       </c>
       <c r="E9" t="n">
-        <v>665.3863961745441</v>
+        <v>692.1068446143685</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5526890526214026</v>
+        <v>0.5091603712115185</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4907310799115874</v>
+        <v>0.4865042159242521</v>
       </c>
       <c r="H9" t="n">
-        <v>1.126256467637994</v>
+        <v>1.046569288704363</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6703839266689977</v>
+        <v>0.6756093178263445</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6543631571776563</v>
+        <v>0.6537743091880179</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.22019843089585</v>
+        <v>7.105844788533714</v>
       </c>
       <c r="E10" t="n">
-        <v>238.1480483919211</v>
+        <v>246.1156271264529</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1910164066975764</v>
+        <v>-0.2082989276328122</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9664985005661142</v>
+        <v>0.9665412922364887</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1976375613471629</v>
+        <v>-0.2155096003718863</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132176428854955</v>
+        <v>0.7132446650041646</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371118353123553</v>
+        <v>1.371211844921672</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.940271713999986</v>
+        <v>6.871517919431515</v>
       </c>
       <c r="E11" t="n">
-        <v>512.0322113872807</v>
+        <v>528.7495457096715</v>
       </c>
       <c r="F11" t="n">
-        <v>1.114198723402611</v>
+        <v>1.086730861660416</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283042650005444</v>
+        <v>0.8283496864619017</v>
       </c>
       <c r="H11" t="n">
-        <v>1.345156327792032</v>
+        <v>1.31192282609791</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626725887222357</v>
+        <v>0.6626866552838578</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091793704652837</v>
+        <v>1.091861491104028</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.541904384183073</v>
+        <v>6.617056240990248</v>
       </c>
       <c r="E12" t="n">
-        <v>136.2725888345335</v>
+        <v>140.3534409115821</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2423511531312955</v>
+        <v>-0.2583569497181868</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663445662287949</v>
+        <v>0.6640687516699398</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3652916386483361</v>
+        <v>-0.3890515087007093</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7885926424744963</v>
+        <v>0.7880838241987259</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040662155784808</v>
+        <v>1.040952877072093</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.811040467888581</v>
+        <v>4.747231004050034</v>
       </c>
       <c r="E13" t="n">
-        <v>93.37359383993183</v>
+        <v>101.7047996505354</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3632359329585338</v>
+        <v>-0.3745999956575028</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8580173447514219</v>
+        <v>0.85824722851448</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4233433451904958</v>
+        <v>-0.4364709645563192</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603630721574579</v>
+        <v>0.7602721576379372</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297683449236664</v>
+        <v>1.297857788404855</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.785736406400283</v>
+        <v>4.739321796994731</v>
       </c>
       <c r="E14" t="n">
-        <v>185.6865672618295</v>
+        <v>191.3529582276061</v>
       </c>
       <c r="F14" t="n">
-        <v>1.864613324048329</v>
+        <v>1.827680165634882</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8664534475081502</v>
+        <v>0.8665729968864067</v>
       </c>
       <c r="H14" t="n">
-        <v>2.152006353498628</v>
+        <v>2.109089681079066</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021604223402232</v>
+        <v>0.6021574619206469</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037789144186936</v>
+        <v>1.037912724219376</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.515671325120485</v>
+        <v>4.458389908549935</v>
       </c>
       <c r="E15" t="n">
-        <v>313.0189010165745</v>
+        <v>316.6635543269663</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7524244617003593</v>
+        <v>0.7076095392228143</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9666804856677218</v>
+        <v>0.9652863293296688</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7783590057480388</v>
+        <v>0.733056625503238</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5115212561031833</v>
+        <v>0.5120504118461705</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9835542486332773</v>
+        <v>0.9831380101823286</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.379088985463375</v>
+        <v>4.260200638868251</v>
       </c>
       <c r="E16" t="n">
-        <v>393.4368850397919</v>
+        <v>426.67266475519</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04924765123698216</v>
+        <v>0.009867589045347014</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7971451520521112</v>
+        <v>0.7978178823456078</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06178002978529402</v>
+        <v>0.01236822245239229</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169608842240661</v>
+        <v>0.7165650279861054</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136801277974849</v>
+        <v>1.137116566390098</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.575535607884759</v>
+        <v>3.551547600590585</v>
       </c>
       <c r="E17" t="n">
-        <v>108.6296818708202</v>
+        <v>108.7778238437417</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.152301101173186</v>
+        <v>-0.1579888497780818</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569310743235265</v>
+        <v>0.7569960148734683</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2012086784907045</v>
+        <v>-0.2087049953684229</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230490952576745</v>
+        <v>0.7230522128746982</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088618733198241</v>
+        <v>1.088701608480217</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.291312544564692</v>
+        <v>3.228884449738603</v>
       </c>
       <c r="E18" t="n">
-        <v>62.56125381155996</v>
+        <v>68.58485459307376</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4339156400189538</v>
+        <v>-0.4495282416463786</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531860764694354</v>
+        <v>0.7532846101091263</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5761068261550136</v>
+        <v>-0.5967575012335068</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764132646840924</v>
+        <v>0.7641370263304482</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144781808759394</v>
+        <v>1.144922131571038</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.987709353509903</v>
+        <v>2.969158023700882</v>
       </c>
       <c r="E19" t="n">
-        <v>100.140503036797</v>
+        <v>99.85114870792871</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1278349488848183</v>
+        <v>0.1154328743404385</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4860365576011608</v>
+        <v>0.4859603613221928</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2630150898849033</v>
+        <v>0.2375355760012414</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173599906055368</v>
+        <v>0.7174847092130376</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693518050421906</v>
+        <v>0.6935201885593894</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.676136092441</v>
+        <v>2.656669906987814</v>
       </c>
       <c r="E20" t="n">
-        <v>112.4829190380893</v>
+        <v>113.7313867331453</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2956487357353516</v>
+        <v>-0.3013341862283638</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858251707306728</v>
+        <v>0.7858156592632695</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3762271135454374</v>
+        <v>-0.3834667617986584</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320146622241214</v>
+        <v>0.7320337454481415</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144188022897767</v>
+        <v>1.144188009831151</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.877373690215</v>
+        <v>580.850016013208</v>
       </c>
       <c r="E2" t="n">
-        <v>9928.458769207919</v>
+        <v>9802.988862390916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6851006012249863</v>
+        <v>0.6841363798218858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027526729345647</v>
+        <v>0.5027554878524485</v>
       </c>
       <c r="H2" t="n">
-        <v>1.362699072739002</v>
+        <v>1.360773569562049</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8051489651916</v>
+        <v>226.8422431178145</v>
       </c>
       <c r="E3" t="n">
-        <v>4283.72155072567</v>
+        <v>4251.971006757836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2855424565774722</v>
+        <v>0.2862870055278433</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035896578953733</v>
+        <v>0.6035858575088136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4730738057592239</v>
+        <v>0.4743103271329761</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908947729976101</v>
+        <v>0.8908981746356693</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069581327366492</v>
+        <v>1.069572688281274</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.52907834167108</v>
+        <v>40.59207868409595</v>
       </c>
       <c r="E4" t="n">
-        <v>1558.576957545233</v>
+        <v>1534.119857769887</v>
       </c>
       <c r="F4" t="n">
-        <v>1.017338999864816</v>
+        <v>1.018786159793824</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117645401554649</v>
+        <v>1.117643208197904</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9102520338290607</v>
+        <v>0.9115486519499567</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716081781917677</v>
+        <v>0.4716067859068709</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048409566109254</v>
+        <v>1.048398543515352</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.30971934453531</v>
+        <v>37.35450392446763</v>
       </c>
       <c r="E5" t="n">
-        <v>365.3562927104558</v>
+        <v>362.8911385440983</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3352840940095975</v>
+        <v>-0.3341464236965374</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672601259530503</v>
+        <v>0.5672480818123197</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5910588082430237</v>
+        <v>-0.5890657622480836</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367628911479764</v>
+        <v>0.7367676932684936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312958496881638</v>
+        <v>0.8312789633248057</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.82058794106589</v>
+        <v>10.88134308740019</v>
       </c>
       <c r="E6" t="n">
-        <v>197.7415874682678</v>
+        <v>198.4892702796337</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3116931325403627</v>
+        <v>-0.3067686662364406</v>
       </c>
       <c r="G6" t="n">
-        <v>0.720533525487168</v>
+        <v>0.7204618964038102</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.432586578576785</v>
+        <v>-0.4257944351639944</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500255281019456</v>
+        <v>0.7500590911664112</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074919273555026</v>
+        <v>1.07485449347351</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.30182350778305</v>
+        <v>10.33796974061714</v>
       </c>
       <c r="E7" t="n">
-        <v>380.6518788224017</v>
+        <v>376.6195793625797</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2844191120203916</v>
+        <v>-0.2832576485712183</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178142573175382</v>
+        <v>1.17814511523012</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2414131519361129</v>
+        <v>-0.2404267903074836</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.73867271890379</v>
+        <v>0.7386584165841806</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730993835804101</v>
+        <v>1.730954363202639</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.98080558278461</v>
+        <v>10.06459577826743</v>
       </c>
       <c r="E8" t="n">
-        <v>719.1994730423006</v>
+        <v>721.7243143950872</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5508987479162897</v>
+        <v>-0.545037109321646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8106926370474029</v>
+        <v>0.8103354209385406</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6795408305701406</v>
+        <v>-0.672606793727932</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6835591970089218</v>
+        <v>0.6838119900059738</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102244578366058</v>
+        <v>1.102160175578108</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.653225505974199</v>
+        <v>7.705910982704047</v>
       </c>
       <c r="E9" t="n">
-        <v>692.1068446143685</v>
+        <v>656.3949559893923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5091603712115185</v>
+        <v>0.525842720674514</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4865042159242521</v>
+        <v>0.4879723587403679</v>
       </c>
       <c r="H9" t="n">
-        <v>1.046569288704363</v>
+        <v>1.077607596528425</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6756093178263445</v>
+        <v>0.6733123027491642</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6537743091880179</v>
+        <v>0.6535140848384837</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.105844788533714</v>
+        <v>7.119448291425626</v>
       </c>
       <c r="E10" t="n">
-        <v>246.1156271264529</v>
+        <v>244.9128265778392</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2082989276328122</v>
+        <v>-0.2060005653235844</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665412922364887</v>
+        <v>0.9665157524823772</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2155096003718863</v>
+        <v>-0.2131373076894993</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132446650041646</v>
+        <v>0.713254980936064</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371211844921672</v>
+        <v>1.371187766753019</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.871517919431515</v>
+        <v>6.881324441076177</v>
       </c>
       <c r="E11" t="n">
-        <v>528.7495457096715</v>
+        <v>529.1186656869119</v>
       </c>
       <c r="F11" t="n">
-        <v>1.086730861660416</v>
+        <v>1.088887650942858</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283496864619017</v>
+        <v>0.8283407772510423</v>
       </c>
       <c r="H11" t="n">
-        <v>1.31192282609791</v>
+        <v>1.314540682829203</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626866552838578</v>
+        <v>0.6626938148525889</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091861491104028</v>
+        <v>1.09185543059762</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.617056240990248</v>
+        <v>6.66460723389959</v>
       </c>
       <c r="E12" t="n">
-        <v>140.3534409115821</v>
+        <v>139.4773494339632</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2583569497181868</v>
+        <v>-0.2512335194324122</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6640687516699398</v>
+        <v>0.6637329496313205</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3890515087007093</v>
+        <v>-0.3785159672605727</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7880838241987259</v>
+        <v>0.7884499412249992</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040952877072093</v>
+        <v>1.04090401352217</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.747231004050034</v>
+        <v>4.762472010310842</v>
       </c>
       <c r="E13" t="n">
-        <v>101.7047996505354</v>
+        <v>101.7154971387146</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3745999956575028</v>
+        <v>-0.3727099211058922</v>
       </c>
       <c r="G13" t="n">
-        <v>0.85824722851448</v>
+        <v>0.858190626107366</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4364709645563192</v>
+        <v>-0.4342973574489538</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7602721576379372</v>
+        <v>0.7603227347728573</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297857788404855</v>
+        <v>1.297851260829763</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.739321796994731</v>
+        <v>4.750798828424755</v>
       </c>
       <c r="E14" t="n">
-        <v>191.3529582276061</v>
+        <v>190.4975175818074</v>
       </c>
       <c r="F14" t="n">
-        <v>1.827680165634882</v>
+        <v>1.835697825497757</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8665729968864067</v>
+        <v>0.8665353170287992</v>
       </c>
       <c r="H14" t="n">
-        <v>2.109089681079066</v>
+        <v>2.118433939648356</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021574619206469</v>
+        <v>0.6021795811575179</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037912724219376</v>
+        <v>1.037899907359625</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.458389908549935</v>
+        <v>4.485873478943964</v>
       </c>
       <c r="E15" t="n">
-        <v>316.6635543269663</v>
+        <v>313.4453921409137</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7076095392228143</v>
+        <v>0.7162582941480593</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9652863293296688</v>
+        <v>0.9655134597265954</v>
       </c>
       <c r="H15" t="n">
-        <v>0.733056625503238</v>
+        <v>0.7418418530911856</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5120504118461705</v>
+        <v>0.5118512304343702</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9831380101823286</v>
+        <v>0.9829813185590601</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.260200638868251</v>
+        <v>4.289812867351717</v>
       </c>
       <c r="E16" t="n">
-        <v>426.67266475519</v>
+        <v>424.2186669466522</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009867589045347014</v>
+        <v>0.02277084582102251</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7978178823456078</v>
+        <v>0.7974561494067212</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01236822245239229</v>
+        <v>0.02855435479175025</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7165650279861054</v>
+        <v>0.7168426358616816</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137116566390098</v>
+        <v>1.137034964186393</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.551547600590585</v>
+        <v>3.570877852202286</v>
       </c>
       <c r="E17" t="n">
-        <v>108.7778238437417</v>
+        <v>110.0496196854574</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1579888497780818</v>
+        <v>-0.1517317439011407</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569960148734683</v>
+        <v>0.7569268961134074</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2087049953684229</v>
+        <v>-0.200457593302917</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230522128746982</v>
+        <v>0.7230770751908466</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088701608480217</v>
+        <v>1.088633539362972</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.228884449738603</v>
+        <v>3.247045527266945</v>
       </c>
       <c r="E18" t="n">
-        <v>68.58485459307376</v>
+        <v>69.89460695853815</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4495282416463786</v>
+        <v>-0.4437082052738645</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7532846101091263</v>
+        <v>0.7531617104170482</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5967575012335068</v>
+        <v>-0.5891274066868986</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641370263304482</v>
+        <v>0.7642028137877628</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144922131571038</v>
+        <v>1.144827480245891</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.969158023700882</v>
+        <v>2.962259727216663</v>
       </c>
       <c r="E19" t="n">
-        <v>99.85114870792871</v>
+        <v>100.4922549154368</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1154328743404385</v>
+        <v>0.1144804418402692</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859603613221928</v>
+        <v>0.4859619934072318</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2375355760012414</v>
+        <v>0.2355748873232059</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174847092130376</v>
+        <v>0.7174891051500834</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935201885593894</v>
+        <v>0.6935228838099443</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.656669906987814</v>
+        <v>2.659913059450385</v>
       </c>
       <c r="E20" t="n">
-        <v>113.7313867331453</v>
+        <v>113.3169351919333</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3013341862283638</v>
+        <v>-0.300301416704851</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858156592632695</v>
+        <v>0.7858129462247178</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3834667617986584</v>
+        <v>-0.3821538168180984</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320337454481415</v>
+        <v>0.7320250306849367</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144188009831151</v>
+        <v>1.144164031962974</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.850016013208</v>
+        <v>580.7061277658756</v>
       </c>
       <c r="E2" t="n">
-        <v>9802.988862390916</v>
+        <v>9607.244513238196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6841363798218858</v>
+        <v>0.6842907073390083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027554878524485</v>
+        <v>0.5027550060812964</v>
       </c>
       <c r="H2" t="n">
-        <v>1.360773569562049</v>
+        <v>1.361081837200756</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8422431178145</v>
+        <v>226.9230867630474</v>
       </c>
       <c r="E3" t="n">
-        <v>4251.971006757836</v>
+        <v>4170.718949690138</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2862870055278433</v>
+        <v>0.2877858896741283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035858575088136</v>
+        <v>0.6035794030686009</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4743103271329761</v>
+        <v>0.4767987247593661</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908981746356693</v>
+        <v>0.8908974123016353</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069572688281274</v>
+        <v>1.069561360519662</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.59207868409595</v>
+        <v>40.55097512842821</v>
       </c>
       <c r="E4" t="n">
-        <v>1534.119857769887</v>
+        <v>1494.306127625645</v>
       </c>
       <c r="F4" t="n">
-        <v>1.018786159793824</v>
+        <v>1.021319380487236</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117643208197904</v>
+        <v>1.117640159419889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9115486519499567</v>
+        <v>0.9138177184124734</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716067859068709</v>
+        <v>0.4716021738062116</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048398543515352</v>
+        <v>1.048386435420815</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.35450392446763</v>
+        <v>37.3432809161196</v>
       </c>
       <c r="E5" t="n">
-        <v>362.8911385440983</v>
+        <v>334.4748543473364</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3341464236965374</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367676932684936</v>
+        <v>0.736767305540857</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312789633248057</v>
+        <v>0.8312793224429917</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.88134308740019</v>
+        <v>10.90340478526134</v>
       </c>
       <c r="E6" t="n">
-        <v>198.4892702796337</v>
+        <v>196.268564058347</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3067686662364406</v>
+        <v>-0.3033774676357378</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204618964038102</v>
+        <v>0.7204413934002278</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4257944351639944</v>
+        <v>-0.4210994404470623</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500590911664112</v>
+        <v>0.7500448628372969</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07485449347351</v>
+        <v>1.074804546069119</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.33796974061714</v>
+        <v>10.33377042041851</v>
       </c>
       <c r="E7" t="n">
-        <v>376.6195793625797</v>
+        <v>367.7933096818594</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2832576485712183</v>
+        <v>-0.2817082201967669</v>
       </c>
       <c r="G7" t="n">
-        <v>1.17814511523012</v>
+        <v>1.178150996614794</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2404267903074836</v>
+        <v>-0.2391104544376781</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386584165841806</v>
+        <v>0.7386462437806335</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730954363202639</v>
+        <v>1.730936137342427</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.06459577826743</v>
+        <v>10.06202442788536</v>
       </c>
       <c r="E8" t="n">
-        <v>721.7243143950872</v>
+        <v>710.921958229326</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.545037109321646</v>
+        <v>-0.5446864961314759</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8103354209385406</v>
+        <v>0.8103185469327863</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.672606793727932</v>
+        <v>-0.6721881144066374</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838119900059738</v>
+        <v>0.6838179116244855</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102160175578108</v>
+        <v>1.102147825107016</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.705910982704047</v>
+        <v>7.713758320928194</v>
       </c>
       <c r="E9" t="n">
-        <v>656.3949559893923</v>
+        <v>707.5752198501611</v>
       </c>
       <c r="F9" t="n">
-        <v>0.525842720674514</v>
+        <v>0.5327266516593518</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4879723587403679</v>
+        <v>0.4886335893107311</v>
       </c>
       <c r="H9" t="n">
-        <v>1.077607596528425</v>
+        <v>1.090237477146871</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6733123027491642</v>
+        <v>0.6723749687558144</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6535140848384837</v>
+        <v>0.6534892549487971</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.119448291425626</v>
+        <v>7.112269261279122</v>
       </c>
       <c r="E10" t="n">
-        <v>244.9128265778392</v>
+        <v>242.9919272268389</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2060005653235844</v>
+        <v>-0.2061442669704099</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665157524823772</v>
+        <v>0.9665171699403856</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2131373076894993</v>
+        <v>-0.2132856749799124</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713254980936064</v>
+        <v>0.7132541606894842</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371187766753019</v>
+        <v>1.371189514771997</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.881324441076177</v>
+        <v>6.869433678648168</v>
       </c>
       <c r="E11" t="n">
-        <v>529.1186656869119</v>
+        <v>528.2211721820933</v>
       </c>
       <c r="F11" t="n">
-        <v>1.088887650942858</v>
+        <v>1.087963237186499</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283407772510423</v>
+        <v>0.8283444839248604</v>
       </c>
       <c r="H11" t="n">
-        <v>1.314540682829203</v>
+        <v>1.313418823086156</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626938148525889</v>
+        <v>0.662692753832541</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09185543059762</v>
+        <v>1.091859614592075</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.66460723389959</v>
+        <v>6.483263239728234</v>
       </c>
       <c r="E12" t="n">
-        <v>139.4773494339632</v>
+        <v>137.946809209776</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2512335194324122</v>
+        <v>-0.2496908433729597</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6637329496313205</v>
+        <v>0.6636726147294962</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3785159672605727</v>
+        <v>-0.3762259249987739</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884499412249992</v>
+        <v>0.7885009373170642</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04090401352217</v>
+        <v>1.040877708736838</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.762472010310842</v>
+        <v>4.759592654437196</v>
       </c>
       <c r="E13" t="n">
-        <v>101.7154971387146</v>
+        <v>101.5332820347715</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3727099211058922</v>
+        <v>-0.3720795456666179</v>
       </c>
       <c r="G13" t="n">
-        <v>0.858190626107366</v>
+        <v>0.8581733838800483</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4342973574489538</v>
+        <v>-0.4335715283831567</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603227347728573</v>
+        <v>0.7603295003747869</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297851260829763</v>
+        <v>1.297837977360583</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.750798828424755</v>
+        <v>4.75501005472695</v>
       </c>
       <c r="E14" t="n">
-        <v>190.4975175818074</v>
+        <v>189.2002893005994</v>
       </c>
       <c r="F14" t="n">
-        <v>1.835697825497757</v>
+        <v>1.842116473749208</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8665353170287992</v>
+        <v>0.8665098490507643</v>
       </c>
       <c r="H14" t="n">
-        <v>2.118433939648356</v>
+        <v>2.125903676417748</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021795811575179</v>
+        <v>0.6021821460578559</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037899907359625</v>
+        <v>1.037874818092378</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.485873478943964</v>
+        <v>4.488888755122223</v>
       </c>
       <c r="E15" t="n">
-        <v>313.4453921409137</v>
+        <v>311.3003346039777</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7162582941480593</v>
+        <v>0.7306997101406387</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9655134597265954</v>
+        <v>0.9659375946966701</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7418418530911856</v>
+        <v>0.7564667884886473</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5118512304343702</v>
+        <v>0.5115878358981649</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9829813185590601</v>
+        <v>0.9829080122648076</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.289812867351717</v>
+        <v>4.288358329929964</v>
       </c>
       <c r="E16" t="n">
-        <v>424.2186669466522</v>
+        <v>424.6614496244263</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02277084582102251</v>
+        <v>0.02347918223285062</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7974561494067212</v>
+        <v>0.7974403049428596</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02855435479175025</v>
+        <v>0.02944318475918145</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168426358616816</v>
+        <v>0.7168488354570944</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137034964186393</v>
+        <v>1.137023295701214</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.570877852202286</v>
+        <v>3.565987440893974</v>
       </c>
       <c r="E17" t="n">
-        <v>110.0496196854574</v>
+        <v>106.0001024465013</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1517317439011407</v>
+        <v>-0.1505927120910012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569268961134074</v>
+        <v>0.7569198029902</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.200457593302917</v>
+        <v>-0.1989546468411674</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230770751908466</v>
+        <v>0.7230742833120694</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088633539362972</v>
+        <v>1.088620177724001</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.247045527266945</v>
+        <v>3.246632141680174</v>
       </c>
       <c r="E18" t="n">
-        <v>69.89460695853815</v>
+        <v>69.21241831268375</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4437082052738645</v>
+        <v>-0.442969245764134</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531617104170482</v>
+        <v>0.7531534662438202</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5891274066868986</v>
+        <v>-0.5881527014319423</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642028137877628</v>
+        <v>0.7642015503313829</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144827480245891</v>
+        <v>1.144814153174067</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.962259727216663</v>
+        <v>2.975131968589812</v>
       </c>
       <c r="E19" t="n">
-        <v>100.4922549154368</v>
+        <v>100.1461957762588</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1144804418402692</v>
+        <v>0.1230604303844198</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859619934072318</v>
+        <v>0.4859858434922239</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2355748873232059</v>
+        <v>0.2532181380019743</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174891051500834</v>
+        <v>0.7173719233311597</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935228838099443</v>
+        <v>0.6934443119226908</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.659913059450385</v>
+        <v>2.66127543814095</v>
       </c>
       <c r="E20" t="n">
-        <v>113.3169351919333</v>
+        <v>112.5952533349817</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.300301416704851</v>
+        <v>-0.2987514712757685</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858129462247178</v>
+        <v>0.7858125786742638</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3821538168180984</v>
+        <v>-0.3801815844940902</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320250306849367</v>
+        <v>0.732011230271575</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144164031962974</v>
+        <v>1.144143022984065</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.7061277658756</v>
+        <v>580.5270952071265</v>
       </c>
       <c r="E2" t="n">
-        <v>9607.244513238196</v>
+        <v>9309.743200018271</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6842907073390083</v>
+        <v>0.6830741203299</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027550060812964</v>
+        <v>0.5027591269867138</v>
       </c>
       <c r="H2" t="n">
-        <v>1.361081837200756</v>
+        <v>1.358650860152264</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.9230867630474</v>
+        <v>226.8946282100284</v>
       </c>
       <c r="E3" t="n">
-        <v>4170.718949690138</v>
+        <v>4064.403791086665</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2877858896741283</v>
+        <v>0.2860985008457411</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035794030686009</v>
+        <v>0.6035867823871482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4767987247593661</v>
+        <v>0.4739972928403755</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908974123016353</v>
+        <v>0.8908996907568534</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069561360519662</v>
+        <v>1.069568405444074</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.55097512842821</v>
+        <v>40.47594435085916</v>
       </c>
       <c r="E4" t="n">
-        <v>1494.306127625645</v>
+        <v>1465.523373493258</v>
       </c>
       <c r="F4" t="n">
-        <v>1.021319380487236</v>
+        <v>1.013360791253078</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117640159419889</v>
+        <v>1.1176531252588</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9138177184124734</v>
+        <v>0.9066863129098556</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716021738062116</v>
+        <v>0.471617702756379</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048386435420815</v>
+        <v>1.048424526019539</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.3432809161196</v>
+        <v>37.31332978572385</v>
       </c>
       <c r="E5" t="n">
-        <v>334.4748543473364</v>
+        <v>327.3694448190353</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3341464236965374</v>
+        <v>-0.334904930389621</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672480818123197</v>
+        <v>0.5672557064977286</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5890657622480836</v>
+        <v>-0.5903949956843</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.736767305540857</v>
+        <v>0.7367724308356398</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312793224429917</v>
+        <v>0.8312894651692007</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.90340478526134</v>
+        <v>10.9084900257413</v>
       </c>
       <c r="E6" t="n">
-        <v>196.268564058347</v>
+        <v>193.2052160889432</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3033774676357378</v>
+        <v>-0.305227780024058</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204413934002278</v>
+        <v>0.7204496733774729</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4210994404470623</v>
+        <v>-0.4236628751501103</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500448628372969</v>
+        <v>0.7500555991834051</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074804546069119</v>
+        <v>1.074823473987195</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.33377042041851</v>
+        <v>10.34941195302341</v>
       </c>
       <c r="E7" t="n">
-        <v>367.7933096818594</v>
+        <v>344.7603226641942</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2817082201967669</v>
+        <v>-0.2820956640815966</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178150996614794</v>
+        <v>1.178149259272702</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2391104544376781</v>
+        <v>-0.2394396651029943</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386462437806335</v>
+        <v>0.7386393059824727</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730936137342427</v>
+        <v>1.730903139299846</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.06202442788536</v>
+        <v>10.05152490493689</v>
       </c>
       <c r="E8" t="n">
-        <v>710.921958229326</v>
+        <v>550.4421285125303</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5446864961314759</v>
+        <v>-0.5467890534938722</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8103185469327863</v>
+        <v>0.8104273181828744</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6721881144066374</v>
+        <v>-0.6746922780439741</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6838179116244855</v>
+        <v>0.6837869103593769</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102147825107016</v>
+        <v>1.102236761553108</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.713758320928194</v>
+        <v>7.711127515615454</v>
       </c>
       <c r="E9" t="n">
-        <v>707.5752198501611</v>
+        <v>708.161081067994</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5327266516593518</v>
+        <v>0.5265798744636476</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4886335893107311</v>
+        <v>0.4880416280183628</v>
       </c>
       <c r="H9" t="n">
-        <v>1.090237477146871</v>
+        <v>1.078965080502999</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6723749687558144</v>
+        <v>0.6730373999786156</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6534892549487971</v>
+        <v>0.6533352668732156</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.112269261279122</v>
+        <v>7.118889056216977</v>
       </c>
       <c r="E10" t="n">
-        <v>242.9919272268389</v>
+        <v>237.969898382608</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2061442669704099</v>
+        <v>-0.2065753287228639</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665171699403856</v>
+        <v>0.9665215653384279</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2132856749799124</v>
+        <v>-0.2137306979286401</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132541606894842</v>
+        <v>0.7132599593337101</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371189514771997</v>
+        <v>1.371195658883898</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.869433678648168</v>
+        <v>6.871302537498257</v>
       </c>
       <c r="E11" t="n">
-        <v>528.2211721820933</v>
+        <v>530.5504937491396</v>
       </c>
       <c r="F11" t="n">
-        <v>1.087963237186499</v>
+        <v>1.084574689048739</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283444839248604</v>
+        <v>0.828359506725294</v>
       </c>
       <c r="H11" t="n">
-        <v>1.313418823086156</v>
+        <v>1.309304330116673</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.662692753832541</v>
+        <v>0.6626997872590235</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091859614592075</v>
+        <v>1.091882055271667</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.483263239728234</v>
+        <v>6.473482650361552</v>
       </c>
       <c r="E12" t="n">
-        <v>137.946809209776</v>
+        <v>133.9492418129469</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2496908433729597</v>
+        <v>-0.2531606283312902</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6636726147294962</v>
+        <v>0.6638145058468101</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3762259249987739</v>
+        <v>-0.3813725462482023</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7885009373170642</v>
+        <v>0.7884098478770192</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040877708736838</v>
+        <v>1.04097144234852</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.759592654437196</v>
+        <v>4.761529289683852</v>
       </c>
       <c r="E13" t="n">
-        <v>101.5332820347715</v>
+        <v>98.80148567156976</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3720795456666179</v>
+        <v>-0.3727099211058922</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8581733838800483</v>
+        <v>0.858190626107366</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4335715283831567</v>
+        <v>-0.4342973574489538</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603295003747869</v>
+        <v>0.7603396008080808</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297837977360583</v>
+        <v>1.297870656237645</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.75501005472695</v>
+        <v>4.75461458403586</v>
       </c>
       <c r="E14" t="n">
-        <v>189.2002893005994</v>
+        <v>184.4109313920697</v>
       </c>
       <c r="F14" t="n">
-        <v>1.842116473749208</v>
+        <v>1.834093791051303</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8665098490507643</v>
+        <v>0.8665423334760156</v>
       </c>
       <c r="H14" t="n">
-        <v>2.125903676417748</v>
+        <v>2.116565712022501</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021821460578559</v>
+        <v>0.6021897456832641</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037874818092378</v>
+        <v>1.037918317957247</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.488888755122223</v>
+        <v>4.468251962103388</v>
       </c>
       <c r="E15" t="n">
-        <v>311.3003346039777</v>
+        <v>306.8203540340286</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7306997101406387</v>
+        <v>0.7047293094093299</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9659375946966701</v>
+        <v>0.9652151809431024</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7564667884886473</v>
+        <v>0.7301266321989939</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5115878358981649</v>
+        <v>0.5119946452815994</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9829080122648076</v>
+        <v>0.9829458634580651</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.288358329929964</v>
+        <v>4.309222927923432</v>
       </c>
       <c r="E16" t="n">
-        <v>424.6614496244263</v>
+        <v>425.2046614858515</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02347918223285062</v>
+        <v>0.02720017340072522</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7974403049428596</v>
+        <v>0.7973639032446573</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02944318475918145</v>
+        <v>0.03411262196600756</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168488354570944</v>
+        <v>0.7169168097482912</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137023295701214</v>
+        <v>1.137012845791085</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.565987440893974</v>
+        <v>3.552977256004888</v>
       </c>
       <c r="E17" t="n">
-        <v>106.0001024465013</v>
+        <v>89.04850483213791</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1505927120910012</v>
+        <v>-0.1585570415261972</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569198029902</v>
+        <v>0.7570048245349368</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1989546468411674</v>
+        <v>-0.2094531453265257</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230742833120694</v>
+        <v>0.7230707703730699</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088620177724001</v>
+        <v>1.088728244344876</v>
       </c>
     </row>
     <row r="18">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.246632141680174</v>
+        <v>3.249359676725387</v>
       </c>
       <c r="E18" t="n">
-        <v>69.21241831268375</v>
+        <v>67.77186598213841</v>
       </c>
       <c r="F18" t="n">
         <v>-0.442969245764134</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642015503313829</v>
+        <v>0.7642033546040297</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144814153174067</v>
+        <v>1.144807472486502</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.975131968589812</v>
+        <v>2.97705119723291</v>
       </c>
       <c r="E19" t="n">
-        <v>100.1461957762588</v>
+        <v>100.1446314107048</v>
       </c>
       <c r="F19" t="n">
         <v>0.1230604303844198</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173719233311597</v>
+        <v>0.7173534903331819</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934443119226908</v>
+        <v>0.693420810023157</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.66127543814095</v>
+        <v>2.661088494490966</v>
       </c>
       <c r="E20" t="n">
-        <v>112.5952533349817</v>
+        <v>111.0851113881822</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2987514712757685</v>
+        <v>-0.3008178542327128</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858125786742638</v>
+        <v>0.785814055944586</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3801815844940902</v>
+        <v>-0.3828104778185921</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732011230271575</v>
+        <v>0.732026003244002</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144143022984065</v>
+        <v>1.144158886013173</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.5270952071265</v>
+        <v>580.5207049360598</v>
       </c>
       <c r="E2" t="n">
-        <v>9309.743200018271</v>
+        <v>8975.119278793009</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6830741203299</v>
+        <v>0.6822637169349703</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027591269867138</v>
+        <v>0.5027622827649803</v>
       </c>
       <c r="H2" t="n">
-        <v>1.358650860152264</v>
+        <v>1.357030430331424</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8946282100284</v>
+        <v>226.8275753597937</v>
       </c>
       <c r="E3" t="n">
-        <v>4064.403791086665</v>
+        <v>3940.357956035887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2860985008457411</v>
+        <v>0.2857403630123041</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035867823871482</v>
+        <v>0.6035886092218957</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4739972928403755</v>
+        <v>0.4734025106614597</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908996907568534</v>
+        <v>0.8909007133198479</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069568405444074</v>
+        <v>1.069566156693761</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.47594435085916</v>
+        <v>40.4067952842319</v>
       </c>
       <c r="E4" t="n">
-        <v>1465.523373493258</v>
+        <v>1441.003589912692</v>
       </c>
       <c r="F4" t="n">
-        <v>1.013360791253078</v>
+        <v>1.001439216659283</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1176531252588</v>
+        <v>1.117691185190498</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9066863129098556</v>
+        <v>0.8959891872893305</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471617702756379</v>
+        <v>0.4716395692828618</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048424526019539</v>
+        <v>1.048502258911328</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.31332978572385</v>
+        <v>37.33688696508915</v>
       </c>
       <c r="E5" t="n">
-        <v>327.3694448190353</v>
+        <v>321.1349869978031</v>
       </c>
       <c r="F5" t="n">
         <v>-0.334904930389621</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367724308356398</v>
+        <v>0.7367749157619955</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312894651692007</v>
+        <v>0.8312870509535497</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.9084900257413</v>
+        <v>10.93736807209257</v>
       </c>
       <c r="E6" t="n">
-        <v>193.2052160889432</v>
+        <v>188.5907546800647</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.305227780024058</v>
+        <v>-0.3046111605438558</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204496733774729</v>
+        <v>0.7204461391102654</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4236628751501103</v>
+        <v>-0.422809067892353</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500555991834051</v>
+        <v>0.7500503383401761</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074823473987195</v>
+        <v>1.074803916124568</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.34941195302341</v>
+        <v>10.37542684646565</v>
       </c>
       <c r="E7" t="n">
-        <v>344.7603226641942</v>
+        <v>334.3273112771583</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2820956640815966</v>
+        <v>-0.2817082201967669</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178149259272702</v>
+        <v>1.178150996614794</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2394396651029943</v>
+        <v>-0.2391104544376781</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386393059824727</v>
+        <v>0.7386274954955585</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730903139299846</v>
+        <v>1.730867150891606</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.05152490493689</v>
+        <v>10.06828616939212</v>
       </c>
       <c r="E8" t="n">
-        <v>550.4421285125303</v>
+        <v>457.4660646311463</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5467890534938722</v>
+        <v>-0.5457381114235342</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8104273181828744</v>
+        <v>0.8103706744927966</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6746922780439741</v>
+        <v>-0.6734425721477477</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837869103593769</v>
+        <v>0.683835974256098</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102236761553108</v>
+        <v>1.102231887111148</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.711127515615454</v>
+        <v>7.664891280230087</v>
       </c>
       <c r="E9" t="n">
-        <v>708.161081067994</v>
+        <v>712.4351534145504</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5265798744636476</v>
+        <v>0.5108753272349698</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4880416280183628</v>
+        <v>0.4866463048815856</v>
       </c>
       <c r="H9" t="n">
-        <v>1.078965080502999</v>
+        <v>1.04978774545361</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6730373999786156</v>
+        <v>0.6749897896665349</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6533352668732156</v>
+        <v>0.6533530820321474</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.118889056216977</v>
+        <v>7.12321530731217</v>
       </c>
       <c r="E10" t="n">
-        <v>237.969898382608</v>
+        <v>232.1316894032533</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2065753287228639</v>
+        <v>-0.2072936209819505</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665215653384279</v>
+        <v>0.9665293677419443</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2137306979286401</v>
+        <v>-0.2144721390786506</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132599593337101</v>
+        <v>0.7132641305847119</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371195658883898</v>
+        <v>1.371206140157712</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.871302537498257</v>
+        <v>6.876059801182573</v>
       </c>
       <c r="E11" t="n">
-        <v>530.5504937491396</v>
+        <v>523.72892805522</v>
       </c>
       <c r="F11" t="n">
-        <v>1.084574689048739</v>
+        <v>1.081495512760257</v>
       </c>
       <c r="G11" t="n">
-        <v>0.828359506725294</v>
+        <v>0.8283751160053745</v>
       </c>
       <c r="H11" t="n">
-        <v>1.309304330116673</v>
+        <v>1.305562530626814</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626997872590235</v>
+        <v>0.6627049414946439</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091882055271667</v>
+        <v>1.091904268889994</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.473482650361552</v>
+        <v>6.576033414393712</v>
       </c>
       <c r="E12" t="n">
-        <v>133.9492418129469</v>
+        <v>129.2336441636437</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2531606283312902</v>
+        <v>-0.2554713438644273</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6638145058468101</v>
+        <v>0.6639213717563519</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3813725462482023</v>
+        <v>-0.3847915652852052</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884098478770192</v>
+        <v>0.7883416839861567</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04097144234852</v>
+        <v>1.041042477105363</v>
       </c>
     </row>
     <row r="13">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.761529289683852</v>
+        <v>4.763821657793398</v>
       </c>
       <c r="E13" t="n">
-        <v>98.80148567156976</v>
+        <v>96.11712680401595</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3727099211058922</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603396008080808</v>
+        <v>0.7603518965772056</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297870656237645</v>
+        <v>1.297883497936426</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.75461458403586</v>
+        <v>4.758127115886977</v>
       </c>
       <c r="E14" t="n">
-        <v>184.4109313920697</v>
+        <v>180.2246850021375</v>
       </c>
       <c r="F14" t="n">
-        <v>1.834093791051303</v>
+        <v>1.832490007778266</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8665423334760156</v>
+        <v>0.866549609692045</v>
       </c>
       <c r="H14" t="n">
-        <v>2.116565712022501</v>
+        <v>2.114697170574571</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021897456832641</v>
+        <v>0.6021975517122604</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037918317957247</v>
+        <v>1.037933972540456</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.468251962103388</v>
+        <v>4.482153826962922</v>
       </c>
       <c r="E15" t="n">
-        <v>306.8203540340286</v>
+        <v>304.1701614267087</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7047293094093299</v>
+        <v>0.7133740326034699</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9652151809431024</v>
+        <v>0.9654354692499353</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7301266321989939</v>
+        <v>0.7389142571669791</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5119946452815994</v>
+        <v>0.5117988143838573</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9829458634580651</v>
+        <v>0.9827879804524127</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.309222927923432</v>
+        <v>4.314800625444489</v>
       </c>
       <c r="E16" t="n">
-        <v>425.2046614858515</v>
+        <v>413.4959468357237</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02720017340072522</v>
+        <v>0.02489626205083217</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7973639032446573</v>
+        <v>0.7974098560284284</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03411262196600756</v>
+        <v>0.03122141250527082</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169168097482912</v>
+        <v>0.7169090711359216</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137012845791085</v>
+        <v>1.137058961654848</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.552977256004888</v>
+        <v>3.550749496867782</v>
       </c>
       <c r="E17" t="n">
-        <v>89.04850483213791</v>
+        <v>83.70087066946495</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1585570415261972</v>
+        <v>-0.1589357770557055</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7570048245349368</v>
+        <v>0.757010931514011</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2094531453265257</v>
+        <v>-0.2099517595311817</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230707703730699</v>
+        <v>0.7230773690970136</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088728244344876</v>
+        <v>1.088740129284332</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.249359676725387</v>
+        <v>3.263102623784536</v>
       </c>
       <c r="E18" t="n">
-        <v>67.77186598213841</v>
+        <v>66.59020817295541</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.442969245764134</v>
+        <v>-0.4399284518786737</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531534662438202</v>
+        <v>0.7531369147890248</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5881527014319423</v>
+        <v>-0.5841281223108155</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642033546040297</v>
+        <v>0.7641709794864558</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144807472486502</v>
+        <v>1.144726630439717</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.97705119723291</v>
+        <v>2.980725580331467</v>
       </c>
       <c r="E19" t="n">
-        <v>100.1446314107048</v>
+        <v>98.54283948501352</v>
       </c>
       <c r="F19" t="n">
         <v>0.1230604303844198</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173534903331819</v>
+        <v>0.7173406243376189</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693420810023157</v>
+        <v>0.6934040208281098</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.661088494490966</v>
+        <v>2.66345567379696</v>
       </c>
       <c r="E20" t="n">
-        <v>111.0851113881822</v>
+        <v>109.4426572855928</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3008178542327128</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732026003244002</v>
+        <v>0.73202316795598</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144158886013173</v>
+        <v>1.144147272729666</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.5207049360598</v>
+        <v>580.6350276938477</v>
       </c>
       <c r="E2" t="n">
-        <v>8975.119278793009</v>
+        <v>8805.275331095778</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6822637169349703</v>
+        <v>0.6842922662227795</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027622827649803</v>
+        <v>0.5027550012755896</v>
       </c>
       <c r="H2" t="n">
-        <v>1.357030430331424</v>
+        <v>1.361084950893763</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8275753597937</v>
+        <v>226.8217584788014</v>
       </c>
       <c r="E3" t="n">
-        <v>3940.357956035887</v>
+        <v>3861.298857583566</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2857403630123041</v>
+        <v>0.2869845393171591</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035886092218957</v>
+        <v>0.6035826550167415</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4734025106614597</v>
+        <v>0.4754684995200848</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909007133198479</v>
+        <v>0.8908979599409783</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069566156693761</v>
+        <v>1.069567790764577</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.4067952842319</v>
+        <v>40.09667325917845</v>
       </c>
       <c r="E4" t="n">
-        <v>1441.003589912692</v>
+        <v>1453.153964579863</v>
       </c>
       <c r="F4" t="n">
-        <v>1.001439216659283</v>
+        <v>0.9859344866133666</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117691185190498</v>
+        <v>1.117774285096111</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8959891872893305</v>
+        <v>0.8820515015950573</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716395692828618</v>
+        <v>0.4716272468544149</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048502258911328</v>
+        <v>1.048568004986521</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.33688696508915</v>
+        <v>37.32425532897325</v>
       </c>
       <c r="E5" t="n">
-        <v>321.1349869978031</v>
+        <v>317.7448094930319</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.334904930389621</v>
+        <v>-0.3345257069468589</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672557064977286</v>
+        <v>0.5672516917812872</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5903949956843</v>
+        <v>-0.5897306465431231</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367749157619955</v>
+        <v>0.7367678095907846</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312870509535497</v>
+        <v>0.8312851893665641</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.93736807209257</v>
+        <v>10.91755098881112</v>
       </c>
       <c r="E6" t="n">
-        <v>188.5907546800647</v>
+        <v>186.7955679371414</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3046111605438558</v>
+        <v>-0.3033774676357378</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204461391102654</v>
+        <v>0.7204413934002278</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.422809067892353</v>
+        <v>-0.4210994404470623</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500503383401761</v>
+        <v>0.750044866681663</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074803916124568</v>
+        <v>1.074804561851828</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.37542684646565</v>
+        <v>10.3437895006674</v>
       </c>
       <c r="E7" t="n">
-        <v>334.3273112771583</v>
+        <v>330.2446085207384</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2817082201967669</v>
+        <v>-0.2820956640815966</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178150996614794</v>
+        <v>1.178149259272702</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2391104544376781</v>
+        <v>-0.2394396651029943</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386274954955585</v>
+        <v>0.7386497375391261</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730867150891606</v>
+        <v>1.730941788616176</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.06828616939212</v>
+        <v>10.04402295863534</v>
       </c>
       <c r="E8" t="n">
-        <v>457.4660646311463</v>
+        <v>425.1301517937907</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5457381114235342</v>
+        <v>-0.5469641450045908</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8103706744927966</v>
+        <v>0.8104371978007029</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6734425721477477</v>
+        <v>-0.6749000989699099</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.683835974256098</v>
+        <v>0.6837492412936458</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102231887111148</v>
+        <v>1.102198521559061</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.664891280230087</v>
+        <v>7.625927935365502</v>
       </c>
       <c r="E9" t="n">
-        <v>712.4351534145504</v>
+        <v>715.5621093536108</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5108753272349698</v>
+        <v>0.5045082088270669</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4866463048815856</v>
+        <v>0.4861290471145399</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04978774545361</v>
+        <v>1.037807166269159</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6749897896665349</v>
+        <v>0.6760506174615522</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6533530820321474</v>
+        <v>0.6536938302631217</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.12321530731217</v>
+        <v>7.105108514635902</v>
       </c>
       <c r="E10" t="n">
-        <v>232.1316894032533</v>
+        <v>229.8639571107562</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2072936209819505</v>
+        <v>-0.2095909458695726</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665293677419443</v>
+        <v>0.9665583398872734</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2144721390786506</v>
+        <v>-0.2168425197117605</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132641305847119</v>
+        <v>0.7132469598779183</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371206140157712</v>
+        <v>1.371234091595535</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.876059801182573</v>
+        <v>6.871942166132021</v>
       </c>
       <c r="E11" t="n">
-        <v>523.72892805522</v>
+        <v>521.2534414076652</v>
       </c>
       <c r="F11" t="n">
-        <v>1.081495512760257</v>
+        <v>1.087347024256542</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283751160053745</v>
+        <v>0.8283470480071986</v>
       </c>
       <c r="H11" t="n">
-        <v>1.305562530626814</v>
+        <v>1.312670850789453</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627049414946439</v>
+        <v>0.6626925365377049</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091904268889994</v>
+        <v>1.091862646785495</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.576033414393712</v>
+        <v>6.578307316944526</v>
       </c>
       <c r="E12" t="n">
-        <v>129.2336441636437</v>
+        <v>127.5734431979774</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2554713438644273</v>
+        <v>-0.2525826399650541</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6639213717563519</v>
+        <v>0.6637893230591371</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3847915652852052</v>
+        <v>-0.380516274050632</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883416839861567</v>
+        <v>0.7883918538862961</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041042477105363</v>
+        <v>1.040916736121451</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.763821657793398</v>
+        <v>4.759646062119159</v>
       </c>
       <c r="E13" t="n">
-        <v>96.11712680401595</v>
+        <v>94.72151954646887</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3727099211058922</v>
+        <v>-0.3733401213032658</v>
       </c>
       <c r="G13" t="n">
-        <v>0.858190626107366</v>
+        <v>0.8582086809901199</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4342973574489538</v>
+        <v>-0.43502254122219</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603518965772056</v>
+        <v>0.7603101805106108</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297883497936426</v>
+        <v>1.297858391271766</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.758127115886977</v>
+        <v>4.739329673090587</v>
       </c>
       <c r="E14" t="n">
-        <v>180.2246850021375</v>
+        <v>176.4955762769638</v>
       </c>
       <c r="F14" t="n">
-        <v>1.832490007778266</v>
+        <v>1.821270563062069</v>
       </c>
       <c r="G14" t="n">
-        <v>0.866549609692045</v>
+        <v>0.8666078161519452</v>
       </c>
       <c r="H14" t="n">
-        <v>2.114697170574571</v>
+        <v>2.101608742867304</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021975517122604</v>
+        <v>0.6021578482859316</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037933972540456</v>
+        <v>1.037950287034096</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.482153826962922</v>
+        <v>4.390778265405896</v>
       </c>
       <c r="E15" t="n">
-        <v>304.1701614267087</v>
+        <v>305.845462019283</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7133740326034699</v>
+        <v>0.6688403305408526</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9654354692499353</v>
+        <v>0.9645184911612</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7389142571669791</v>
+        <v>0.6934447982802532</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5117988143838573</v>
+        <v>0.5125443776485402</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9827879804524127</v>
+        <v>0.983299079130869</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.314800625444489</v>
+        <v>4.296138245568027</v>
       </c>
       <c r="E16" t="n">
-        <v>413.4959468357237</v>
+        <v>403.7221123847656</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02489626205083217</v>
+        <v>0.02347918223285062</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7974098560284284</v>
+        <v>0.7974403049428596</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03122141250527082</v>
+        <v>0.02944318475918145</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169090711359216</v>
+        <v>0.7168488000089213</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137058961654848</v>
+        <v>1.137023250343929</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.550749496867782</v>
+        <v>3.547208454447468</v>
       </c>
       <c r="E17" t="n">
-        <v>83.70087066946495</v>
+        <v>81.06379878499091</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1589357770557055</v>
+        <v>-0.1595037918724005</v>
       </c>
       <c r="G17" t="n">
-        <v>0.757010931514011</v>
+        <v>0.7570204427784452</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2099517595311817</v>
+        <v>-0.2106994512420082</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230773690970136</v>
+        <v>0.7230500361965152</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088740129284332</v>
+        <v>1.088728420729155</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.263102623784536</v>
+        <v>3.259208206310251</v>
       </c>
       <c r="E18" t="n">
-        <v>66.59020817295541</v>
+        <v>66.80005762987841</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4399284518786737</v>
+        <v>-0.4416548700405569</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531369147890248</v>
+        <v>0.7531428853688008</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5841281223108155</v>
+        <v>-0.5864157766348497</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641709794864558</v>
+        <v>0.764196092159684</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144726630439717</v>
+        <v>1.144789904379717</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.980725580331467</v>
+        <v>2.96217641506336</v>
       </c>
       <c r="E19" t="n">
-        <v>98.54283948501352</v>
+        <v>97.53894801215115</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1230604303844198</v>
+        <v>0.1144804418402692</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859858434922239</v>
+        <v>0.4859619934072318</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2532181380019743</v>
+        <v>0.2355748873232059</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173406243376189</v>
+        <v>0.7174893327265539</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934040208281098</v>
+        <v>0.6935237749909383</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.66345567379696</v>
+        <v>2.660740397506228</v>
       </c>
       <c r="E20" t="n">
-        <v>109.4426572855928</v>
+        <v>108.0353911043074</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3008178542327128</v>
+        <v>-0.300301416704851</v>
       </c>
       <c r="G20" t="n">
-        <v>0.785814055944586</v>
+        <v>0.7858129462247178</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3828104778185921</v>
+        <v>-0.3821538168180984</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.73202316795598</v>
+        <v>0.7320255239012184</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144147272729666</v>
+        <v>1.144165910212773</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.6350276938477</v>
+        <v>580.891069317092</v>
       </c>
       <c r="E2" t="n">
-        <v>8805.275331095778</v>
+        <v>8724.689320776988</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6842922662227795</v>
+        <v>0.6844341263172291</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027550012755896</v>
+        <v>0.502754569035442</v>
       </c>
       <c r="H2" t="n">
-        <v>1.361084950893763</v>
+        <v>1.361368286777279</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8217584788014</v>
+        <v>227.0093819261526</v>
       </c>
       <c r="E3" t="n">
-        <v>3861.298857583566</v>
+        <v>3782.355770379477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2869845393171591</v>
+        <v>0.2875124722753162</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035826550167415</v>
+        <v>0.6035804612961025</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4754684995200848</v>
+        <v>0.4763448963505617</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908979599409783</v>
+        <v>0.8908975837800115</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069567790764577</v>
+        <v>1.06956437137345</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.09667325917845</v>
+        <v>40.19178554430352</v>
       </c>
       <c r="E4" t="n">
-        <v>1453.153964579863</v>
+        <v>1454.364895326254</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9859344866133666</v>
+        <v>0.9916997901249314</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117774285096111</v>
+        <v>1.11773893532363</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8820515015950573</v>
+        <v>0.8872374029252139</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716272468544149</v>
+        <v>0.4716273252924</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048568004986521</v>
+        <v>1.048535919729645</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.32425532897325</v>
+        <v>37.35648475461629</v>
       </c>
       <c r="E5" t="n">
-        <v>317.7448094930319</v>
+        <v>309.6172472029135</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3345257069468589</v>
+        <v>-0.3341464236965374</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672516917812872</v>
+        <v>0.5672480818123197</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5897306465431231</v>
+        <v>-0.5890657622480836</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367678095907846</v>
+        <v>0.7367669296048477</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312851893665641</v>
+        <v>0.8312796209150709</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.91755098881112</v>
+        <v>10.96224364775805</v>
       </c>
       <c r="E6" t="n">
-        <v>186.7955679371414</v>
+        <v>183.924299864882</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3033774676357378</v>
+        <v>-0.3012170498787368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204413934002278</v>
+        <v>0.720440540929546</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4210994404470623</v>
+        <v>-0.4181011933199824</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.750044866681663</v>
+        <v>0.7500242870038986</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074804561851828</v>
+        <v>1.074774723730643</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.3437895006674</v>
+        <v>10.37462735316146</v>
       </c>
       <c r="E7" t="n">
-        <v>330.2446085207384</v>
+        <v>323.9646908030606</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2820956640815966</v>
+        <v>-0.2809331589283122</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178149259272702</v>
+        <v>1.178155005286223</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2394396651029943</v>
+        <v>-0.2384517806806429</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386497375391261</v>
+        <v>0.7386402700435043</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730941788616176</v>
+        <v>1.73092953272867</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.04402295863534</v>
+        <v>10.02600680700246</v>
       </c>
       <c r="E8" t="n">
-        <v>425.1301517937907</v>
+        <v>406.6749120316949</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5469641450045908</v>
+        <v>-0.5486265800805543</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8104371978007029</v>
+        <v>0.8105373086880634</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6749000989699099</v>
+        <v>-0.6768677693178146</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837492412936458</v>
+        <v>0.6836834429588746</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102198521559061</v>
+        <v>1.102229540973918</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.625927935365502</v>
+        <v>7.678717013017487</v>
       </c>
       <c r="E9" t="n">
-        <v>715.5621093536108</v>
+        <v>807.8329367547102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5045082088270669</v>
+        <v>0.52019448331116</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4861290471145399</v>
+        <v>0.4874538974632871</v>
       </c>
       <c r="H9" t="n">
-        <v>1.037807166269159</v>
+        <v>1.067166527990145</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6760506174615522</v>
+        <v>0.6741179641411037</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6536938302631217</v>
+        <v>0.6536020738728134</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.105108514635902</v>
+        <v>7.113854541826544</v>
       </c>
       <c r="E10" t="n">
-        <v>229.8639571107562</v>
+        <v>228.6903462741725</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2095909458695726</v>
+        <v>-0.207437257829275</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665583398872734</v>
+        <v>0.9665309997326335</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2168425197117605</v>
+        <v>-0.2146203876406006</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132469598779183</v>
+        <v>0.7132517248996996</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371234091595535</v>
+        <v>1.371205644238975</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.871942166132021</v>
+        <v>6.88948133857923</v>
       </c>
       <c r="E11" t="n">
-        <v>521.2534414076652</v>
+        <v>522.3080580110836</v>
       </c>
       <c r="F11" t="n">
-        <v>1.087347024256542</v>
+        <v>1.092278136486498</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283470480071986</v>
+        <v>0.8283286178301976</v>
       </c>
       <c r="H11" t="n">
-        <v>1.312670850789453</v>
+        <v>1.318653144385756</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626925365377049</v>
+        <v>0.6626919600949974</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091862646785495</v>
+        <v>1.09183834252529</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.578307316944526</v>
+        <v>6.485269381951884</v>
       </c>
       <c r="E12" t="n">
-        <v>127.5734431979774</v>
+        <v>124.4410922770871</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2525826399650541</v>
+        <v>-0.2514262921523949</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6637893230591371</v>
+        <v>0.6637407984061898</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.380516274050632</v>
+        <v>-0.3788019250227396</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883918538862961</v>
+        <v>0.7884330949909693</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040916736121451</v>
+        <v>1.040895984223821</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.759646062119159</v>
+        <v>4.764013455759246</v>
       </c>
       <c r="E13" t="n">
-        <v>94.72151954646887</v>
+        <v>94.45796922800326</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3733401213032658</v>
+        <v>-0.3727099211058922</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8582086809901199</v>
+        <v>0.858190626107366</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.43502254122219</v>
+        <v>-0.4342973574489538</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603101805106108</v>
+        <v>0.760317854887817</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297858391271766</v>
+        <v>1.297845302885327</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.739329673090587</v>
+        <v>4.747544246014638</v>
       </c>
       <c r="E14" t="n">
-        <v>176.4955762769638</v>
+        <v>173.2354284535498</v>
       </c>
       <c r="F14" t="n">
-        <v>1.821270563062069</v>
+        <v>1.827680165634882</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8666078161519452</v>
+        <v>0.8665729968864067</v>
       </c>
       <c r="H14" t="n">
-        <v>2.101608742867304</v>
+        <v>2.109089681079066</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021578482859316</v>
+        <v>0.6021666477206397</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037950287034096</v>
+        <v>1.037924642915636</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.390778265405896</v>
+        <v>4.407116262876785</v>
       </c>
       <c r="E15" t="n">
-        <v>305.845462019283</v>
+        <v>305.8991717880688</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6688403305408526</v>
+        <v>0.6702718267844736</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9645184911612</v>
+        <v>0.9645395032145995</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6934447982802532</v>
+        <v>0.6949138159200365</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5125443776485402</v>
+        <v>0.512532968028387</v>
       </c>
       <c r="N15" t="n">
-        <v>0.983299079130869</v>
+        <v>0.9832994562568651</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.296138245568027</v>
+        <v>4.326148758285809</v>
       </c>
       <c r="E16" t="n">
-        <v>403.7221123847656</v>
+        <v>397.2344330955848</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02347918223285062</v>
+        <v>0.02826399976036287</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7974403049428596</v>
+        <v>0.7973441671332764</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02944318475918145</v>
+        <v>0.03544767858775661</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168488000089213</v>
+        <v>0.7169027748703631</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137023250343929</v>
+        <v>1.136972752015403</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.547208454447468</v>
+        <v>3.569386290949379</v>
       </c>
       <c r="E17" t="n">
-        <v>81.06379878499091</v>
+        <v>82.76283103977694</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1595037918724005</v>
+        <v>-0.1513521136256459</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7570204427784452</v>
+        <v>0.7569243445823266</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2106994512420082</v>
+        <v>-0.1999567258061472</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230500361965152</v>
+        <v>0.7230757599256993</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088728420729155</v>
+        <v>1.088629879018652</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.259208206310251</v>
+        <v>3.260314879912331</v>
       </c>
       <c r="E18" t="n">
-        <v>66.80005762987841</v>
+        <v>66.28687381338973</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4416548700405569</v>
+        <v>-0.4408329500938456</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531428853688008</v>
+        <v>0.7531389214341092</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5864157766348497</v>
+        <v>-0.585327537254909</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764196092159684</v>
+        <v>0.7641903155594647</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144789904379717</v>
+        <v>1.144776209861304</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.96217641506336</v>
+        <v>2.973079285091976</v>
       </c>
       <c r="E19" t="n">
-        <v>97.53894801215115</v>
+        <v>97.3430018836096</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1144804418402692</v>
+        <v>0.1230604303844198</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859619934072318</v>
+        <v>0.4859858434922239</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2355748873232059</v>
+        <v>0.2532181380019743</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174893327265539</v>
+        <v>0.7173740266197967</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935237749909383</v>
+        <v>0.6934469478718114</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.660740397506228</v>
+        <v>2.665332114542992</v>
       </c>
       <c r="E20" t="n">
-        <v>108.0353911043074</v>
+        <v>105.9686129377092</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.300301416704851</v>
+        <v>-0.2987514712757685</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858129462247178</v>
+        <v>0.7858125786742638</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3821538168180984</v>
+        <v>-0.3801815844940902</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320255239012184</v>
+        <v>0.7320120084106129</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144165910212773</v>
+        <v>1.144145233833011</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.891069317092</v>
+        <v>581.0514817977404</v>
       </c>
       <c r="E2" t="n">
-        <v>8724.689320776988</v>
+        <v>8543.117932811634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6844341263172291</v>
+        <v>0.6850553877550689</v>
       </c>
       <c r="G2" t="n">
-        <v>0.502754569035442</v>
+        <v>0.5027527945477245</v>
       </c>
       <c r="H2" t="n">
-        <v>1.361368286777279</v>
+        <v>1.362608811297297</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.0093819261526</v>
+        <v>227.1250429193636</v>
       </c>
       <c r="E3" t="n">
-        <v>3782.355770379477</v>
+        <v>3708.825625824441</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2875124722753162</v>
+        <v>0.2883610614619414</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035804612961025</v>
+        <v>0.6035773504322144</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4763448963505617</v>
+        <v>0.4777532842401219</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908975837800115</v>
+        <v>0.8908966057452101</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06956437137345</v>
+        <v>1.069561459700057</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.19178554430352</v>
+        <v>40.39518484592099</v>
       </c>
       <c r="E4" t="n">
-        <v>1454.364895326254</v>
+        <v>1394.869687882631</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9916997901249314</v>
+        <v>1.007216927344809</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11773893532363</v>
+        <v>1.117669942871088</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8872374029252139</v>
+        <v>0.9011756411355699</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716273252924</v>
+        <v>0.4716183338778138</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048535919729645</v>
+        <v>1.048454910641252</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.35648475461629</v>
+        <v>37.33647689017784</v>
       </c>
       <c r="E5" t="n">
-        <v>309.6172472029135</v>
+        <v>305.6112252645191</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3341464236965374</v>
+        <v>-0.3352840940095975</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672480818123197</v>
+        <v>0.5672601259530503</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5890657622480836</v>
+        <v>-0.5910588082430237</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367669296048477</v>
+        <v>0.7367631474853445</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312796209150709</v>
+        <v>0.8312959378297978</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.96224364775805</v>
+        <v>10.96982431377189</v>
       </c>
       <c r="E6" t="n">
-        <v>183.924299864882</v>
+        <v>180.6098773979682</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3012170498787368</v>
+        <v>-0.2996727616349352</v>
       </c>
       <c r="G6" t="n">
-        <v>0.720440540929546</v>
+        <v>0.7204457391912906</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4181011933199824</v>
+        <v>-0.415954658807923</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500242870038986</v>
+        <v>0.7500084702403309</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074774723730643</v>
+        <v>1.074763606690866</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.37462735316146</v>
+        <v>10.37190644579257</v>
       </c>
       <c r="E7" t="n">
-        <v>323.9646908030606</v>
+        <v>320.3673551349686</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2809331589283122</v>
+        <v>-0.2813207184743625</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178155005286223</v>
+        <v>1.178152911952924</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2384517806806429</v>
+        <v>-0.2387811595763414</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386402700435043</v>
+        <v>0.7386492355226014</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73092953272867</v>
+        <v>1.730953576350822</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.02600680700246</v>
+        <v>10.01601301785521</v>
       </c>
       <c r="E8" t="n">
-        <v>406.6749120316949</v>
+        <v>387.2707025624628</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5486265800805543</v>
+        <v>-0.5495882690708039</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8105373086880634</v>
+        <v>0.810600439442079</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6768677693178146</v>
+        <v>-0.6780014447673816</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6836834429588746</v>
+        <v>0.6836226706236889</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102229540973918</v>
+        <v>1.102221296887345</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.678717013017487</v>
+        <v>7.651054012259292</v>
       </c>
       <c r="E9" t="n">
-        <v>807.8329367547102</v>
+        <v>809.04489704818</v>
       </c>
       <c r="F9" t="n">
-        <v>0.52019448331116</v>
+        <v>0.5128359367376534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4874538974632871</v>
+        <v>0.4868112395688378</v>
       </c>
       <c r="H9" t="n">
-        <v>1.067166527990145</v>
+        <v>1.053459524048511</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6741179641411037</v>
+        <v>0.6751526902481542</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6536020738728134</v>
+        <v>0.6537445870064476</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.113854541826544</v>
+        <v>7.124975575294664</v>
       </c>
       <c r="E10" t="n">
-        <v>228.6903462741725</v>
+        <v>224.858109249809</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.207437257829275</v>
+        <v>-0.2065753287228639</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665309997326335</v>
+        <v>0.9665215653384279</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2146203876406006</v>
+        <v>-0.2137306979286401</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132517248996996</v>
+        <v>0.713249419211809</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371205644238975</v>
+        <v>1.371192666872153</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.88948133857923</v>
+        <v>6.884885194517005</v>
       </c>
       <c r="E11" t="n">
-        <v>522.3080580110836</v>
+        <v>497.6295933542576</v>
       </c>
       <c r="F11" t="n">
-        <v>1.092278136486498</v>
+        <v>1.087347024256542</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283286178301976</v>
+        <v>0.8283470480071986</v>
       </c>
       <c r="H11" t="n">
-        <v>1.318653144385756</v>
+        <v>1.312670850789453</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626919600949974</v>
+        <v>0.6626874757942711</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09183834252529</v>
+        <v>1.091859101090323</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.485269381951884</v>
+        <v>6.487438739641387</v>
       </c>
       <c r="E12" t="n">
-        <v>124.4410922770871</v>
+        <v>122.8091176324782</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2514262921523949</v>
+        <v>-0.2521972456584646</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6637407984061898</v>
+        <v>0.6637728754287172</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3788019250227396</v>
+        <v>-0.3799450911512098</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884330949909693</v>
+        <v>0.7883817718568832</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040895984223821</v>
+        <v>1.040882201583377</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.764013455759246</v>
+        <v>4.766048291865308</v>
       </c>
       <c r="E13" t="n">
-        <v>94.45796922800326</v>
+        <v>94.19116385348148</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3727099211058922</v>
+        <v>-0.3733401213032658</v>
       </c>
       <c r="G13" t="n">
-        <v>0.858190626107366</v>
+        <v>0.8582086809901199</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4342973574489538</v>
+        <v>-0.43502254122219</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.760317854887817</v>
+        <v>0.7602967103929547</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297845302885327</v>
+        <v>1.297841094199082</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.747544246014638</v>
+        <v>4.755639785878063</v>
       </c>
       <c r="E14" t="n">
-        <v>173.2354284535498</v>
+        <v>169.3478103771228</v>
       </c>
       <c r="F14" t="n">
-        <v>1.827680165634882</v>
+        <v>1.832490007778266</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8665729968864067</v>
+        <v>0.866549609692045</v>
       </c>
       <c r="H14" t="n">
-        <v>2.109089681079066</v>
+        <v>2.114697170574571</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021666477206397</v>
+        <v>0.6021654880864196</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037924642915636</v>
+        <v>1.037898295803055</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.407116262876785</v>
+        <v>4.438670840430076</v>
       </c>
       <c r="E15" t="n">
-        <v>305.8991717880688</v>
+        <v>299.8532648625303</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6702718267844736</v>
+        <v>0.6903483697421617</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9645395032145995</v>
+        <v>0.9648936744443455</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6949138159200365</v>
+        <v>0.7154657430412874</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.512532968028387</v>
+        <v>0.5123062792020606</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9832994562568651</v>
+        <v>0.9832289219294692</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.326148758285809</v>
+        <v>4.31785014754577</v>
       </c>
       <c r="E16" t="n">
-        <v>397.2344330955848</v>
+        <v>392.2516075762184</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02826399976036287</v>
+        <v>0.02737745663232904</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7973441671332764</v>
+        <v>0.7973605492895229</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03544767858775661</v>
+        <v>0.03433510305560433</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169027748703631</v>
+        <v>0.7168815819369835</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136972752015403</v>
+        <v>1.136966513459239</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.569386290949379</v>
+        <v>3.552487258008179</v>
       </c>
       <c r="E17" t="n">
-        <v>82.76283103977694</v>
+        <v>82.64080922314713</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1513521136256459</v>
+        <v>-0.1598824094179762</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569243445823266</v>
+        <v>0.757027017478427</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1999567258061472</v>
+        <v>-0.2111977587676153</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230757599256993</v>
+        <v>0.7230365162915591</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088629879018652</v>
+        <v>1.088722297304371</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.260314879912331</v>
+        <v>3.257473917283316</v>
       </c>
       <c r="E18" t="n">
-        <v>66.28687381338973</v>
+        <v>65.80136652774723</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4408329500938456</v>
+        <v>-0.442887122398217</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531389214341092</v>
+        <v>0.7531526521088063</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.585327537254909</v>
+        <v>-0.5880442977371791</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641903155594647</v>
+        <v>0.7641997807374079</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144776209861304</v>
+        <v>1.144815300571564</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.973079285091976</v>
+        <v>2.9862061484092</v>
       </c>
       <c r="E19" t="n">
-        <v>97.3430018836096</v>
+        <v>98.45796618720757</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1230604303844198</v>
+        <v>0.1259244689469892</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859858434922239</v>
+        <v>0.4860130613230994</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2532181380019743</v>
+        <v>0.2590968823022539</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173740266197967</v>
+        <v>0.7173187882764258</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934469478718114</v>
+        <v>0.6934348332134597</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.665332114542992</v>
+        <v>2.670138338649387</v>
       </c>
       <c r="E20" t="n">
-        <v>105.9686129377092</v>
+        <v>104.8238545548774</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2987514712757685</v>
+        <v>-0.2972005773074909</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858125786742638</v>
+        <v>0.7858166535326181</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3801815844940902</v>
+        <v>-0.3782060051430999</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320120084106129</v>
+        <v>0.7319985910757717</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144145233833011</v>
+        <v>1.144134233499822</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.0514817977404</v>
+        <v>579.7780992297874</v>
       </c>
       <c r="E2" t="n">
-        <v>8543.117932811634</v>
+        <v>8168.15210414279</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6850553877550689</v>
+        <v>0.6803550205411333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027527945477245</v>
+        <v>0.5027710138469011</v>
       </c>
       <c r="H2" t="n">
-        <v>1.362608811297297</v>
+        <v>1.353210510955009</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.1250429193636</v>
+        <v>226.4597172544863</v>
       </c>
       <c r="E3" t="n">
-        <v>3708.825625824441</v>
+        <v>3552.30603310039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2883610614619414</v>
+        <v>0.2839312466162636</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035773504322144</v>
+        <v>0.6035992333588248</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4777532842401219</v>
+        <v>0.4703969636215118</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908966057452101</v>
+        <v>0.8909045379480659</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069561459700057</v>
+        <v>1.069571000099661</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.39518484592099</v>
+        <v>39.21675941733715</v>
       </c>
       <c r="E4" t="n">
-        <v>1394.869687882631</v>
+        <v>1413.601558814399</v>
       </c>
       <c r="F4" t="n">
-        <v>1.007216927344809</v>
+        <v>0.9317531924837246</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117669942871088</v>
+        <v>1.118366296452834</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9011756411355699</v>
+        <v>0.8331377612496037</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716183338778138</v>
+        <v>0.4716300593778948</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048454910641252</v>
+        <v>1.049096205380889</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.33647689017784</v>
+        <v>37.20757771800861</v>
       </c>
       <c r="E5" t="n">
-        <v>305.6112252645191</v>
+        <v>300.8373690872323</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3352840940095975</v>
+        <v>-0.3379365630302862</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672601259530503</v>
+        <v>0.5673023939252353</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5910588082430237</v>
+        <v>-0.5956903525332607</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367631474853445</v>
+        <v>0.7367863254790732</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312959378297978</v>
+        <v>0.8313539061401322</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.96982431377189</v>
+        <v>10.8803895324225</v>
       </c>
       <c r="E6" t="n">
-        <v>180.6098773979682</v>
+        <v>177.1906550192946</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2996727616349352</v>
+        <v>-0.3067686662364406</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204457391912906</v>
+        <v>0.7204618964038102</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.415954658807923</v>
+        <v>-0.4257944351639944</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500084702403309</v>
+        <v>0.7500654895882041</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074763606690866</v>
+        <v>1.074830469881315</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.37190644579257</v>
+        <v>10.2328980970805</v>
       </c>
       <c r="E7" t="n">
-        <v>320.3673551349686</v>
+        <v>310.6684383853454</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2813207184743625</v>
+        <v>-0.2921488582583445</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178152911952924</v>
+        <v>1.178166565915225</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2387811595763414</v>
+        <v>-0.2479690620242622</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386492355226014</v>
+        <v>0.7387030701513069</v>
       </c>
       <c r="N7" t="n">
-        <v>1.730953576350822</v>
+        <v>1.731037063437826</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.01601301785521</v>
+        <v>9.975446949842661</v>
       </c>
       <c r="E8" t="n">
-        <v>387.2707025624628</v>
+        <v>379.4056338747445</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5495882690708039</v>
+        <v>-0.5515972377407161</v>
       </c>
       <c r="G8" t="n">
-        <v>0.810600439442079</v>
+        <v>0.8107446911307291</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6780014447673816</v>
+        <v>-0.6803587415064225</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6836226706236889</v>
+        <v>0.6836954988188703</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102221296887345</v>
+        <v>1.102494934575058</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.651054012259292</v>
+        <v>7.640108408309902</v>
       </c>
       <c r="E9" t="n">
-        <v>809.04489704818</v>
+        <v>811.2357817357464</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5128359367376534</v>
+        <v>0.5072010815986188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4868112395688378</v>
+        <v>0.4863443782971592</v>
       </c>
       <c r="H9" t="n">
-        <v>1.053459524048511</v>
+        <v>1.042884639428722</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6751526902481542</v>
+        <v>0.6751740480326776</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6537445870064476</v>
+        <v>0.6531146259215731</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.124975575294664</v>
+        <v>7.075323062995588</v>
       </c>
       <c r="E10" t="n">
-        <v>224.858109249809</v>
+        <v>217.3632895030592</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2065753287228639</v>
+        <v>-0.2147531731362908</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665215653384279</v>
+        <v>0.9666458351188928</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2137306979286401</v>
+        <v>-0.2221632425591294</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713249419211809</v>
+        <v>0.7132683988813976</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371192666872153</v>
+        <v>1.371355762586936</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.884885194517005</v>
+        <v>6.848315107366727</v>
       </c>
       <c r="E11" t="n">
-        <v>497.6295933542576</v>
+        <v>461.6430410134079</v>
       </c>
       <c r="F11" t="n">
-        <v>1.087347024256542</v>
+        <v>1.073495552935965</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283470480071986</v>
+        <v>0.8284244005128699</v>
       </c>
       <c r="H11" t="n">
-        <v>1.312670850789453</v>
+        <v>1.295828022775976</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626874757942711</v>
+        <v>0.6627186173616608</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091859101090323</v>
+        <v>1.091972803077569</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.487438739641387</v>
+        <v>6.457996103110085</v>
       </c>
       <c r="E12" t="n">
-        <v>122.8091176324782</v>
+        <v>119.9344816906947</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2521972456584646</v>
+        <v>-0.2554713438644273</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6637728754287172</v>
+        <v>0.6639213717563519</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3799450911512098</v>
+        <v>-0.3847915652852052</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883817718568832</v>
+        <v>0.7884112526594923</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040882201583377</v>
+        <v>1.041116265571404</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.766048291865308</v>
+        <v>4.738032907219968</v>
       </c>
       <c r="E13" t="n">
-        <v>94.19116385348148</v>
+        <v>92.70933402139082</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3733401213032658</v>
+        <v>-0.3764884909046167</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8582086809901199</v>
+        <v>0.8583111433597249</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.43502254122219</v>
+        <v>-0.438638707905983</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7602967103929547</v>
+        <v>0.7603309740162879</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297841094199082</v>
+        <v>1.298007501757961</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.755639785878063</v>
+        <v>4.724719748572282</v>
       </c>
       <c r="E14" t="n">
-        <v>169.3478103771228</v>
+        <v>162.0962646423144</v>
       </c>
       <c r="F14" t="n">
-        <v>1.832490007778266</v>
+        <v>1.808463442773672</v>
       </c>
       <c r="G14" t="n">
-        <v>0.866549609692045</v>
+        <v>0.8666899201851433</v>
       </c>
       <c r="H14" t="n">
-        <v>2.114697170574571</v>
+        <v>2.086632601412216</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021654880864196</v>
+        <v>0.6022020563227066</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037898295803055</v>
+        <v>1.038091770916186</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.438670840430076</v>
+        <v>4.34507212054183</v>
       </c>
       <c r="E15" t="n">
-        <v>299.8532648625303</v>
+        <v>291.974609276</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6903483697421617</v>
+        <v>0.6445569745931294</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9648936744443455</v>
+        <v>0.9642487781659309</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7154657430412874</v>
+        <v>0.6684550597192586</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5123062792020606</v>
+        <v>0.5126938444448723</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9832289219294692</v>
+        <v>0.9832794641373277</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.31785014754577</v>
+        <v>4.287008131891933</v>
       </c>
       <c r="E16" t="n">
-        <v>392.2516075762184</v>
+        <v>384.87947135542</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02737745663232904</v>
+        <v>0.01816996921440794</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7973605492895229</v>
+        <v>0.7975692115725752</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03433510305560433</v>
+        <v>0.02278168333326462</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168815819369835</v>
+        <v>0.7168713857807534</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136966513459239</v>
+        <v>1.137206661102782</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.552487258008179</v>
+        <v>3.535388489790402</v>
       </c>
       <c r="E17" t="n">
-        <v>82.64080922314713</v>
+        <v>80.87073475644574</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1598824094179762</v>
+        <v>-0.1621531229446288</v>
       </c>
       <c r="G17" t="n">
-        <v>0.757027017478427</v>
+        <v>0.7570703941770566</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2111977587676153</v>
+        <v>-0.2141850007500174</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230365162915591</v>
+        <v>0.7230819517005062</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088722297304371</v>
+        <v>1.0888136410404</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.257473917283316</v>
+        <v>3.240237351670001</v>
       </c>
       <c r="E18" t="n">
-        <v>65.80136652774723</v>
+        <v>64.96298350109278</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.442887122398217</v>
+        <v>-0.446579354073715</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531526521088063</v>
+        <v>0.7532094602416388</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5880442977371791</v>
+        <v>-0.5929019451381384</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641997807374079</v>
+        <v>0.7642194389983017</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144815300571564</v>
+        <v>1.144889612370056</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.9862061484092</v>
+        <v>2.971666279367375</v>
       </c>
       <c r="E19" t="n">
-        <v>98.45796618720757</v>
+        <v>97.73135062044801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1259244689469892</v>
+        <v>0.1192448543832518</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4860130613230994</v>
+        <v>0.4859645383810026</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2590968823022539</v>
+        <v>0.2453776869820948</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173187882764258</v>
+        <v>0.717399737503713</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934348332134597</v>
+        <v>0.6934187187983079</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.670138338649387</v>
+        <v>2.654676541021865</v>
       </c>
       <c r="E20" t="n">
-        <v>104.8238545548774</v>
+        <v>104.1893359622672</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2972005773074909</v>
+        <v>-0.302882548673685</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858166535326181</v>
+        <v>0.785823430777346</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3782060051430999</v>
+        <v>-0.3854333388533223</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7319985910757717</v>
+        <v>0.7320378129649593</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144134233499822</v>
+        <v>1.144163943027231</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.7780992297874</v>
+        <v>580.1722208521164</v>
       </c>
       <c r="E2" t="n">
-        <v>8168.15210414279</v>
+        <v>7699.592654809722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6803550205411333</v>
+        <v>0.6814020026077008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027710138469011</v>
+        <v>0.5027659987861194</v>
       </c>
       <c r="H2" t="n">
-        <v>1.353210510955009</v>
+        <v>1.355306453206623</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.4597172544863</v>
+        <v>226.7385243073286</v>
       </c>
       <c r="E3" t="n">
-        <v>3552.30603310039</v>
+        <v>3401.041924999187</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2839312466162636</v>
+        <v>0.2857120901483516</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035992333588248</v>
+        <v>0.603588757327981</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4703969636215118</v>
+        <v>0.4733555532299287</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909045379480659</v>
+        <v>0.8909010446360619</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069571000099661</v>
+        <v>1.069558911566012</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.21675941733715</v>
+        <v>39.23258789079681</v>
       </c>
       <c r="E4" t="n">
-        <v>1413.601558814399</v>
+        <v>1472.826816752732</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9317531924837246</v>
+        <v>0.9271080134975198</v>
       </c>
       <c r="G4" t="n">
-        <v>1.118366296452834</v>
+        <v>1.118439097130487</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8331377612496037</v>
+        <v>0.8289302617157659</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716300593778948</v>
+        <v>0.471582265553516</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049096205380889</v>
+        <v>1.049068641439294</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.20757771800861</v>
+        <v>37.32247714345596</v>
       </c>
       <c r="E5" t="n">
-        <v>300.8373690872323</v>
+        <v>294.1337544469178</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3379365630302862</v>
+        <v>-0.3341464236965374</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5673023939252353</v>
+        <v>0.5672480818123197</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5956903525332607</v>
+        <v>-0.5890657622480836</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367863254790732</v>
+        <v>0.7367716734013025</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8313539061401322</v>
+        <v>0.831266075032121</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.8803895324225</v>
+        <v>10.89883569548543</v>
       </c>
       <c r="E6" t="n">
-        <v>177.1906550192946</v>
+        <v>171.9514020479797</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3067686662364406</v>
+        <v>-0.3061524253584075</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204618964038102</v>
+        <v>0.7204564265123495</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4257944351639944</v>
+        <v>-0.4249423200240683</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500654895882041</v>
+        <v>0.7500611151801404</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074830469881315</v>
+        <v>1.074826762377056</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.2328980970805</v>
+        <v>10.25703514457813</v>
       </c>
       <c r="E7" t="n">
-        <v>310.6684383853454</v>
+        <v>289.0278733981823</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2921488582583445</v>
+        <v>-0.2917629230683954</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178166565915225</v>
+        <v>1.178163675319933</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2479690620242622</v>
+        <v>-0.2476420969176175</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7387030701513069</v>
+        <v>0.7387019474910341</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731037063437826</v>
+        <v>1.73104745253918</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.975446949842661</v>
+        <v>9.991287186281841</v>
       </c>
       <c r="E8" t="n">
-        <v>379.4056338747445</v>
+        <v>365.8847529495506</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5515972377407161</v>
+        <v>-0.5505493902134506</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8107446911307291</v>
+        <v>0.8106673617746877</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6803587415064225</v>
+        <v>-0.6791310667894722</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6836954988188703</v>
+        <v>0.6837027953956814</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102494934575058</v>
+        <v>1.102412539271934</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.640108408309902</v>
+        <v>7.598768769452074</v>
       </c>
       <c r="E9" t="n">
-        <v>811.2357817357464</v>
+        <v>815.6626731055228</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5072010815986188</v>
+        <v>0.4981485379502024</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4863443782971592</v>
+        <v>0.4856405815682349</v>
       </c>
       <c r="H9" t="n">
-        <v>1.042884639428722</v>
+        <v>1.025755583154885</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6751740480326776</v>
+        <v>0.676401828423646</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531146259215731</v>
+        <v>0.6533619578940906</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.075323062995588</v>
+        <v>7.08034183670303</v>
       </c>
       <c r="E10" t="n">
-        <v>217.3632895030592</v>
+        <v>210.4584786439387</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2147531731362908</v>
+        <v>-0.2126033826919609</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9666458351188928</v>
+        <v>0.9666056253611117</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2221632425591294</v>
+        <v>-0.2199484227215571</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132683988813976</v>
+        <v>0.713264241330977</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371355762586936</v>
+        <v>1.371304403448219</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.848315107366727</v>
+        <v>6.851029632049866</v>
       </c>
       <c r="E11" t="n">
-        <v>461.6430410134079</v>
+        <v>431.6441173801588</v>
       </c>
       <c r="F11" t="n">
-        <v>1.073495552935965</v>
+        <v>1.075033344602561</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8284244005128699</v>
+        <v>0.8284139467855655</v>
       </c>
       <c r="H11" t="n">
-        <v>1.295828022775976</v>
+        <v>1.297700683063021</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627186173616608</v>
+        <v>0.6627088467531767</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091972803077569</v>
+        <v>1.09195381675374</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.457996103110085</v>
+        <v>6.466485410735077</v>
       </c>
       <c r="E12" t="n">
-        <v>119.9344816906947</v>
+        <v>116.2843783087961</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2554713438644273</v>
+        <v>-0.2548938507565598</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6639213717563519</v>
+        <v>0.6638937352115637</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3847915652852052</v>
+        <v>-0.3839377256291363</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884112526594923</v>
+        <v>0.7883975713897701</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041116265571404</v>
+        <v>1.0410652465867</v>
       </c>
     </row>
     <row r="13">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.738032907219968</v>
+        <v>4.739005481943229</v>
       </c>
       <c r="E13" t="n">
-        <v>92.70933402139082</v>
+        <v>90.75270252264247</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3764884909046167</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603309740162879</v>
+        <v>0.7603104081377238</v>
       </c>
       <c r="N13" t="n">
-        <v>1.298007501757961</v>
+        <v>1.297985339686033</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.724719748572282</v>
+        <v>4.730029602608993</v>
       </c>
       <c r="E14" t="n">
-        <v>162.0962646423144</v>
+        <v>155.7535898908849</v>
       </c>
       <c r="F14" t="n">
-        <v>1.808463442773672</v>
+        <v>1.813264223184841</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8666899201851433</v>
+        <v>0.8666571836363818</v>
       </c>
       <c r="H14" t="n">
-        <v>2.086632601412216</v>
+        <v>2.092250843149557</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6022020563227066</v>
+        <v>0.6021911078286145</v>
       </c>
       <c r="N14" t="n">
-        <v>1.038091770916186</v>
+        <v>1.038044041923442</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.34507212054183</v>
+        <v>4.328820741272981</v>
       </c>
       <c r="E15" t="n">
-        <v>291.974609276</v>
+        <v>287.6087479160463</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6445569745931294</v>
+        <v>0.6345866307209549</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9642487781659309</v>
+        <v>0.9641857733409912</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6684550597192586</v>
+        <v>0.6581580523865797</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5126938444448723</v>
+        <v>0.5127966405783407</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9832794641373277</v>
+        <v>0.9834221619131897</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.287008131891933</v>
+        <v>4.298378955208282</v>
       </c>
       <c r="E16" t="n">
-        <v>384.87947135542</v>
+        <v>381.067764743514</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01816996921440794</v>
+        <v>0.02206264512989908</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7975692115725752</v>
+        <v>0.7974724071757117</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02278168333326462</v>
+        <v>0.0276657159939051</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168713857807534</v>
+        <v>0.7168957153708542</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137206661102782</v>
+        <v>1.137118566512205</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.535388489790402</v>
+        <v>3.548180145788668</v>
       </c>
       <c r="E17" t="n">
-        <v>80.87073475644574</v>
+        <v>77.42611520699427</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1621531229446288</v>
+        <v>-0.1576099963239277</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7570703941770566</v>
+        <v>0.7569903756436019</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2141850007500174</v>
+        <v>-0.2082060768473124</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230819517005062</v>
+        <v>0.7230900927826761</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0888136410404</v>
+        <v>1.088721676249593</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.240237351670001</v>
+        <v>3.25070428711236</v>
       </c>
       <c r="E18" t="n">
-        <v>64.96298350109278</v>
+        <v>64.38007072955978</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.446579354073715</v>
+        <v>-0.442887122398217</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7532094602416388</v>
+        <v>0.7531526521088063</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5929019451381384</v>
+        <v>-0.5880442977371791</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642194389983017</v>
+        <v>0.7642033413055735</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144889612370056</v>
+        <v>1.144790567867244</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.971666279367375</v>
+        <v>2.974436334390121</v>
       </c>
       <c r="E19" t="n">
-        <v>97.73135062044801</v>
+        <v>95.77972791888216</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1192448543832518</v>
+        <v>0.1211521932308668</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859645383810026</v>
+        <v>0.4859730500284088</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2453776869820948</v>
+        <v>0.2492981724475967</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717399737503713</v>
+        <v>0.7173721255420382</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934187187983079</v>
+        <v>0.6934110912367689</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.654676541021865</v>
+        <v>2.661912485459339</v>
       </c>
       <c r="E20" t="n">
-        <v>104.1893359622672</v>
+        <v>102.2352838170759</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.302882548673685</v>
+        <v>-0.300301416704851</v>
       </c>
       <c r="G20" t="n">
-        <v>0.785823430777346</v>
+        <v>0.7858129462247178</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3854333388533223</v>
+        <v>-0.3821538168180984</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320378129649593</v>
+        <v>0.7320135033429066</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144163943027231</v>
+        <v>1.144122094825414</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.1722208521164</v>
+        <v>580.0818621597192</v>
       </c>
       <c r="E2" t="n">
-        <v>7699.592654809722</v>
+        <v>7549.026172202424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6814020026077008</v>
+        <v>0.6805528738578746</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027659987861194</v>
+        <v>0.5027700240719021</v>
       </c>
       <c r="H2" t="n">
-        <v>1.355306453206623</v>
+        <v>1.353606701422095</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.7385243073286</v>
+        <v>226.967174828314</v>
       </c>
       <c r="E3" t="n">
-        <v>3401.041924999187</v>
+        <v>3359.882312550752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2857120901483516</v>
+        <v>0.2863058564165122</v>
       </c>
       <c r="G3" t="n">
-        <v>0.603588757327981</v>
+        <v>0.6035857664097797</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4733555532299287</v>
+        <v>0.4743416302201809</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909010446360619</v>
+        <v>0.8908987453911146</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069558911566012</v>
+        <v>1.069542288291843</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.23258789079681</v>
+        <v>39.32912014732971</v>
       </c>
       <c r="E4" t="n">
-        <v>1472.826816752732</v>
+        <v>1486.382556634375</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9271080134975198</v>
+        <v>0.9310383481641427</v>
       </c>
       <c r="G4" t="n">
-        <v>1.118439097130487</v>
+        <v>1.118377271412436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8289302617157659</v>
+        <v>0.8324904054857115</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471582265553516</v>
+        <v>0.4716219102509066</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049068641439294</v>
+        <v>1.049090438711791</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.32247714345596</v>
+        <v>37.29427608700546</v>
       </c>
       <c r="E5" t="n">
-        <v>294.1337544469178</v>
+        <v>289.8333730675606</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3341464236965374</v>
+        <v>-0.3360422417202369</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672480818123197</v>
+        <v>0.5672701790416299</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5890657622480836</v>
+        <v>-0.5923848179150908</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367716734013025</v>
+        <v>0.7367848218616654</v>
       </c>
       <c r="N5" t="n">
-        <v>0.831266075032121</v>
+        <v>0.8313066368349149</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.89883569548543</v>
+        <v>10.95401574455709</v>
       </c>
       <c r="E6" t="n">
-        <v>171.9514020479797</v>
+        <v>172.4745115026037</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3061524253584075</v>
+        <v>-0.3021431698630492</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204564265123495</v>
+        <v>0.7204397448362025</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4249423200240683</v>
+        <v>-0.4193871479588397</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500611151801404</v>
+        <v>0.750011665773065</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074826762377056</v>
+        <v>1.074722412321955</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.25703514457813</v>
+        <v>10.23601522249934</v>
       </c>
       <c r="E7" t="n">
-        <v>289.0278733981823</v>
+        <v>284.5579495722221</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2917629230683954</v>
+        <v>-0.2967755355501995</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178163675319933</v>
+        <v>1.178215135743827</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2476420969176175</v>
+        <v>-0.2518856926437634</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7387019474910341</v>
+        <v>0.7387188677284158</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73104745253918</v>
+        <v>1.731148854038855</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.991287186281841</v>
+        <v>10.00538004416951</v>
       </c>
       <c r="E8" t="n">
-        <v>365.8847529495506</v>
+        <v>358.8283118596821</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5505493902134506</v>
+        <v>-0.5497630606219275</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8106673617746877</v>
+        <v>0.8106123251474818</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6791310667894722</v>
+        <v>-0.678207132517883</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837027953956814</v>
+        <v>0.6837594619948765</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102412539271934</v>
+        <v>1.102420233490276</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.598768769452074</v>
+        <v>7.62109627440577</v>
       </c>
       <c r="E9" t="n">
-        <v>815.6626731055228</v>
+        <v>818.1104672412152</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4981485379502024</v>
+        <v>0.505976883332891</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4856405815682349</v>
+        <v>0.4862458620324812</v>
       </c>
       <c r="H9" t="n">
-        <v>1.025755583154885</v>
+        <v>1.040578281155824</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.676401828423646</v>
+        <v>0.6753538459698361</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6533619578940906</v>
+        <v>0.6531575020144622</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.08034183670303</v>
+        <v>7.089540707431564</v>
       </c>
       <c r="E10" t="n">
-        <v>210.4584786439387</v>
+        <v>207.4124875773938</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2126033826919609</v>
+        <v>-0.2121732294936703</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9666056253611117</v>
+        <v>0.9665982268221521</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2199484227215571</v>
+        <v>-0.2195050886770444</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713264241330977</v>
+        <v>0.7132732909559792</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371304403448219</v>
+        <v>1.371300326725626</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.851029632049866</v>
+        <v>6.85906659047089</v>
       </c>
       <c r="E11" t="n">
-        <v>431.6441173801588</v>
+        <v>418.5501171333064</v>
       </c>
       <c r="F11" t="n">
-        <v>1.075033344602561</v>
+        <v>1.078109874087699</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8284139467855655</v>
+        <v>0.8283944334916357</v>
       </c>
       <c r="H11" t="n">
-        <v>1.297700683063021</v>
+        <v>1.301445097287202</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627088467531767</v>
+        <v>0.6627182960175311</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09195381675374</v>
+        <v>1.091934922746055</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.466485410735077</v>
+        <v>6.478754401194092</v>
       </c>
       <c r="E12" t="n">
-        <v>116.2843783087961</v>
+        <v>114.624227720129</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2548938507565598</v>
+        <v>-0.2529679792904751</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6638937352115637</v>
+        <v>0.6638060434087409</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3839377256291363</v>
+        <v>-0.3810871892510161</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883975713897701</v>
+        <v>0.7884999570599724</v>
       </c>
       <c r="N12" t="n">
-        <v>1.0410652465867</v>
+        <v>1.041054580949099</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.739005481943229</v>
+        <v>4.740910897915241</v>
       </c>
       <c r="E13" t="n">
-        <v>90.75270252264247</v>
+        <v>90.4538615192356</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3764884909046167</v>
+        <v>-0.3777466092909418</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8583111433597249</v>
+        <v>0.8583578149232118</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.438638707905983</v>
+        <v>-0.4400805849536476</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603104081377238</v>
+        <v>0.760305037715415</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297985339686033</v>
+        <v>1.298036357782504</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.730029602608993</v>
+        <v>4.73751381532739</v>
       </c>
       <c r="E14" t="n">
-        <v>155.7535898908849</v>
+        <v>153.565517806459</v>
       </c>
       <c r="F14" t="n">
-        <v>1.813264223184841</v>
+        <v>1.818067271616245</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8666571836363818</v>
+        <v>0.8666267840761923</v>
       </c>
       <c r="H14" t="n">
-        <v>2.092250843149557</v>
+        <v>2.097866469190968</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021911078286145</v>
+        <v>0.6022099586925436</v>
       </c>
       <c r="N14" t="n">
-        <v>1.038044041923442</v>
+        <v>1.038031813459386</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.328820741272981</v>
+        <v>4.33131268249907</v>
       </c>
       <c r="E15" t="n">
-        <v>287.6087479160463</v>
+        <v>286.5158862445979</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6345866307209549</v>
+        <v>0.6331636662465536</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9641857733409912</v>
+        <v>0.9641790615818525</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6581580523865797</v>
+        <v>0.6566868038056872</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5127966405783407</v>
+        <v>0.5127957402182938</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9834221619131897</v>
+        <v>0.9834057161612659</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.298378955208282</v>
+        <v>4.308917632157115</v>
       </c>
       <c r="E16" t="n">
-        <v>381.067764743514</v>
+        <v>380.5629813102228</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02206264512989908</v>
+        <v>0.02595942786937289</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7974724071757117</v>
+        <v>0.7973881044471413</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0276657159939051</v>
+        <v>0.03255557453715906</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168957153708542</v>
+        <v>0.7169509051574117</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137118566512205</v>
+        <v>1.137076786350677</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.548180145788668</v>
+        <v>3.564567486673109</v>
       </c>
       <c r="E17" t="n">
-        <v>77.42611520699427</v>
+        <v>77.4397581864054</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1576099963239277</v>
+        <v>-0.155525459715035</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569903756436019</v>
+        <v>0.7569627045242909</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2082060768473124</v>
+        <v>-0.2054598711210932</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230900927826761</v>
+        <v>0.7230961928473981</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088721676249593</v>
+        <v>1.088682346922708</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.25070428711236</v>
+        <v>3.243793794130716</v>
       </c>
       <c r="E18" t="n">
-        <v>64.38007072955978</v>
+        <v>65.110052672412</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.442887122398217</v>
+        <v>-0.4447751118337083</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531526521088063</v>
+        <v>0.7531765324693959</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5880442977371791</v>
+        <v>-0.5905323555096044</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642033413055735</v>
+        <v>0.7642158628953742</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144790567867244</v>
+        <v>1.144836458251793</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.974436334390121</v>
+        <v>2.975691372427427</v>
       </c>
       <c r="E19" t="n">
-        <v>95.77972791888216</v>
+        <v>93.13018262877104</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1211521932308668</v>
+        <v>0.1182915220376524</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859730500284088</v>
+        <v>0.485961888313183</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2492981724475967</v>
+        <v>0.2434172820594075</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173721255420382</v>
+        <v>0.7174205966998473</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934110912367689</v>
+        <v>0.6934364643767403</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.661912485459339</v>
+        <v>2.664419872854431</v>
       </c>
       <c r="E20" t="n">
-        <v>102.2352838170759</v>
+        <v>101.0366671007934</v>
       </c>
       <c r="F20" t="n">
         <v>-0.300301416704851</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320135033429066</v>
+        <v>0.7320088157775662</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144122094825414</v>
+        <v>1.144105608226103</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.0818621597192</v>
+        <v>579.8662077281505</v>
       </c>
       <c r="E2" t="n">
-        <v>7549.026172202424</v>
+        <v>7471.961634810388</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6805528738578746</v>
+        <v>0.6809813184838136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027700240719021</v>
+        <v>0.502767947921507</v>
       </c>
       <c r="H2" t="n">
-        <v>1.353606701422095</v>
+        <v>1.354464462778621</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.967174828314</v>
+        <v>226.8497329407746</v>
       </c>
       <c r="E3" t="n">
-        <v>3359.882312550752</v>
+        <v>3357.611377338028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2863058564165122</v>
+        <v>0.2872956354171843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035857664097797</v>
+        <v>0.6035813383311595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4743416302201809</v>
+        <v>0.4759849537620353</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908987453911146</v>
+        <v>0.8908956618286915</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069542288291843</v>
+        <v>1.069535156532963</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.32912014732971</v>
+        <v>39.56547061799837</v>
       </c>
       <c r="E4" t="n">
-        <v>1486.382556634375</v>
+        <v>1526.409912056297</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9310383481641427</v>
+        <v>0.9543081979197254</v>
       </c>
       <c r="G4" t="n">
-        <v>1.118377271412436</v>
+        <v>1.118062507706165</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8324904054857115</v>
+        <v>0.8535374286698867</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716219102509066</v>
+        <v>0.4716578877913331</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049090438711791</v>
+        <v>1.048879513866108</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.29427608700546</v>
+        <v>37.28085831326419</v>
       </c>
       <c r="E5" t="n">
-        <v>289.8333730675606</v>
+        <v>288.1400316972389</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3360422417202369</v>
+        <v>-0.3356631977915515</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672701790416299</v>
+        <v>0.5672649501377927</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5923848179150908</v>
+        <v>-0.5917220827939688</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367848218616654</v>
+        <v>0.7367818290332311</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8313066368349149</v>
+        <v>0.8312990301725012</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.95401574455709</v>
+        <v>10.91504025709351</v>
       </c>
       <c r="E6" t="n">
-        <v>172.4745115026037</v>
+        <v>172.8015330266868</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3021431698630492</v>
+        <v>-0.303685947587514</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204397448362025</v>
+        <v>0.7204422894720067</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4193871479588397</v>
+        <v>-0.4215270980415065</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.750011665773065</v>
+        <v>0.7500365832390363</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074722412321955</v>
+        <v>1.074766351853548</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.23601522249934</v>
+        <v>10.2292261911174</v>
       </c>
       <c r="E7" t="n">
-        <v>284.5579495722221</v>
+        <v>282.5768368911312</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2967755355501995</v>
+        <v>-0.2921488582583445</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178215135743827</v>
+        <v>1.178166565915225</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2518856926437634</v>
+        <v>-0.2479690620242622</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7387188677284158</v>
+        <v>0.7387035114364071</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731148854038855</v>
+        <v>1.731048653551847</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.00538004416951</v>
+        <v>9.987072826493629</v>
       </c>
       <c r="E8" t="n">
-        <v>358.8283118596821</v>
+        <v>345.7591177702704</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5497630606219275</v>
+        <v>-0.5500252127443356</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8106123251474818</v>
+        <v>0.8106303887089761</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.678207132517883</v>
+        <v>-0.6785154127028413</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837594619948765</v>
+        <v>0.6837366251607138</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102420233490276</v>
+        <v>1.102412531506731</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.62109627440577</v>
+        <v>7.606525904388559</v>
       </c>
       <c r="E9" t="n">
-        <v>818.1104672412152</v>
+        <v>819.4779770249413</v>
       </c>
       <c r="F9" t="n">
-        <v>0.505976883332891</v>
+        <v>0.4988819655883168</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4862458620324812</v>
+        <v>0.4856954707210843</v>
       </c>
       <c r="H9" t="n">
-        <v>1.040578281155824</v>
+        <v>1.027149717594968</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6753538459698361</v>
+        <v>0.6762616213215624</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531575020144622</v>
+        <v>0.6532978242870393</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.089540707431564</v>
+        <v>7.0835579573697</v>
       </c>
       <c r="E10" t="n">
-        <v>207.4124875773938</v>
+        <v>204.8903675236653</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2121732294936703</v>
+        <v>-0.2113127281145668</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665982268221521</v>
+        <v>0.9665840731970849</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2195050886770444</v>
+        <v>-0.2186180529704222</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132732909559792</v>
+        <v>0.7132709339462726</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371300326725626</v>
+        <v>1.371281378371624</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.85906659047089</v>
+        <v>6.856395263798862</v>
       </c>
       <c r="E11" t="n">
-        <v>418.5501171333064</v>
+        <v>416.2842326020098</v>
       </c>
       <c r="F11" t="n">
-        <v>1.078109874087699</v>
+        <v>1.078725331312286</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283944334916357</v>
+        <v>0.8283907539075548</v>
       </c>
       <c r="H11" t="n">
-        <v>1.301445097287202</v>
+        <v>1.302193833313436</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627182960175311</v>
+        <v>0.6627147470337555</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091934922746055</v>
+        <v>1.091928734101912</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.478754401194092</v>
+        <v>6.474258497321776</v>
       </c>
       <c r="E12" t="n">
-        <v>114.624227720129</v>
+        <v>112.4010136001625</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2529679792904751</v>
+        <v>-0.252775316501202</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6638060434087409</v>
+        <v>0.6637976491453214</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3810871892510161</v>
+        <v>-0.3808017651563924</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884999570599724</v>
+        <v>0.7884932396461993</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041054580949099</v>
+        <v>1.041036846139284</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.740910897915241</v>
+        <v>4.741457835732041</v>
       </c>
       <c r="E13" t="n">
-        <v>90.4538615192356</v>
+        <v>90.15257046746888</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3777466092909418</v>
+        <v>-0.3758591680987849</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8583578149232118</v>
+        <v>0.8582890260151793</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4400805849536476</v>
+        <v>-0.4379167817673317</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.760305037715415</v>
+        <v>0.7603291644339851</v>
       </c>
       <c r="N13" t="n">
-        <v>1.298036357782504</v>
+        <v>1.297978880099299</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.73751381532739</v>
+        <v>4.738600809334217</v>
       </c>
       <c r="E14" t="n">
-        <v>153.565517806459</v>
+        <v>151.2724065061891</v>
       </c>
       <c r="F14" t="n">
-        <v>1.818067271616245</v>
+        <v>1.819668791465936</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8666267840761923</v>
+        <v>0.866617170263308</v>
       </c>
       <c r="H14" t="n">
-        <v>2.097866469190968</v>
+        <v>2.099737754922463</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6022099586925436</v>
+        <v>0.6022051778754158</v>
       </c>
       <c r="N14" t="n">
-        <v>1.038031813459386</v>
+        <v>1.038016343973029</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.33131268249907</v>
+        <v>4.348770674398008</v>
       </c>
       <c r="E15" t="n">
-        <v>286.5158862445979</v>
+        <v>287.1300611782846</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6331636662465536</v>
+        <v>0.6516889092705458</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9641790615818525</v>
+        <v>0.9643109463728905</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6566868038056872</v>
+        <v>0.6758078519400561</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5127957402182938</v>
+        <v>0.512636760525892</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9834057161612659</v>
+        <v>0.9832393686429532</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.308917632157115</v>
+        <v>4.306624317252479</v>
       </c>
       <c r="E16" t="n">
-        <v>380.5629813102228</v>
+        <v>379.9263698573323</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02595942786937289</v>
+        <v>0.02578221238556844</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7973881044471413</v>
+        <v>0.7973916651172547</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03255557453715906</v>
+        <v>0.03233318520049645</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169509051574117</v>
+        <v>0.7169418102666362</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137076786350677</v>
+        <v>1.137072134856823</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.564567486673109</v>
+        <v>3.546605191236297</v>
       </c>
       <c r="E17" t="n">
-        <v>77.4397581864054</v>
+        <v>74.96053421394859</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.155525459715035</v>
+        <v>-0.1606395028690517</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569627045242909</v>
+        <v>0.7570407281132404</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2054598711210932</v>
+        <v>-0.2121940034447166</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230961928473981</v>
+        <v>0.7230829715142343</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088682346922708</v>
+        <v>1.088779150509577</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.243793794130716</v>
+        <v>3.249133187209511</v>
       </c>
       <c r="E18" t="n">
-        <v>65.110052672412</v>
+        <v>65.00491462574061</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4447751118337083</v>
+        <v>-0.4430513657798946</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531765324693959</v>
+        <v>0.7531543007558692</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5905323555096044</v>
+        <v>-0.5882610845284242</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642158628953742</v>
+        <v>0.7642045373951923</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144836458251793</v>
+        <v>1.144790427424376</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.975691372427427</v>
+        <v>2.977647322963098</v>
       </c>
       <c r="E19" t="n">
-        <v>93.13018262877104</v>
+        <v>92.47834027611059</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1182915220376524</v>
+        <v>0.1221061995620547</v>
       </c>
       <c r="G19" t="n">
-        <v>0.485961888313183</v>
+        <v>0.4859789115517475</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2434172820594075</v>
+        <v>0.2512582267657775</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174205966998473</v>
+        <v>0.7173435657360363</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934364643767403</v>
+        <v>0.6933891603994509</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.664419872854431</v>
+        <v>2.660826812709236</v>
       </c>
       <c r="E20" t="n">
-        <v>101.0366671007934</v>
+        <v>101.6522925975833</v>
       </c>
       <c r="F20" t="n">
         <v>-0.300301416704851</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320088157775662</v>
+        <v>0.7320112466341981</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144105608226103</v>
+        <v>1.144114132106632</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.8662077281505</v>
+        <v>579.6665185788328</v>
       </c>
       <c r="E2" t="n">
-        <v>7471.961634810388</v>
+        <v>7364.715233984815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6809813184838136</v>
+        <v>0.6792272239764254</v>
       </c>
       <c r="G2" t="n">
-        <v>0.502767947921507</v>
+        <v>0.5027770300977437</v>
       </c>
       <c r="H2" t="n">
-        <v>1.354464462778621</v>
+        <v>1.350951183757099</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8497329407746</v>
+        <v>226.6918027497649</v>
       </c>
       <c r="E3" t="n">
-        <v>3357.611377338028</v>
+        <v>3327.375855254086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2872956354171843</v>
+        <v>0.2847320705667913</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035813383311595</v>
+        <v>0.6035942429047342</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4759849537620353</v>
+        <v>0.4717276115765253</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908956618286915</v>
+        <v>0.8909026922055248</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069535156532963</v>
+        <v>1.069547142794176</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.56547061799837</v>
+        <v>39.34973015357448</v>
       </c>
       <c r="E4" t="n">
-        <v>1526.409912056297</v>
+        <v>1496.782274502215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9543081979197254</v>
+        <v>0.9392634753168916</v>
       </c>
       <c r="G4" t="n">
-        <v>1.118062507706165</v>
+        <v>1.118256003142517</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8535374286698867</v>
+        <v>0.8399360009491373</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716578877913331</v>
+        <v>0.4716797019955645</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048879513866108</v>
+        <v>1.049090604267405</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.28085831326419</v>
+        <v>37.23209847365634</v>
       </c>
       <c r="E5" t="n">
-        <v>288.1400316972389</v>
+        <v>287.6045168897488</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3356631977915515</v>
+        <v>-0.3375578185970007</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672649501377927</v>
+        <v>0.5672951416111104</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5917220827939688</v>
+        <v>-0.5950303357760851</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367818290332311</v>
+        <v>0.7367949644657633</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312990301725012</v>
+        <v>0.8313430779120908</v>
       </c>
     </row>
     <row r="6">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.91504025709351</v>
+        <v>10.927037288699</v>
       </c>
       <c r="E6" t="n">
-        <v>172.8015330266868</v>
+        <v>170.4216476228862</v>
       </c>
       <c r="F6" t="n">
         <v>-0.303685947587514</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500365832390363</v>
+        <v>0.7500276851880335</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074766351853548</v>
+        <v>1.074734186999768</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.2292261911174</v>
+        <v>10.19344537324878</v>
       </c>
       <c r="E7" t="n">
-        <v>282.5768368911312</v>
+        <v>277.1999561939575</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2921488582583445</v>
+        <v>-0.2979308921111387</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178166565915225</v>
+        <v>1.178231282596731</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2479690620242622</v>
+        <v>-0.2528628262649095</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7387035114364071</v>
+        <v>0.7387262784320611</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731048653551847</v>
+        <v>1.731165821866816</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.987072826493629</v>
+        <v>9.972382371541009</v>
       </c>
       <c r="E8" t="n">
-        <v>345.7591177702704</v>
+        <v>335.3756553157652</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5500252127443356</v>
+        <v>-0.5517718131816705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8106303887089761</v>
+        <v>0.8107580178535125</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6785154127028413</v>
+        <v>-0.6805628819342301</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837366251607138</v>
+        <v>0.6837272564906838</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102412531506731</v>
+        <v>1.102551075408197</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.606525904388559</v>
+        <v>7.621165337512346</v>
       </c>
       <c r="E9" t="n">
-        <v>819.4779770249413</v>
+        <v>822.4987644641518</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4988819655883168</v>
+        <v>0.5057320767132978</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4856954707210843</v>
+        <v>0.4862262864447206</v>
       </c>
       <c r="H9" t="n">
-        <v>1.027149717594968</v>
+        <v>1.040116692191208</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6762616213215624</v>
+        <v>0.6751965220361212</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532978242870393</v>
+        <v>0.6529699605930498</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.0835579573697</v>
+        <v>7.072564416106847</v>
       </c>
       <c r="E10" t="n">
-        <v>204.8903675236653</v>
+        <v>203.51990082475</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2113127281145668</v>
+        <v>-0.2141800547229007</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665840731970849</v>
+        <v>0.9666345882747395</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2186180529704222</v>
+        <v>-0.2215729266476712</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132709339462726</v>
+        <v>0.7132823136601526</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371281378371624</v>
+        <v>1.37135014989546</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.856395263798862</v>
+        <v>6.846788071474596</v>
       </c>
       <c r="E11" t="n">
-        <v>416.2842326020098</v>
+        <v>412.5174829275438</v>
       </c>
       <c r="F11" t="n">
-        <v>1.078725331312286</v>
+        <v>1.072880524609975</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8283907539075548</v>
+        <v>0.8284287121199716</v>
       </c>
       <c r="H11" t="n">
-        <v>1.302193833313436</v>
+        <v>1.295078875120642</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627147470337555</v>
+        <v>0.6627299624388457</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091928734101912</v>
+        <v>1.091984113036738</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.474258497321776</v>
+        <v>6.472487773168154</v>
       </c>
       <c r="E12" t="n">
-        <v>112.4010136001625</v>
+        <v>111.0768210944186</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.252775316501202</v>
+        <v>-0.2545087865270873</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6637976491453214</v>
+        <v>0.6638756515818331</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3808017651563924</v>
+        <v>-0.3833681592639568</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884932396461993</v>
+        <v>0.7884873642746963</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041036846139284</v>
+        <v>1.041132612243925</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.741457835732041</v>
+        <v>4.73664893193846</v>
       </c>
       <c r="E13" t="n">
-        <v>90.15257046746888</v>
+        <v>89.266237786662</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3758591680987849</v>
+        <v>-0.3771176379950814</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8582890260151793</v>
+        <v>0.8583340730174354</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4379167817673317</v>
+        <v>-0.4393599763194079</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603291644339851</v>
+        <v>0.7603427922374502</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297978880099299</v>
+        <v>1.298046821319073</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.738600809334217</v>
+        <v>4.724479115673041</v>
       </c>
       <c r="E14" t="n">
-        <v>151.2724065061891</v>
+        <v>149.7527930160799</v>
       </c>
       <c r="F14" t="n">
-        <v>1.819668791465936</v>
+        <v>1.803664932113271</v>
       </c>
       <c r="G14" t="n">
-        <v>0.866617170263308</v>
+        <v>0.8667249934576701</v>
       </c>
       <c r="H14" t="n">
-        <v>2.099737754922463</v>
+        <v>2.081011792353903</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6022051778754158</v>
+        <v>0.6022156663096782</v>
       </c>
       <c r="N14" t="n">
-        <v>1.038016343973029</v>
+        <v>1.038144820062464</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.348770674398008</v>
+        <v>4.303020903301076</v>
       </c>
       <c r="E15" t="n">
-        <v>287.1300611782846</v>
+        <v>284.551589430602</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6516889092705458</v>
+        <v>0.6246330868809418</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9643109463728905</v>
+        <v>0.9641508091063551</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6758078519400561</v>
+        <v>0.64785828210827</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.512636760525892</v>
+        <v>0.5128439664635138</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9832393686429532</v>
+        <v>0.9834556783848749</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.306624317252479</v>
+        <v>4.293896397806213</v>
       </c>
       <c r="E16" t="n">
-        <v>379.9263698573323</v>
+        <v>374.4441764047706</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02578221238556844</v>
+        <v>0.02223968257656783</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7973916651172547</v>
+        <v>0.7974683039874795</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03233318520049645</v>
+        <v>0.02788785769335981</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169418102666362</v>
+        <v>0.7169438282177178</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137072134856823</v>
+        <v>1.137164079735154</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.546605191236297</v>
+        <v>3.539658384392207</v>
       </c>
       <c r="E17" t="n">
-        <v>74.96053421394859</v>
+        <v>73.93799265358288</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1606395028690517</v>
+        <v>-0.1636659867435217</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7570407281132404</v>
+        <v>0.7571030530028964</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2121940034447166</v>
+        <v>-0.2161739885929315</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230829715142343</v>
+        <v>0.723087662087237</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088779150509577</v>
+        <v>1.088856180340111</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.249133187209511</v>
+        <v>3.243376383917894</v>
       </c>
       <c r="E18" t="n">
-        <v>65.00491462574061</v>
+        <v>64.81283619433995</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4430513657798946</v>
+        <v>-0.4455134073344411</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531543007558692</v>
+        <v>0.7531888110432167</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5882610845284242</v>
+        <v>-0.5915029549063208</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642045373951923</v>
+        <v>0.7642229174685741</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144790427424376</v>
+        <v>1.144849736807252</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.977647322963098</v>
+        <v>2.983606837629444</v>
       </c>
       <c r="E19" t="n">
-        <v>92.47834027611059</v>
+        <v>92.59026503468517</v>
       </c>
       <c r="F19" t="n">
         <v>0.1221061995620547</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173435657360363</v>
+        <v>0.7173150943936305</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6933891603994509</v>
+        <v>0.6933491149054388</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.660826812709236</v>
+        <v>2.655779016016281</v>
       </c>
       <c r="E20" t="n">
-        <v>101.6522925975833</v>
+        <v>101.7029641413076</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.300301416704851</v>
+        <v>-0.3033984581919745</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858129462247178</v>
+        <v>0.7858270084517756</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3821538168180984</v>
+        <v>-0.3860881019980791</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320112466341981</v>
+        <v>0.7320406134464453</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144114132106632</v>
+        <v>1.144159838045879</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-22.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.6665185788328</v>
+        <v>577.2711317029466</v>
       </c>
       <c r="E2" t="n">
-        <v>7364.715233984815</v>
+        <v>7657.434069874494</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6792272239764254</v>
+        <v>0.6684272183130053</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5027770300977437</v>
+        <v>0.5028669595731686</v>
       </c>
       <c r="H2" t="n">
-        <v>1.350951183757099</v>
+        <v>1.329232723661868</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.6918027497649</v>
+        <v>223.3357753161293</v>
       </c>
       <c r="E3" t="n">
-        <v>3327.375855254086</v>
+        <v>3889.515720245944</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2847320705667913</v>
+        <v>0.2571603302158698</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6035942429047342</v>
+        <v>0.6040304364164248</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4717276115765253</v>
+        <v>0.4257406824423344</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909026922055248</v>
+        <v>0.8908571318185516</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069547142794176</v>
+        <v>1.070073926856888</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.34973015357448</v>
+        <v>38.43740162473676</v>
       </c>
       <c r="E4" t="n">
-        <v>1496.782274502215</v>
+        <v>1593.397811081196</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9392634753168916</v>
+        <v>0.8712540189617255</v>
       </c>
       <c r="G4" t="n">
-        <v>1.118256003142517</v>
+        <v>1.119591183842134</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8399360009491373</v>
+        <v>0.778189424439569</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716797019955645</v>
+        <v>0.4719588199020865</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049090604267405</v>
+        <v>1.050776798593842</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.23209847365634</v>
+        <v>37.03180059077151</v>
       </c>
       <c r="E5" t="n">
-        <v>287.6045168897488</v>
+        <v>301.6055662704077</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3375578185970007</v>
+        <v>-0.3424768161342928</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5672951416111104</v>
+        <v>0.5674209782298553</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5950303357760851</v>
+        <v>-0.6035674204409828</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367949644657633</v>
+        <v>0.7368996757183047</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8313430779120908</v>
+        <v>0.8314969335194592</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.927037288699</v>
+        <v>10.76858927056385</v>
       </c>
       <c r="E6" t="n">
-        <v>170.4216476228862</v>
+        <v>174.7266402997987</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.303685947587514</v>
+        <v>-0.3184483802586411</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7204422894720067</v>
+        <v>0.7207128913071768</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4215270980415065</v>
+        <v>-0.4418519275838989</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500276851880335</v>
+        <v>0.750187284827607</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074734186999768</v>
+        <v>1.075174331455189</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.19344537324878</v>
+        <v>9.858850473694874</v>
       </c>
       <c r="E7" t="n">
-        <v>277.1999561939575</v>
+        <v>323.2986101312717</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2979308921111387</v>
+        <v>-0.3315857481595222</v>
       </c>
       <c r="G7" t="n">
-        <v>1.178231282596731</v>
+        <v>1.179416982693493</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2528628262649095</v>
+        <v>-0.2811437795327175</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7387262784320611</v>
+        <v>0.7387354566607357</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731165821866816</v>
+        <v>1.732619585989585</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.972382371541009</v>
+        <v>9.834437618689577</v>
       </c>
       <c r="E8" t="n">
-        <v>335.3756553157652</v>
+        <v>350.0588842949372</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5517718131816705</v>
+        <v>-0.5606501424284787</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8107580178535125</v>
+        <v>0.8116036334026523</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6805628819342301</v>
+        <v>-0.6907930415219435</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837272564906838</v>
+        <v>0.6837852704965962</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102551075408197</v>
+        <v>1.103597282417009</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.621165337512346</v>
+        <v>7.548677831809929</v>
       </c>
       <c r="E9" t="n">
-        <v>822.4987644641518</v>
+        <v>828.0488303671982</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5057320767132978</v>
+        <v>0.4764354686901386</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4862262864447206</v>
+        <v>0.4841876411117194</v>
       </c>
       <c r="H9" t="n">
-        <v>1.040116692191208</v>
+        <v>0.9839893219831441</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6751965220361212</v>
+        <v>0.6772511118539861</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6529699605930498</v>
+        <v>0.6520941812665622</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.072564416106847</v>
+        <v>6.949014827437345</v>
       </c>
       <c r="E10" t="n">
-        <v>203.51990082475</v>
+        <v>215.1436883493915</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2141800547229007</v>
+        <v>-0.2365877290913555</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9666345882747395</v>
+        <v>0.9673620455393179</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2215729266476712</v>
+        <v>-0.2445699933983398</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132823136601526</v>
+        <v>0.7133560556245223</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37135014989546</v>
+        <v>1.3722786117277</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.846788071474596</v>
+        <v>6.741807543427711</v>
       </c>
       <c r="E11" t="n">
-        <v>412.5174829275438</v>
+        <v>435.9187588496733</v>
       </c>
       <c r="F11" t="n">
-        <v>1.072880524609975</v>
+        <v>1.024758892966668</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8284287121199716</v>
+        <v>0.8289990483545635</v>
       </c>
       <c r="H11" t="n">
-        <v>1.295078875120642</v>
+        <v>1.236140011258948</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627299624388457</v>
+        <v>0.6628608992297892</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091984113036738</v>
+        <v>1.0927563328467</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.472487773168154</v>
+        <v>6.390680088358476</v>
       </c>
       <c r="E12" t="n">
-        <v>111.0768210944186</v>
+        <v>112.6326744411829</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2545087865270873</v>
+        <v>-0.2691024142026687</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6638756515818331</v>
+        <v>0.6647542454036515</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3833681592639568</v>
+        <v>-0.404814886197928</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,45 +1084,45 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884873642746963</v>
+        <v>0.7882931244053618</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041132612243925</v>
+        <v>1.042067272655496</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.73664893193846</v>
+        <v>4.661198062103157</v>
       </c>
       <c r="E13" t="n">
-        <v>89.266237786662</v>
+        <v>157.6766294744388</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3771176379950814</v>
+        <v>1.736725084108888</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8583340730174354</v>
+        <v>0.8674611821760467</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4393599763194079</v>
+        <v>2.002078156111</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4691011235955056</v>
+        <v>0.3000688231245698</v>
       </c>
       <c r="J13" t="n">
         <v>264</v>
@@ -1138,45 +1138,45 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603427922374502</v>
+        <v>0.6023761172579836</v>
       </c>
       <c r="N13" t="n">
-        <v>1.298046821319073</v>
+        <v>1.039117581387243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.724479115673041</v>
+        <v>4.650979824152505</v>
       </c>
       <c r="E14" t="n">
-        <v>149.7527930160799</v>
+        <v>98.02284387993976</v>
       </c>
       <c r="F14" t="n">
-        <v>1.803664932113271</v>
+        <v>-0.3959099466416898</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8667249934576701</v>
+        <v>0.8593992830400563</v>
       </c>
       <c r="H14" t="n">
-        <v>2.081011792353903</v>
+        <v>-0.4606821933120423</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3000688231245698</v>
+        <v>0.4691011235955056</v>
       </c>
       <c r="J14" t="n">
         <v>264</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6022156663096782</v>
+        <v>0.7602061917674571</v>
       </c>
       <c r="N14" t="n">
-        <v>1.038144820062464</v>
+        <v>1.29919185130417</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.303020903301076</v>
+        <v>4.237300837483274</v>
       </c>
       <c r="E15" t="n">
-        <v>284.551589430602</v>
+        <v>289.5890900854175</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6246330868809418</v>
+        <v>0.5863990616327004</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9641508091063551</v>
+        <v>0.9642786368248555</v>
       </c>
       <c r="H15" t="n">
-        <v>0.64785828210827</v>
+        <v>0.6081220087625042</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5128439664635138</v>
+        <v>0.5130980230551877</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9834556783848749</v>
+        <v>0.9838973366815407</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.293896397806213</v>
+        <v>4.227045415896777</v>
       </c>
       <c r="E16" t="n">
-        <v>374.4441764047706</v>
+        <v>390.0536248074178</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02223968257656783</v>
+        <v>-0.004923725601785334</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7974683039874795</v>
+        <v>0.7984042024362286</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02788785769335981</v>
+        <v>-0.0061669585239672</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169438282177178</v>
+        <v>0.7168907613081112</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137164079735154</v>
+        <v>1.138210784422838</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.539658384392207</v>
+        <v>3.496015530957842</v>
       </c>
       <c r="E17" t="n">
-        <v>73.93799265358288</v>
+        <v>76.6563465393742</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1636659867435217</v>
+        <v>-0.1815732134020568</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7571030530028964</v>
+        <v>0.757719488281352</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2161739885929315</v>
+        <v>-0.2396311777778059</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.723087662087237</v>
+        <v>0.7231331231744251</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088856180340111</v>
+        <v>1.08961634806173</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.243376383917894</v>
+        <v>3.199037519059596</v>
       </c>
       <c r="E18" t="n">
-        <v>64.81283619433995</v>
+        <v>66.83611837914816</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4455134073344411</v>
+        <v>-0.4567997908679058</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7531888110432167</v>
+        <v>0.7535836611957539</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5915029549063208</v>
+        <v>-0.6061699773892067</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642229174685741</v>
+        <v>0.7643111338678098</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144849736807252</v>
+        <v>1.145377264478989</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.983606837629444</v>
+        <v>2.961574714707959</v>
       </c>
       <c r="E19" t="n">
-        <v>92.59026503468517</v>
+        <v>93.92141528186875</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1221061995620547</v>
+        <v>0.11067296445824</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4859789115517475</v>
+        <v>0.4859792268227819</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2512582267657775</v>
+        <v>0.2277318830720274</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173150943936305</v>
+        <v>0.7174821935598737</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6933491149054388</v>
+        <v>0.6933870580427485</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.655779016016281</v>
+        <v>2.617579630352167</v>
       </c>
       <c r="E20" t="n">
-        <v>101.7029641413076</v>
+        <v>106.7488544035216</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3033984581919745</v>
+        <v>-0.3167748998125569</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7858270084517756</v>
+        <v>0.786093233856305</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3860881019980791</v>
+        <v>-0.4029737010437902</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320406134464453</v>
+        <v>0.7321807349690428</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144159838045879</v>
+        <v>1.144561818512864</v>
       </c>
     </row>
   </sheetData>
